--- a/बजेट माग estimate/नगर बजेट estimate/प‍‍‌‌‌‌ञ्चपाले भिमसेन मन्दिर अधुरो/प‍‍‌‌‌‌ञ्चपाले भिमसेन मन्दिर अधुरो.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/प‍‍‌‌‌‌ञ्चपाले भिमसेन मन्दिर अधुरो/प‍‍‌‌‌‌ञ्चपाले भिमसेन मन्दिर अधुरो.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8883805-A7E4-4379-A8A4-D6AD1AA9F4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A311324-1119-4D4B-BB44-C280597B93C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'bhotange chihaanpaati'!$A$1:$K$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'bhotange chihaanpaati'!$A$1:$K$153</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">chihaan!$A$1:$K$202</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'bhotange chihaanpaati'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">chihaan!$1:$8</definedName>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="148">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -494,14 +494,75 @@
       <t xml:space="preserve"> k~rkfn] led;]g dlGb/ cw'/f]</t>
     </r>
   </si>
+  <si>
+    <t>-flooring</t>
+  </si>
+  <si>
+    <t>Carved salwood lattice (jali) shutter of carved door/window including wood</t>
+  </si>
+  <si>
+    <t>-door</t>
+  </si>
+  <si>
+    <t>-window</t>
+  </si>
+  <si>
+    <t>-13% VAT for salwood</t>
+  </si>
+  <si>
+    <t>Water tap size</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>thickness</t>
+  </si>
+  <si>
+    <t>Height 1</t>
+  </si>
+  <si>
+    <t>Height 2</t>
+  </si>
+  <si>
+    <t>Width of stand tap</t>
+  </si>
+  <si>
+    <t>-for stand tap</t>
+  </si>
+  <si>
+    <t>-for wing walls of stand tap</t>
+  </si>
+  <si>
+    <t>-for side wall of stand tap</t>
+  </si>
+  <si>
+    <t>-for floor area</t>
+  </si>
+  <si>
+    <t>20mm GI pipe threaded-Medium class</t>
+  </si>
+  <si>
+    <t>-for pipe laying</t>
+  </si>
+  <si>
+    <t>sub-total</t>
+  </si>
+  <si>
+    <t>-13% VAT</t>
+  </si>
+  <si>
+    <t>-stand</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -710,7 +771,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -849,6 +910,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -868,24 +947,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -904,6 +965,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1430,12 +1514,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:Y153"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
     <col min="6" max="6" width="7.28515625" customWidth="1"/>
@@ -1444,116 +1528,116 @@
     <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+    </row>
+    <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+    </row>
+    <row r="6" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="59" t="s">
+      <c r="H7" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-    </row>
-    <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+    </row>
+    <row r="8" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -1587,262 +1671,325 @@
       <c r="K8" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
+      <c r="M8" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" s="44" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="76">
+        <v>1</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="76"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="78"/>
+      <c r="M9" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+    </row>
+    <row r="10" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="26">
+        <v>1</v>
+      </c>
+      <c r="D10" s="27">
+        <f>5.5/3.281</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="E10" s="27">
+        <f>5.5/3.281</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="F10" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="27">
+        <f>PRODUCT(C10:F10)</f>
+        <v>0.42150640397118022</v>
+      </c>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="79">
+        <f>5.5/3.281</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="N10" s="79">
+        <f>5.5/3.281</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="O10" s="79">
+        <v>0.23</v>
+      </c>
+      <c r="P10" s="79">
+        <f>TRUNC(2/3.281,1)</f>
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="79">
+        <f>TRUNC(4/3.281,1)</f>
+        <v>1.2</v>
+      </c>
+      <c r="R10" s="79">
+        <f>1.17/3.281</f>
+        <v>0.35659859798841814</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="2">
+        <f>SUM(G10)</f>
+        <v>0.42150640397118022</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="2">
+        <v>963.05</v>
+      </c>
+      <c r="J11" s="22">
+        <f>G11*I11</f>
+        <v>405.93174234444507</v>
+      </c>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="24">
+        <v>2</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+    </row>
+    <row r="14" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25" t="str">
+        <f>B10</f>
+        <v>-for stand tap</v>
+      </c>
+      <c r="C14" s="26">
+        <f>C10</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="27">
+        <f>D10</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="E14" s="27">
+        <f>E10</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="27">
+        <f>PRODUCT(C14:F14)</f>
+        <v>2.8100426931412015</v>
+      </c>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+    </row>
+    <row r="15" spans="1:25" s="10" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="2">
+        <f>SUM(G14)</f>
+        <v>2.8100426931412015</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1017.47</v>
+      </c>
+      <c r="J15" s="22">
+        <f>G15*I15</f>
+        <v>2859.1341389903782</v>
+      </c>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="22">
+        <f>0.13*G15*6360.9/10</f>
+        <v>232.36720736842426</v>
+      </c>
+      <c r="K16" s="26"/>
+    </row>
+    <row r="17" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="22">
+        <f>0.13*G15*2256.3/10</f>
+        <v>82.423891270948417</v>
+      </c>
+      <c r="K17" s="26"/>
+    </row>
+    <row r="18" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="26"/>
+    </row>
+    <row r="19" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
         <v>3</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B19" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16" t="s">
+      <c r="C19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C20" s="15">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D20" s="3">
         <f>15/3.281</f>
         <v>4.5717768972874122</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E20" s="3">
         <v>0.35</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F20" s="3">
         <v>0.1</v>
       </c>
-      <c r="G10" s="3">
-        <f>PRODUCT(C10:F10)</f>
+      <c r="G20" s="3">
+        <f>PRODUCT(C20:F20)</f>
         <v>0.32002438281011886</v>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="15">
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="15">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D21" s="3">
         <f>9.75/3.281</f>
         <v>2.9716549832368178</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E21" s="3">
         <v>0.35</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F21" s="3">
         <v>0.1</v>
       </c>
-      <c r="G11" s="3">
-        <f>PRODUCT(C11:F11)</f>
+      <c r="G21" s="3">
+        <f>PRODUCT(C21:F21)</f>
         <v>0.20801584882657723</v>
-      </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-    </row>
-    <row r="12" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="2">
-        <f>SUM(G10:G11)</f>
-        <v>0.52804023163669611</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="2">
-        <v>12884.61</v>
-      </c>
-      <c r="J12" s="22">
-        <f>G12*I12</f>
-        <v>6803.5924489484914</v>
-      </c>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="22">
-        <f>0.13*G12*4169.92</f>
-        <v>286.24511795184395</v>
-      </c>
-      <c r="K13" s="26"/>
-    </row>
-    <row r="14" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="22">
-        <f>0.13*G12*(1652.5+1106.96)</f>
-        <v>189.42376668698569</v>
-      </c>
-      <c r="K14" s="26"/>
-    </row>
-    <row r="15" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="22">
-        <f>0.13*G12*1414.16</f>
-        <v>97.075338616275545</v>
-      </c>
-      <c r="K15" s="26"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
-      <c r="B16" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="22">
-        <f>0.13*G12*36.4</f>
-        <v>2.4986863761048461</v>
-      </c>
-      <c r="K16" s="15"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="22">
-        <f>0.13*G12*392.92</f>
-        <v>26.972083815909787</v>
-      </c>
-      <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
-      <c r="B18" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="22">
-        <f>0.13*G12*14.15</f>
-        <v>0.97133000609570264</v>
-      </c>
-      <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="11">
-        <v>4</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="15">
-        <v>2</v>
-      </c>
-      <c r="D21" s="3">
-        <f>15/3.281</f>
-        <v>4.5717768972874122</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="G21" s="3">
-        <f t="shared" ref="G21:G22" si="0">PRODUCT(C21:F21)</f>
-        <v>0.48369399573300831</v>
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
@@ -1851,348 +1998,350 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="15">
-        <f>2*2</f>
-        <v>4</v>
-      </c>
-      <c r="D22" s="3">
-        <f>9.75/3.281</f>
-        <v>2.9716549832368178</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0.23</v>
+      <c r="B22" s="16" t="str">
+        <f>B14</f>
+        <v>-for stand tap</v>
+      </c>
+      <c r="C22" s="16">
+        <f t="shared" ref="C22:E22" si="0">C14</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="82">
+        <f t="shared" si="0"/>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="E22" s="82">
+        <f t="shared" si="0"/>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="F22" s="82">
+        <v>0.1</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="0"/>
-        <v>0.62880219445291075</v>
+        <f>PRODUCT(C22:F22)</f>
+        <v>0.28100426931412015</v>
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
-      <c r="B23" s="16" t="s">
+    <row r="23" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="2">
+        <f>SUM(G20:G22)</f>
+        <v>0.80904450095081626</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="2">
+        <v>12884.61</v>
+      </c>
+      <c r="J23" s="22">
+        <f>G23*I23</f>
+        <v>10424.222867395898</v>
+      </c>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="22">
+        <f>0.13*G23*4169.92</f>
+        <v>438.57460990262763</v>
+      </c>
+      <c r="K24" s="26"/>
+    </row>
+    <row r="25" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="22">
+        <f>0.13*G23*(1652.5+1106.96)</f>
+        <v>290.22837201718613</v>
+      </c>
+      <c r="K25" s="26"/>
+    </row>
+    <row r="26" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="22">
+        <f>0.13*G23*1414.16</f>
+        <v>148.73538829039884</v>
+      </c>
+      <c r="K26" s="26"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="22">
+        <f>0.13*G23*36.4</f>
+        <v>3.8283985784992627</v>
+      </c>
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="22">
+        <f>0.13*G23*392.92</f>
+        <v>41.325669490767318</v>
+      </c>
+      <c r="K28" s="15"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="22">
+        <f>0.13*G23*14.15</f>
+        <v>1.4882373594990266</v>
+      </c>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A31" s="11">
+        <v>4</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="15">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3">
+        <f>15/3.281</f>
+        <v>4.5717768972874122</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" ref="G32:G33" si="1">PRODUCT(C32:F32)</f>
+        <v>0.48369399573300831</v>
+      </c>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="15">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D33" s="3">
+        <f>9.75/3.281</f>
+        <v>2.9716549832368178</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.62880219445291075</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C34" s="15">
         <v>2</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D34" s="3">
         <f>8.17/3.281</f>
         <v>2.4900944833892105</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E34" s="3">
         <v>0.23</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F34" s="3">
         <v>0.23</v>
       </c>
-      <c r="G23" s="3">
-        <f t="shared" ref="G23:G25" si="1">PRODUCT(C23:F23)</f>
+      <c r="G34" s="3">
+        <f t="shared" ref="G34:G36" si="2">PRODUCT(C34:F34)</f>
         <v>0.26345199634257849</v>
       </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="15">
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="15">
         <v>2</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D35" s="3">
         <f>3.75/3.281</f>
         <v>1.1429442243218531</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E35" s="3">
         <v>0.23</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F35" s="3">
         <v>0.23</v>
       </c>
-      <c r="G24" s="3">
-        <f t="shared" si="1"/>
+      <c r="G35" s="3">
+        <f t="shared" si="2"/>
         <v>0.12092349893325208</v>
       </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="15">
-        <v>2</v>
-      </c>
-      <c r="D25" s="3">
-        <f>((17.667+8.17)/2)/3.281</f>
-        <v>3.9373666565071628</v>
-      </c>
-      <c r="E25" s="3">
-        <f>6.33/3.281</f>
-        <v>1.929289850655288</v>
-      </c>
-      <c r="F25" s="3">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G25" s="3">
-        <f t="shared" si="1"/>
-        <v>1.1394482293061723</v>
-      </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="15">
-        <v>2</v>
-      </c>
-      <c r="D26" s="3">
-        <f>((14.75+5.25)/2)/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E26" s="3">
-        <f>6.33/3.281</f>
-        <v>1.929289850655288</v>
-      </c>
-      <c r="F26" s="3">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G26" s="3">
-        <f t="shared" ref="G26:G27" si="2">PRODUCT(C26:F26)</f>
-        <v>0.88202827673969275</v>
-      </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" s="15">
-        <v>4</v>
-      </c>
-      <c r="D27" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F27" s="3">
-        <f>2.25/3.281</f>
-        <v>0.68576653459311188</v>
-      </c>
-      <c r="G27" s="3">
-        <f t="shared" si="2"/>
-        <v>0.14510819871990249</v>
-      </c>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-    </row>
-    <row r="28" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="2">
-        <f>SUM(G21:G27)</f>
-        <v>3.663456390227517</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="2">
-        <v>13957.29</v>
-      </c>
-      <c r="J28" s="22">
-        <f>G28*I28</f>
-        <v>51131.923240758624</v>
-      </c>
-      <c r="K28" s="20"/>
-    </row>
-    <row r="29" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="22">
-        <f>0.13*G28*5212.4</f>
-        <v>2482.402011494848</v>
-      </c>
-      <c r="K29" s="26"/>
-    </row>
-    <row r="30" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="22">
-        <f>0.13*G28*(1912.03+921.59)</f>
-        <v>1349.5096285419445</v>
-      </c>
-      <c r="K30" s="26"/>
-    </row>
-    <row r="31" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="22">
-        <f>0.13*G28*1350.6</f>
-        <v>643.22234608336692</v>
-      </c>
-      <c r="K31" s="26"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
-      <c r="B32" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="22">
-        <f>0.13*G28*56</f>
-        <v>26.669962520856323</v>
-      </c>
-      <c r="K32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
-      <c r="B33" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="22">
-        <f>0.13*G28*392.92</f>
-        <v>187.12788703026547</v>
-      </c>
-      <c r="K33" s="26"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="15"/>
-      <c r="B34" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="22">
-        <f>0.13*G28*14.15</f>
-        <v>6.7389280298235175</v>
-      </c>
-      <c r="K34" s="15"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
       <c r="H35" s="15"/>
       <c r="I35" s="15"/>
       <c r="J35" s="15"/>
       <c r="K35" s="15"/>
     </row>
-    <row r="36" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A36" s="11">
-        <v>5</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="15">
+        <v>2</v>
+      </c>
+      <c r="D36" s="3">
+        <f>((17.667+8.17)/2)/3.281</f>
+        <v>3.9373666565071628</v>
+      </c>
+      <c r="E36" s="3">
+        <f>6.33/3.281</f>
+        <v>1.929289850655288</v>
+      </c>
+      <c r="F36" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1394482293061723</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
-      <c r="B37" s="16" t="str">
-        <f>B21</f>
-        <v>-beam</v>
-      </c>
+      <c r="B37" s="16"/>
       <c r="C37" s="15">
-        <f>C21</f>
         <v>2</v>
       </c>
       <c r="D37" s="3">
-        <f>D21</f>
-        <v>4.5717768972874122</v>
-      </c>
-      <c r="E37" s="3"/>
+        <f>((14.75+5.25)/2)/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="E37" s="3">
+        <f>6.33/3.281</f>
+        <v>1.929289850655288</v>
+      </c>
       <c r="F37" s="3">
-        <f>0.23*2</f>
-        <v>0.46</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G37" s="3">
-        <f t="shared" ref="G37" si="3">PRODUCT(C37:F37)</f>
-        <v>4.2060347455044198</v>
+        <f t="shared" ref="G37:G38" si="3">PRODUCT(C37:F37)</f>
+        <v>0.88202827673969275</v>
       </c>
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
@@ -2201,323 +2350,294 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
-      <c r="B38" s="16"/>
+      <c r="B38" s="16" t="s">
+        <v>126</v>
+      </c>
       <c r="C38" s="15">
-        <f>C22</f>
         <v>4</v>
       </c>
       <c r="D38" s="3">
-        <f>D22</f>
-        <v>2.9716549832368178</v>
-      </c>
-      <c r="E38" s="3"/>
+        <v>0.23</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.23</v>
+      </c>
       <c r="F38" s="3">
-        <f t="shared" ref="F38:F40" si="4">0.23*2</f>
-        <v>0.46</v>
+        <f>2.25/3.281</f>
+        <v>0.68576653459311188</v>
       </c>
       <c r="G38" s="3">
-        <f t="shared" ref="G38:G43" si="5">PRODUCT(C38:F38)</f>
-        <v>5.467845169155745</v>
+        <f t="shared" si="3"/>
+        <v>0.14510819871990249</v>
       </c>
       <c r="H38" s="15"/>
       <c r="I38" s="15"/>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
-      <c r="B39" s="16" t="str">
-        <f t="shared" ref="B39:D39" si="6">B23</f>
-        <v>-upper beam</v>
-      </c>
-      <c r="C39" s="15">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="D39" s="3">
-        <f t="shared" si="6"/>
-        <v>2.4900944833892105</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3">
-        <f t="shared" si="4"/>
-        <v>0.46</v>
-      </c>
-      <c r="G39" s="3">
-        <f t="shared" si="5"/>
-        <v>2.2908869247180736</v>
-      </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="15">
-        <f>C24</f>
-        <v>2</v>
-      </c>
-      <c r="D40" s="3">
-        <f>D24</f>
-        <v>1.1429442243218531</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3">
-        <f t="shared" si="4"/>
-        <v>0.46</v>
-      </c>
-      <c r="G40" s="3">
-        <f t="shared" si="5"/>
-        <v>1.051508686376105</v>
-      </c>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
-      <c r="B41" s="16" t="str">
-        <f t="shared" ref="B41:D41" si="7">B25</f>
-        <v>-slab</v>
-      </c>
-      <c r="C41" s="15">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="D41" s="3">
-        <f t="shared" si="7"/>
-        <v>3.9373666565071628</v>
-      </c>
-      <c r="E41" s="3">
-        <f>E25</f>
-        <v>1.929289850655288</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3">
-        <f t="shared" si="5"/>
-        <v>15.19264305741563</v>
-      </c>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="15"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="15">
-        <f>C26</f>
-        <v>2</v>
-      </c>
-      <c r="D42" s="3">
-        <f>D26</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E42" s="3">
-        <f>E26</f>
-        <v>1.929289850655288</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3">
-        <f t="shared" si="5"/>
-        <v>11.760377023195904</v>
-      </c>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
+    <row r="39" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="2">
+        <f>SUM(G32:G38)</f>
+        <v>3.663456390227517</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="2">
+        <v>13957.29</v>
+      </c>
+      <c r="J39" s="22">
+        <f>G39*I39</f>
+        <v>51131.923240758624</v>
+      </c>
+      <c r="K39" s="20"/>
+    </row>
+    <row r="40" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="26"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="22">
+        <f>0.13*G39*5212.4</f>
+        <v>2482.402011494848</v>
+      </c>
+      <c r="K40" s="26"/>
+    </row>
+    <row r="41" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="22">
+        <f>0.13*G39*(1912.03+921.59)</f>
+        <v>1349.5096285419445</v>
+      </c>
+      <c r="K41" s="26"/>
+    </row>
+    <row r="42" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+      <c r="B42" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="26"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="22">
+        <f>0.13*G39*1350.6</f>
+        <v>643.22234608336692</v>
+      </c>
+      <c r="K42" s="26"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
-      <c r="B43" s="16" t="str">
-        <f>B27</f>
-        <v>-column</v>
-      </c>
-      <c r="C43" s="15">
-        <f>C27</f>
-        <v>4</v>
-      </c>
-      <c r="D43" s="3">
-        <f>0.23*4</f>
-        <v>0.92</v>
-      </c>
+      <c r="B43" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="15"/>
+      <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3">
-        <f>F27</f>
-        <v>0.68576653459311188</v>
-      </c>
-      <c r="G43" s="3">
-        <f t="shared" si="5"/>
-        <v>2.5236208473026518</v>
-      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
+      <c r="J43" s="22">
+        <f>0.13*G39*56</f>
+        <v>26.669962520856323</v>
+      </c>
       <c r="K43" s="15"/>
     </row>
-    <row r="44" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="2">
-        <f>SUM(G37:G43)</f>
-        <v>42.492916453668528</v>
-      </c>
-      <c r="H44" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="2">
-        <v>922.71</v>
-      </c>
+    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="B44" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
       <c r="J44" s="22">
-        <f>G44*I44</f>
-        <v>39208.638940964491</v>
-      </c>
-      <c r="K44" s="20"/>
-    </row>
-    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
+        <f>0.13*G39*392.92</f>
+        <v>187.12788703026547</v>
+      </c>
+      <c r="K44" s="26"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="15"/>
       <c r="B45" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="26"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
+        <v>45</v>
+      </c>
+      <c r="C45" s="15"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
       <c r="J45" s="22">
-        <f>0.13*G44*20062.02/100</f>
-        <v>1108.2418616773753</v>
-      </c>
-      <c r="K45" s="26"/>
-    </row>
-    <row r="46" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="26"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="22">
-        <f>0.13*G44*13328.25/100</f>
-        <v>736.26307784068979</v>
-      </c>
-      <c r="K46" s="26"/>
-    </row>
-    <row r="47" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="B47" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="22">
-        <f>0.13*G44*10137.6/100</f>
-        <v>560.00904679292307</v>
-      </c>
-      <c r="K47" s="26"/>
+        <f>0.13*G39*14.15</f>
+        <v>6.7389280298235175</v>
+      </c>
+      <c r="K45" s="15"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+    </row>
+    <row r="47" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A47" s="11">
+        <v>5</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
-      <c r="B48" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="15"/>
-      <c r="D48" s="3"/>
+      <c r="B48" s="16" t="str">
+        <f>B32</f>
+        <v>-beam</v>
+      </c>
+      <c r="C48" s="15">
+        <f>C32</f>
+        <v>2</v>
+      </c>
+      <c r="D48" s="3">
+        <f>D32</f>
+        <v>4.5717768972874122</v>
+      </c>
       <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="F48" s="3">
+        <f>0.23*2</f>
+        <v>0.46</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" ref="G48" si="4">PRODUCT(C48:F48)</f>
+        <v>4.2060347455044198</v>
+      </c>
       <c r="H48" s="15"/>
       <c r="I48" s="15"/>
-      <c r="J48" s="22">
-        <f>0.13*G44*3300/100</f>
-        <v>182.29461158623798</v>
-      </c>
+      <c r="J48" s="15"/>
       <c r="K48" s="15"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="3"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="15">
+        <f>C33</f>
+        <v>4</v>
+      </c>
+      <c r="D49" s="3">
+        <f>D33</f>
+        <v>2.9716549832368178</v>
+      </c>
       <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="F49" s="3">
+        <f t="shared" ref="F49:F51" si="5">0.23*2</f>
+        <v>0.46</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" ref="G49:G54" si="6">PRODUCT(C49:F49)</f>
+        <v>5.467845169155745</v>
+      </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
       <c r="J49" s="15"/>
       <c r="K49" s="15"/>
     </row>
-    <row r="50" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>6</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="F50" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G50" s="23"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="16" t="str">
+        <f t="shared" ref="B50:D50" si="7">B34</f>
+        <v>-upper beam</v>
+      </c>
+      <c r="C50" s="15">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="7"/>
+        <v>2.4900944833892105</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3">
+        <f t="shared" si="5"/>
+        <v>0.46</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="6"/>
+        <v>2.2908869247180736</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="15"/>
-      <c r="B51" s="16" t="str">
-        <f>B21</f>
-        <v>-beam</v>
-      </c>
+      <c r="B51" s="16"/>
       <c r="C51" s="15">
-        <f>C37*(3*2)</f>
-        <v>12</v>
+        <f>C35</f>
+        <v>2</v>
       </c>
       <c r="D51" s="3">
-        <f>D21+(0.583/3.281)*2</f>
-        <v>4.9271563547698873</v>
-      </c>
-      <c r="E51" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
+        <f>D35</f>
+        <v>1.1429442243218531</v>
+      </c>
+      <c r="E51" s="3"/>
       <c r="F51" s="3">
-        <f t="shared" ref="F51:F52" si="8">PRODUCT(C51:E51)</f>
-        <v>52.556334450878794</v>
+        <f t="shared" si="5"/>
+        <v>0.46</v>
       </c>
       <c r="G51" s="3">
-        <f t="shared" ref="G51:G52" si="9">F51/1000</f>
-        <v>5.2556334450878796E-2</v>
+        <f t="shared" si="6"/>
+        <v>1.051508686376105</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
@@ -2526,28 +2646,26 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="15"/>
-      <c r="B52" s="16" t="s">
-        <v>125</v>
+      <c r="B52" s="16" t="str">
+        <f t="shared" ref="B52:D52" si="8">B36</f>
+        <v>-slab</v>
       </c>
       <c r="C52" s="15">
-        <f>2*(TRUNC((D37-0.1-0.23*2)/0.125,0))</f>
-        <v>64</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="D52" s="3">
-        <f>((0.583*4)+0.17*2)/3.281</f>
-        <v>0.81438585797013097</v>
+        <f t="shared" si="8"/>
+        <v>3.9373666565071628</v>
       </c>
       <c r="E52" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F52" s="3">
-        <f t="shared" si="8"/>
-        <v>20.590891816331212</v>
-      </c>
+        <f>E36</f>
+        <v>1.929289850655288</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3">
-        <f t="shared" si="9"/>
-        <v>2.0590891816331211E-2</v>
+        <f t="shared" si="6"/>
+        <v>15.19264305741563</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="15"/>
@@ -2556,29 +2674,23 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="15"/>
-      <c r="B53" s="16" t="str">
-        <f>B37</f>
-        <v>-beam</v>
-      </c>
+      <c r="B53" s="16"/>
       <c r="C53" s="15">
-        <f>C39*(3*2)</f>
-        <v>12</v>
+        <f>C37</f>
+        <v>2</v>
       </c>
       <c r="D53" s="3">
-        <f>D22+0.23*2+(0.583/3.281)*2</f>
-        <v>3.7870344407192924</v>
+        <f>D37</f>
+        <v>3.047851264858275</v>
       </c>
       <c r="E53" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F53" s="3">
-        <f t="shared" ref="F53:F56" si="10">PRODUCT(C53:E53)</f>
-        <v>40.395034034339119</v>
-      </c>
+        <f>E37</f>
+        <v>1.929289850655288</v>
+      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="3">
-        <f t="shared" ref="G53:G56" si="11">F53/1000</f>
-        <v>4.0395034034339118E-2</v>
+        <f t="shared" si="6"/>
+        <v>11.760377023195904</v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="15"/>
@@ -2587,266 +2699,192 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="15"/>
-      <c r="B54" s="16" t="s">
-        <v>125</v>
+      <c r="B54" s="16" t="str">
+        <f>B38</f>
+        <v>-column</v>
       </c>
       <c r="C54" s="15">
-        <f>4*(TRUNC((D38-0.1)/0.125,0))</f>
-        <v>88</v>
+        <f>C38</f>
+        <v>4</v>
       </c>
       <c r="D54" s="3">
-        <f>((0.583*4)+0.17*2)/3.281</f>
-        <v>0.81438585797013097</v>
-      </c>
-      <c r="E54" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
-      </c>
+        <f>0.23*4</f>
+        <v>0.92</v>
+      </c>
+      <c r="E54" s="3"/>
       <c r="F54" s="3">
-        <f t="shared" si="10"/>
-        <v>28.312476247455418</v>
+        <f>F38</f>
+        <v>0.68576653459311188</v>
       </c>
       <c r="G54" s="3">
-        <f t="shared" si="11"/>
-        <v>2.8312476247455417E-2</v>
+        <f t="shared" si="6"/>
+        <v>2.5236208473026518</v>
       </c>
       <c r="H54" s="15"/>
       <c r="I54" s="15"/>
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
-      <c r="B55" s="16" t="str">
-        <f>B39</f>
-        <v>-upper beam</v>
-      </c>
-      <c r="C55" s="15">
-        <f>C39*(3*2)</f>
-        <v>12</v>
-      </c>
-      <c r="D55" s="3">
-        <f>D23+(0.583/3.281)*2</f>
-        <v>2.8454739408716851</v>
-      </c>
-      <c r="E55" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F55" s="3">
-        <f t="shared" si="10"/>
-        <v>30.351722035964642</v>
-      </c>
-      <c r="G55" s="3">
-        <f t="shared" si="11"/>
-        <v>3.0351722035964642E-2</v>
-      </c>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
-      <c r="K55" s="15"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
-      <c r="B56" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C56" s="15">
-        <f>2*(TRUNC((D39-0.1-0.23*2)/0.125,0))</f>
-        <v>30</v>
-      </c>
-      <c r="D56" s="3">
-        <f>((0.583*4)+0.17*2)/3.281</f>
-        <v>0.81438585797013097</v>
-      </c>
-      <c r="E56" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F56" s="3">
-        <f t="shared" si="10"/>
-        <v>9.6519805389052564</v>
-      </c>
-      <c r="G56" s="3">
-        <f t="shared" si="11"/>
-        <v>9.6519805389052565E-3</v>
-      </c>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
-      <c r="B57" s="16" t="str">
-        <f>B23</f>
-        <v>-upper beam</v>
-      </c>
-      <c r="C57" s="15">
-        <f>C40*(3*2)</f>
-        <v>12</v>
-      </c>
-      <c r="D57" s="3">
-        <f>D24+0.23*2+(0.583/3.281)*2</f>
-        <v>1.9583236818043277</v>
-      </c>
-      <c r="E57" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F57" s="3">
-        <f t="shared" ref="F57:F58" si="12">PRODUCT(C57:E57)</f>
-        <v>20.888785939246162</v>
-      </c>
-      <c r="G57" s="3">
-        <f t="shared" ref="G57:G58" si="13">F57/1000</f>
-        <v>2.0888785939246163E-2</v>
-      </c>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="15"/>
-      <c r="B58" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C58" s="15">
-        <f>2*(TRUNC((D40-0.1)/0.125,0))</f>
+    <row r="55" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D58" s="3">
-        <f>((0.583*4)+0.17*2)/3.281</f>
-        <v>0.81438585797013097</v>
-      </c>
-      <c r="E58" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F58" s="3">
-        <f t="shared" si="12"/>
-        <v>5.1477229540828029</v>
-      </c>
-      <c r="G58" s="3">
-        <f t="shared" si="13"/>
-        <v>5.1477229540828028E-3</v>
-      </c>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="2">
+        <f>SUM(G48:G54)</f>
+        <v>42.492916453668528</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I55" s="2">
+        <v>922.71</v>
+      </c>
+      <c r="J55" s="22">
+        <f>G55*I55</f>
+        <v>39208.638940964491</v>
+      </c>
+      <c r="K55" s="20"/>
+    </row>
+    <row r="56" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="24"/>
+      <c r="B56" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="22">
+        <f>0.13*G55*20062.02/100</f>
+        <v>1108.2418616773753</v>
+      </c>
+      <c r="K56" s="26"/>
+    </row>
+    <row r="57" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="24"/>
+      <c r="B57" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" s="26"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="22">
+        <f>0.13*G55*13328.25/100</f>
+        <v>736.26307784068979</v>
+      </c>
+      <c r="K57" s="26"/>
+    </row>
+    <row r="58" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="24"/>
+      <c r="B58" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" s="26"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="22">
+        <f>0.13*G55*10137.6/100</f>
+        <v>560.00904679292307</v>
+      </c>
+      <c r="K58" s="26"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="15"/>
-      <c r="B59" s="16" t="str">
-        <f>B41</f>
-        <v>-slab</v>
-      </c>
-      <c r="C59" s="15">
-        <f>TRUNC(((E41-0.1)/0.15),0)</f>
-        <v>12</v>
-      </c>
-      <c r="D59" s="3">
-        <f>D41*C41+D42*C42</f>
-        <v>13.970435842730875</v>
-      </c>
-      <c r="E59" s="3">
-        <f t="shared" ref="E59:E61" si="14">8*8/162</f>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F59" s="3">
-        <f t="shared" ref="F59:F61" si="15">PRODUCT(C59:E59)</f>
-        <v>66.230214365538956</v>
-      </c>
-      <c r="G59" s="3">
-        <f t="shared" ref="G59:G61" si="16">F59/1000</f>
-        <v>6.6230214365538956E-2</v>
-      </c>
+      <c r="B59" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" s="15"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
       <c r="H59" s="15"/>
       <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
+      <c r="J59" s="22">
+        <f>0.13*G55*3300/100</f>
+        <v>182.29461158623798</v>
+      </c>
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="15"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="15">
-        <f>2*(TRUNC(((D41-0.1)/0.15),0))</f>
-        <v>50</v>
-      </c>
-      <c r="D60" s="3">
-        <f>E41</f>
-        <v>1.929289850655288</v>
-      </c>
-      <c r="E60" s="3">
-        <f t="shared" si="14"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F60" s="3">
-        <f t="shared" si="15"/>
-        <v>38.109429148746429</v>
-      </c>
-      <c r="G60" s="3">
-        <f t="shared" si="16"/>
-        <v>3.8109429148746432E-2</v>
-      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
       <c r="H60" s="15"/>
       <c r="I60" s="15"/>
       <c r="J60" s="15"/>
       <c r="K60" s="15"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="15">
-        <f>2*(TRUNC(((D42-0.1)/0.15),0))</f>
-        <v>38</v>
-      </c>
-      <c r="D61" s="3">
-        <f>E42</f>
-        <v>1.929289850655288</v>
-      </c>
-      <c r="E61" s="3">
-        <f t="shared" si="14"/>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F61" s="3">
-        <f t="shared" si="15"/>
-        <v>28.963166153047286</v>
-      </c>
-      <c r="G61" s="3">
-        <f t="shared" si="16"/>
-        <v>2.8963166153047285E-2</v>
-      </c>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
+    <row r="61" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>6</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G61" s="23"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="15"/>
-      <c r="B62" s="16" t="s">
-        <v>126</v>
+      <c r="B62" s="16" t="str">
+        <f>B32</f>
+        <v>-beam</v>
       </c>
       <c r="C62" s="15">
-        <v>8</v>
+        <f>C48*(3*2)</f>
+        <v>12</v>
       </c>
       <c r="D62" s="3">
-        <f>((3.75-0.33)/3.281)+(0.45*2)</f>
-        <v>1.9423651325815299</v>
+        <f>D32+(0.583/3.281)*2</f>
+        <v>4.9271563547698873</v>
       </c>
       <c r="E62" s="3">
         <f>12*12/162</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="F62" s="3">
-        <f t="shared" ref="F62:F63" si="17">PRODUCT(C62:E62)</f>
-        <v>13.812374276135323</v>
+        <f t="shared" ref="F62:F63" si="9">PRODUCT(C62:E62)</f>
+        <v>52.556334450878794</v>
       </c>
       <c r="G62" s="3">
-        <f t="shared" ref="G62:G63" si="18">F62/1000</f>
-        <v>1.3812374276135323E-2</v>
+        <f t="shared" ref="G62:G63" si="10">F62/1000</f>
+        <v>5.2556334450878796E-2</v>
       </c>
       <c r="H62" s="15"/>
       <c r="I62" s="15"/>
@@ -2855,26 +2893,28 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="15"/>
-      <c r="B63" s="16"/>
+      <c r="B63" s="16" t="s">
+        <v>125</v>
+      </c>
       <c r="C63" s="15">
-        <f>4*(TRUNC((2.25-0.17*2)/0.33,0)+1)</f>
-        <v>24</v>
+        <f>2*(TRUNC((D48-0.1-0.23*2)/0.125,0))</f>
+        <v>64</v>
       </c>
       <c r="D63" s="3">
-        <f>(6*4+2*2)/12/3.281</f>
-        <v>0.7111652951335975</v>
+        <f>((0.583*4)+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
       </c>
       <c r="E63" s="3">
         <f>8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
       <c r="F63" s="3">
-        <f t="shared" si="17"/>
-        <v>6.7429005760815173</v>
+        <f t="shared" si="9"/>
+        <v>20.590891816331212</v>
       </c>
       <c r="G63" s="3">
-        <f t="shared" si="18"/>
-        <v>6.7429005760815171E-3</v>
+        <f t="shared" si="10"/>
+        <v>2.0590891816331211E-2</v>
       </c>
       <c r="H63" s="15"/>
       <c r="I63" s="15"/>
@@ -2883,118 +2923,182 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="15"/>
-      <c r="B64" s="16"/>
+      <c r="B64" s="16" t="str">
+        <f>B48</f>
+        <v>-beam</v>
+      </c>
       <c r="C64" s="15">
-        <f>C63</f>
-        <v>24</v>
+        <f>C50*(3*2)</f>
+        <v>12</v>
       </c>
       <c r="D64" s="3">
-        <f>(4*4+2*2)/12/3.281</f>
-        <v>0.50797521080971253</v>
+        <f>D33+0.23*2+(0.583/3.281)*2</f>
+        <v>3.7870344407192924</v>
       </c>
       <c r="E64" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F64" s="3">
-        <f t="shared" ref="F64" si="19">PRODUCT(C64:E64)</f>
-        <v>4.8163575543439414</v>
+        <f t="shared" ref="F64:F67" si="11">PRODUCT(C64:E64)</f>
+        <v>40.395034034339119</v>
       </c>
       <c r="G64" s="3">
-        <f t="shared" ref="G64" si="20">F64/1000</f>
-        <v>4.8163575543439417E-3</v>
+        <f t="shared" ref="G64:G67" si="12">F64/1000</f>
+        <v>4.0395034034339118E-2</v>
       </c>
       <c r="H64" s="15"/>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
       <c r="K64" s="15"/>
     </row>
-    <row r="65" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
-      <c r="B65" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="2">
-        <f>SUM(G51:G64)</f>
-        <v>0.36656939009109685</v>
-      </c>
-      <c r="H65" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="I65" s="46">
-        <v>132360</v>
-      </c>
-      <c r="J65" s="22">
-        <f>G65*I65</f>
-        <v>48519.124472457581</v>
-      </c>
-      <c r="K65" s="20"/>
-    </row>
-    <row r="66" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="24"/>
-      <c r="B66" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="26"/>
-      <c r="G66" s="26"/>
-      <c r="H66" s="26"/>
-      <c r="I66" s="26"/>
-      <c r="J66" s="22">
-        <f>0.13*G65*105000</f>
-        <v>5003.6721747434722</v>
-      </c>
-      <c r="K66" s="26"/>
-    </row>
-    <row r="67" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="24"/>
-      <c r="B67" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
-      <c r="H67" s="26"/>
-      <c r="I67" s="26"/>
-      <c r="J67" s="22">
-        <f>0.13*G65*1200</f>
-        <v>57.184824854211108</v>
-      </c>
-      <c r="K67" s="26"/>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="15"/>
+      <c r="B65" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" s="15">
+        <f>4*(TRUNC((D49-0.1)/0.125,0))</f>
+        <v>88</v>
+      </c>
+      <c r="D65" s="3">
+        <f>((0.583*4)+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
+      </c>
+      <c r="E65" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F65" s="3">
+        <f t="shared" si="11"/>
+        <v>28.312476247455418</v>
+      </c>
+      <c r="G65" s="3">
+        <f t="shared" si="12"/>
+        <v>2.8312476247455417E-2</v>
+      </c>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="15"/>
+      <c r="B66" s="16" t="str">
+        <f>B50</f>
+        <v>-upper beam</v>
+      </c>
+      <c r="C66" s="15">
+        <f>C50*(3*2)</f>
+        <v>12</v>
+      </c>
+      <c r="D66" s="3">
+        <f>D34+(0.583/3.281)*2</f>
+        <v>2.8454739408716851</v>
+      </c>
+      <c r="E66" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F66" s="3">
+        <f t="shared" si="11"/>
+        <v>30.351722035964642</v>
+      </c>
+      <c r="G66" s="3">
+        <f t="shared" si="12"/>
+        <v>3.0351722035964642E-2</v>
+      </c>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="15"/>
+      <c r="B67" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="15">
+        <f>2*(TRUNC((D50-0.1-0.23*2)/0.125,0))</f>
+        <v>30</v>
+      </c>
+      <c r="D67" s="3">
+        <f>((0.583*4)+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
+      </c>
+      <c r="E67" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F67" s="3">
+        <f t="shared" si="11"/>
+        <v>9.6519805389052564</v>
+      </c>
+      <c r="G67" s="3">
+        <f t="shared" si="12"/>
+        <v>9.6519805389052565E-3</v>
+      </c>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="15"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
+      <c r="B68" s="16" t="str">
+        <f>B34</f>
+        <v>-upper beam</v>
+      </c>
+      <c r="C68" s="15">
+        <f>C51*(3*2)</f>
+        <v>12</v>
+      </c>
+      <c r="D68" s="3">
+        <f>D35+0.23*2+(0.583/3.281)*2</f>
+        <v>1.9583236818043277</v>
+      </c>
+      <c r="E68" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F68" s="3">
+        <f t="shared" ref="F68:F69" si="13">PRODUCT(C68:E68)</f>
+        <v>20.888785939246162</v>
+      </c>
+      <c r="G68" s="3">
+        <f t="shared" ref="G68:G69" si="14">F68/1000</f>
+        <v>2.0888785939246163E-2</v>
+      </c>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
     </row>
-    <row r="69" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="11">
-        <v>7</v>
-      </c>
-      <c r="B69" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="15"/>
+      <c r="B69" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="15">
+        <f>2*(TRUNC((D51-0.1)/0.125,0))</f>
+        <v>16</v>
+      </c>
+      <c r="D69" s="3">
+        <f>((0.583*4)+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
+      </c>
+      <c r="E69" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F69" s="3">
+        <f t="shared" si="13"/>
+        <v>5.1477229540828029</v>
+      </c>
+      <c r="G69" s="3">
+        <f t="shared" si="14"/>
+        <v>5.1477229540828028E-3</v>
+      </c>
       <c r="H69" s="15"/>
       <c r="I69" s="15"/>
       <c r="J69" s="15"/>
@@ -3002,780 +3106,890 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="15"/>
-      <c r="B70" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="B70" s="16" t="str">
+        <f>B52</f>
+        <v>-slab</v>
       </c>
       <c r="C70" s="15">
-        <v>1</v>
+        <f>TRUNC(((E52-0.1)/0.15),0)</f>
+        <v>12</v>
       </c>
       <c r="D70" s="3">
-        <f>12.667/3.281</f>
-        <v>3.8607131971959765</v>
+        <f>D52*C52+D53*C53</f>
+        <v>13.970435842730875</v>
       </c>
       <c r="E70" s="3">
-        <f>9.75/3.281</f>
-        <v>2.9716549832368178</v>
-      </c>
-      <c r="F70" s="15"/>
+        <f t="shared" ref="E70:E72" si="15">8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F70" s="3">
+        <f t="shared" ref="F70:F72" si="16">PRODUCT(C70:E70)</f>
+        <v>66.230214365538956</v>
+      </c>
       <c r="G70" s="3">
-        <f>PRODUCT(C70:F70)</f>
-        <v>11.47270761129557</v>
+        <f t="shared" ref="G70:G72" si="17">F70/1000</f>
+        <v>6.6230214365538956E-2</v>
       </c>
       <c r="H70" s="15"/>
       <c r="I70" s="15"/>
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
     </row>
-    <row r="71" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
-      <c r="B71" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="19"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="2">
-        <f>SUM(G70)</f>
-        <v>11.47270761129557</v>
-      </c>
-      <c r="H71" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I71" s="2">
-        <v>689.98</v>
-      </c>
-      <c r="J71" s="22">
-        <f>G71*I71</f>
-        <v>7915.9387976417174</v>
-      </c>
-      <c r="K71" s="20"/>
-    </row>
-    <row r="72" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="24"/>
-      <c r="B72" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C72" s="26"/>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="22">
-        <f>0.13*G71*1694.03/10</f>
-        <v>252.65644137191944</v>
-      </c>
-      <c r="K72" s="26"/>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="15"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="15">
+        <f>2*(TRUNC(((D52-0.1)/0.15),0))</f>
+        <v>50</v>
+      </c>
+      <c r="D71" s="3">
+        <f>E52</f>
+        <v>1.929289850655288</v>
+      </c>
+      <c r="E71" s="3">
+        <f t="shared" si="15"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F71" s="3">
+        <f t="shared" si="16"/>
+        <v>38.109429148746429</v>
+      </c>
+      <c r="G71" s="3">
+        <f t="shared" si="17"/>
+        <v>3.8109429148746432E-2</v>
+      </c>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="15"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="15">
+        <f>2*(TRUNC(((D53-0.1)/0.15),0))</f>
+        <v>38</v>
+      </c>
+      <c r="D72" s="3">
+        <f>E53</f>
+        <v>1.929289850655288</v>
+      </c>
+      <c r="E72" s="3">
+        <f t="shared" si="15"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F72" s="3">
+        <f t="shared" si="16"/>
+        <v>28.963166153047286</v>
+      </c>
+      <c r="G72" s="3">
+        <f t="shared" si="17"/>
+        <v>2.8963166153047285E-2</v>
+      </c>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="15"/>
-      <c r="B73" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="26"/>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="27"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="22">
-        <f>0.13*G71*472.02/10</f>
-        <v>70.399516806888556</v>
-      </c>
+      <c r="B73" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C73" s="15">
+        <v>8</v>
+      </c>
+      <c r="D73" s="3">
+        <f>((3.75-0.33)/3.281)+(0.45*2)</f>
+        <v>1.9423651325815299</v>
+      </c>
+      <c r="E73" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F73" s="3">
+        <f t="shared" ref="F73:F74" si="18">PRODUCT(C73:E73)</f>
+        <v>13.812374276135323</v>
+      </c>
+      <c r="G73" s="3">
+        <f t="shared" ref="G73:G74" si="19">F73/1000</f>
+        <v>1.3812374276135323E-2</v>
+      </c>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
       <c r="K73" s="15"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="15"/>
-      <c r="B74" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C74" s="26"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="22">
-        <f>0.13*G71*1207.6/10</f>
-        <v>180.10774224820688</v>
-      </c>
+      <c r="B74" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C74" s="15">
+        <f>4*(TRUNC((2.25-0.17*2)/0.33,0)+1)</f>
+        <v>24</v>
+      </c>
+      <c r="D74" s="3">
+        <f>(6*4+2*2)/12/3.281</f>
+        <v>0.7111652951335975</v>
+      </c>
+      <c r="E74" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F74" s="3">
+        <f t="shared" si="18"/>
+        <v>6.7429005760815173</v>
+      </c>
+      <c r="G74" s="3">
+        <f t="shared" si="19"/>
+        <v>6.7429005760815171E-3</v>
+      </c>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
       <c r="K74" s="15"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="15"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="15">
+        <f>C74</f>
+        <v>24</v>
+      </c>
+      <c r="D75" s="3">
+        <f>(4*4+2*2)/12/3.281</f>
+        <v>0.50797521080971253</v>
+      </c>
+      <c r="E75" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F75" s="3">
+        <f t="shared" ref="F75" si="20">PRODUCT(C75:E75)</f>
+        <v>4.8163575543439414</v>
+      </c>
+      <c r="G75" s="83">
+        <f t="shared" ref="G75" si="21">F75/1000</f>
+        <v>4.8163575543439417E-3</v>
+      </c>
       <c r="H75" s="15"/>
       <c r="I75" s="15"/>
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
     </row>
-    <row r="76" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="11">
-        <v>8</v>
-      </c>
-      <c r="B76" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="15"/>
-      <c r="K76" s="15"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16" t="e">
-        <f>B70</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C77" s="15">
-        <f>C70</f>
-        <v>1</v>
-      </c>
-      <c r="D77" s="3">
-        <f>D70</f>
-        <v>3.8607131971959765</v>
-      </c>
-      <c r="E77" s="3">
-        <f>E70</f>
-        <v>2.9716549832368178</v>
-      </c>
-      <c r="F77" s="15"/>
-      <c r="G77" s="3">
-        <f>PRODUCT(C77:F77)</f>
-        <v>11.47270761129557</v>
-      </c>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-    </row>
-    <row r="78" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
-      <c r="B78" s="18" t="s">
+    <row r="76" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="17"/>
+      <c r="B76" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C78" s="19"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="2">
-        <f>SUM(G77:G77)</f>
-        <v>11.47270761129557</v>
-      </c>
-      <c r="H78" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I78" s="2">
-        <v>415.5</v>
-      </c>
+      <c r="C76" s="19"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="2">
+        <f>SUM(G62:G75)</f>
+        <v>0.36656939009109685</v>
+      </c>
+      <c r="H76" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" s="46">
+        <v>132360</v>
+      </c>
+      <c r="J76" s="22">
+        <f>G76*I76</f>
+        <v>48519.124472457581</v>
+      </c>
+      <c r="K76" s="20"/>
+    </row>
+    <row r="77" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="24"/>
+      <c r="B77" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="22">
+        <f>0.13*G76*105000</f>
+        <v>5003.6721747434722</v>
+      </c>
+      <c r="K77" s="26"/>
+    </row>
+    <row r="78" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="24"/>
+      <c r="B78" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
       <c r="J78" s="22">
-        <f>G78*I78</f>
-        <v>4766.9100124933093</v>
-      </c>
-      <c r="K78" s="20"/>
-    </row>
-    <row r="79" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="24"/>
-      <c r="B79" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C79" s="26"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="26"/>
-      <c r="I79" s="26"/>
-      <c r="J79" s="22">
-        <f>0.13*G78*7010.67/100</f>
-        <v>104.56077719006596</v>
-      </c>
-      <c r="K79" s="26"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="15"/>
-      <c r="B80" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="26"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="22">
-        <f>0.13*G78*4639.73/100</f>
-        <v>69.199345390963302</v>
-      </c>
+        <f>0.13*G76*1200</f>
+        <v>57.184824854211108</v>
+      </c>
+      <c r="K78" s="26"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="15"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="15"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
+      <c r="J79" s="15"/>
+      <c r="K79" s="15"/>
+    </row>
+    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A80" s="11">
+        <v>7</v>
+      </c>
+      <c r="B80" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="15"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
+      <c r="J80" s="15"/>
       <c r="K80" s="15"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="15"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
+      <c r="B81" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C81" s="15">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3">
+        <f>12.667/3.281</f>
+        <v>3.8607131971959765</v>
+      </c>
+      <c r="E81" s="3">
+        <f>9.75/3.281</f>
+        <v>2.9716549832368178</v>
+      </c>
       <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
+      <c r="G81" s="3">
+        <f>PRODUCT(C81:F81)</f>
+        <v>11.47270761129557</v>
+      </c>
       <c r="H81" s="15"/>
       <c r="I81" s="15"/>
       <c r="J81" s="15"/>
       <c r="K81" s="15"/>
     </row>
-    <row r="82" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="11">
-        <v>9</v>
-      </c>
-      <c r="B82" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="15"/>
-      <c r="K82" s="15"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
-      <c r="B83" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C83" s="3">
-        <v>2</v>
-      </c>
-      <c r="D83" s="3">
-        <f>9.75/3.281</f>
-        <v>2.9716549832368178</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F83" s="3">
-        <f>(10-3.5-0.33)/3.281</f>
-        <v>1.8805242304175556</v>
-      </c>
-      <c r="G83" s="3">
-        <f t="shared" ref="G83:G86" si="21">PRODUCT(C83:F83)</f>
-        <v>3.9117884402925371</v>
-      </c>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="15"/>
-      <c r="K83" s="15"/>
+    <row r="82" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="17"/>
+      <c r="B82" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="19"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="2">
+        <f>SUM(G81)</f>
+        <v>11.47270761129557</v>
+      </c>
+      <c r="H82" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I82" s="2">
+        <v>689.98</v>
+      </c>
+      <c r="J82" s="22">
+        <f>G82*I82</f>
+        <v>7915.9387976417174</v>
+      </c>
+      <c r="K82" s="20"/>
+    </row>
+    <row r="83" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="24"/>
+      <c r="B83" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" s="26"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
+      <c r="J83" s="22">
+        <f>0.13*G82*1694.03/10</f>
+        <v>252.65644137191944</v>
+      </c>
+      <c r="K83" s="26"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
-      <c r="B84" s="16"/>
-      <c r="C84" s="3">
-        <v>2</v>
-      </c>
-      <c r="D84" s="3">
-        <f>15/3.281</f>
-        <v>4.5717768972874122</v>
-      </c>
-      <c r="E84" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F84" s="3">
-        <f>(10-3.5-0.33)/3.281</f>
-        <v>1.8805242304175556</v>
-      </c>
-      <c r="G84" s="3">
-        <f t="shared" si="21"/>
-        <v>6.0181360619885194</v>
-      </c>
-      <c r="H84" s="15"/>
-      <c r="I84" s="15"/>
-      <c r="J84" s="15"/>
+      <c r="B84" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="26"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="22">
+        <f>0.13*G82*472.02/10</f>
+        <v>70.399516806888556</v>
+      </c>
       <c r="K84" s="15"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="15"/>
-      <c r="B85" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C85" s="3">
-        <v>-1</v>
-      </c>
-      <c r="D85" s="3">
-        <f>1.5</f>
-        <v>1.5</v>
-      </c>
-      <c r="E85" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F85" s="3">
-        <f>(7-3.5)/3.281</f>
-        <v>1.0667479427003961</v>
-      </c>
-      <c r="G85" s="3">
-        <f t="shared" ref="G85" si="22">PRODUCT(C85:F85)</f>
-        <v>-0.56004266991770779</v>
-      </c>
-      <c r="H85" s="15"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="15"/>
+      <c r="B85" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" s="26"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="22">
+        <f>0.13*G82*1207.6/10</f>
+        <v>180.10774224820688</v>
+      </c>
       <c r="K85" s="15"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
-      <c r="B86" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C86" s="3">
-        <v>-2</v>
-      </c>
-      <c r="D86" s="3">
-        <f>3.5/3.281</f>
-        <v>1.0667479427003961</v>
-      </c>
-      <c r="E86" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F86" s="3">
-        <f>(7-3.5)/3.281</f>
-        <v>1.0667479427003961</v>
-      </c>
-      <c r="G86" s="3">
-        <f t="shared" si="21"/>
-        <v>-0.79656582127886921</v>
-      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="15"/>
+      <c r="G86" s="15"/>
       <c r="H86" s="15"/>
       <c r="I86" s="15"/>
       <c r="J86" s="15"/>
       <c r="K86" s="15"/>
     </row>
-    <row r="87" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="17"/>
-      <c r="B87" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" s="19"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="2">
-        <f>SUM(G83:G86)</f>
-        <v>8.5733160110844793</v>
-      </c>
-      <c r="H87" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I87" s="2">
-        <f>14491.84</f>
-        <v>14491.84</v>
-      </c>
-      <c r="J87" s="22">
-        <f>G87*I87</f>
-        <v>124243.1239020745</v>
-      </c>
-      <c r="K87" s="20"/>
-    </row>
-    <row r="88" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="24"/>
-      <c r="B88" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C88" s="26"/>
-      <c r="D88" s="27"/>
-      <c r="E88" s="27"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="27"/>
-      <c r="H88" s="26"/>
-      <c r="I88" s="26"/>
-      <c r="J88" s="22">
-        <f>0.13*G87*8481.2</f>
-        <v>9452.5610079172602</v>
-      </c>
-      <c r="K88" s="26"/>
+    <row r="87" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="11">
+        <v>8</v>
+      </c>
+      <c r="B87" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="15"/>
+      <c r="G87" s="15"/>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="15"/>
+      <c r="B88" s="16" t="str">
+        <f>B81</f>
+        <v>-flooring</v>
+      </c>
+      <c r="C88" s="15">
+        <f>C81</f>
+        <v>1</v>
+      </c>
+      <c r="D88" s="3">
+        <f>D81</f>
+        <v>3.8607131971959765</v>
+      </c>
+      <c r="E88" s="3">
+        <f>E81</f>
+        <v>2.9716549832368178</v>
+      </c>
+      <c r="F88" s="15"/>
+      <c r="G88" s="3">
+        <f>PRODUCT(C88:F88)</f>
+        <v>11.47270761129557</v>
+      </c>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
     </row>
     <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="24"/>
-      <c r="B89" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C89" s="26"/>
-      <c r="D89" s="27"/>
+      <c r="B89" s="25" t="str">
+        <f>B117</f>
+        <v>-for wing walls of stand tap</v>
+      </c>
+      <c r="C89" s="26">
+        <f>C117</f>
+        <v>4</v>
+      </c>
+      <c r="D89" s="27">
+        <f>D117</f>
+        <v>1.2163181956720512</v>
+      </c>
       <c r="E89" s="27"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="27"/>
+      <c r="F89" s="27">
+        <f>F117</f>
+        <v>0.6</v>
+      </c>
+      <c r="G89" s="27">
+        <f>PRODUCT(C89:F89)</f>
+        <v>2.9191636696129231</v>
+      </c>
       <c r="H89" s="26"/>
       <c r="I89" s="26"/>
-      <c r="J89" s="22">
-        <f>0.13*G87*912.17</f>
-        <v>1016.6418165580208</v>
-      </c>
+      <c r="J89" s="26"/>
       <c r="K89" s="26"/>
     </row>
     <row r="90" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="24"/>
-      <c r="B90" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C90" s="26"/>
-      <c r="D90" s="27"/>
+      <c r="B90" s="25" t="str">
+        <f>B118</f>
+        <v>-for side wall of stand tap</v>
+      </c>
+      <c r="C90" s="26">
+        <f>C118</f>
+        <v>1</v>
+      </c>
+      <c r="D90" s="27">
+        <f>D118</f>
+        <v>1.3197195976836331</v>
+      </c>
       <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="27"/>
+      <c r="F90" s="27">
+        <f>F118</f>
+        <v>0.6</v>
+      </c>
+      <c r="G90" s="27">
+        <f>PRODUCT(C90:F90)</f>
+        <v>0.79183175861017985</v>
+      </c>
       <c r="H90" s="26"/>
       <c r="I90" s="26"/>
-      <c r="J90" s="22">
-        <f>0.13*G87*953.37</f>
-        <v>1062.5604971133894</v>
-      </c>
+      <c r="J90" s="26"/>
       <c r="K90" s="26"/>
     </row>
     <row r="91" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="24"/>
-      <c r="B91" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C91" s="26"/>
-      <c r="D91" s="27"/>
+      <c r="B91" s="25" t="str">
+        <f>B119</f>
+        <v>-stand</v>
+      </c>
+      <c r="C91" s="26">
+        <f>C119</f>
+        <v>1</v>
+      </c>
+      <c r="D91" s="27">
+        <f>D119</f>
+        <v>0.35659859798841814</v>
+      </c>
       <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
+      <c r="F91" s="27">
+        <f>F119</f>
+        <v>1.2</v>
+      </c>
+      <c r="G91" s="27">
+        <f>PRODUCT(C91:F91)</f>
+        <v>0.42791831758610177</v>
+      </c>
       <c r="H91" s="26"/>
       <c r="I91" s="26"/>
-      <c r="J91" s="22">
-        <f>0.13*G87*28</f>
-        <v>31.206870280347506</v>
-      </c>
+      <c r="J91" s="26"/>
       <c r="K91" s="26"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
-    </row>
-    <row r="93" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A93" s="11">
-        <v>10</v>
-      </c>
-      <c r="B93" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="15"/>
-      <c r="B94" s="16" t="str">
-        <f>B83</f>
-        <v>-for wall continue</v>
-      </c>
-      <c r="C94" s="45">
+    <row r="92" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="24"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="26">
+        <f>C120</f>
         <v>1</v>
       </c>
-      <c r="D94" s="3">
-        <f>(15*2+(9.75+1.17*2)*2)/3.281</f>
-        <v>16.513258153002134</v>
-      </c>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="G94" s="3">
-        <f>PRODUCT(C94:F94)</f>
-        <v>50.329954748558777</v>
-      </c>
-      <c r="H94" s="15"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="15"/>
-      <c r="K94" s="15"/>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
-      <c r="B95" s="16"/>
-      <c r="C95" s="45">
+      <c r="D92" s="27">
+        <f>D120</f>
+        <v>0.46</v>
+      </c>
+      <c r="E92" s="27"/>
+      <c r="F92" s="27">
+        <f>F120</f>
+        <v>0.6</v>
+      </c>
+      <c r="G92" s="27">
+        <f>PRODUCT(C92:F92)</f>
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="H92" s="26"/>
+      <c r="I92" s="26"/>
+      <c r="J92" s="26"/>
+      <c r="K92" s="26"/>
+    </row>
+    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="24"/>
+      <c r="B93" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93" s="26">
+        <f>C14</f>
         <v>1</v>
       </c>
-      <c r="D95" s="3">
-        <f>((15-1.17*2)*2+(9.75*2))/3.281</f>
-        <v>13.660469369094788</v>
-      </c>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="G95" s="3">
-        <f>PRODUCT(C95:F95)</f>
-        <v>41.635078845153267</v>
-      </c>
-      <c r="H95" s="15"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="15"/>
-      <c r="K95" s="15"/>
+      <c r="D93" s="27">
+        <f>M10</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="E93" s="27">
+        <f>N10</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="F93" s="27"/>
+      <c r="G93" s="27">
+        <f>PRODUCT(C93:F93)</f>
+        <v>2.8100426931412015</v>
+      </c>
+      <c r="H93" s="26"/>
+      <c r="I93" s="26"/>
+      <c r="J93" s="26"/>
+      <c r="K93" s="26"/>
+    </row>
+    <row r="94" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="17"/>
+      <c r="B94" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="19"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="20"/>
+      <c r="F94" s="20"/>
+      <c r="G94" s="2">
+        <f>SUM(G88:G93)</f>
+        <v>18.697664050245976</v>
+      </c>
+      <c r="H94" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I94" s="2">
+        <v>415.5</v>
+      </c>
+      <c r="J94" s="22">
+        <f>G94*I94</f>
+        <v>7768.8794128772033</v>
+      </c>
+      <c r="K94" s="20"/>
+    </row>
+    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="24"/>
+      <c r="B95" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" s="26"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+      <c r="H95" s="26"/>
+      <c r="I95" s="26"/>
+      <c r="J95" s="22">
+        <f>0.13*G94*7010.67/100</f>
+        <v>170.40809815527933</v>
+      </c>
+      <c r="K95" s="26"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="15"/>
-      <c r="B96" s="16" t="str">
-        <f>B85</f>
-        <v>-deduction for door</v>
-      </c>
-      <c r="C96" s="45">
-        <f>2*C85</f>
-        <v>-2</v>
-      </c>
-      <c r="D96" s="3">
-        <f>D85</f>
-        <v>1.5</v>
-      </c>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3">
-        <f>7/3.281</f>
-        <v>2.1334958854007922</v>
-      </c>
-      <c r="G96" s="3">
-        <f t="shared" ref="G96" si="23">PRODUCT(C96:F96)</f>
-        <v>-6.400487656202376</v>
-      </c>
-      <c r="H96" s="15"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="15"/>
+      <c r="B96" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="26"/>
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="27"/>
+      <c r="G96" s="27"/>
+      <c r="H96" s="26"/>
+      <c r="I96" s="26"/>
+      <c r="J96" s="22">
+        <f>0.13*G94*4639.73/100</f>
+        <v>112.77774667100208</v>
+      </c>
       <c r="K96" s="15"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="15"/>
-      <c r="B97" s="16" t="str">
-        <f>B86</f>
-        <v>-deduction for window</v>
-      </c>
-      <c r="C97" s="45">
-        <f>2*C86</f>
-        <v>-4</v>
-      </c>
-      <c r="D97" s="3">
-        <f>D86</f>
-        <v>1.0667479427003961</v>
-      </c>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3">
-        <f>F86</f>
-        <v>1.0667479427003961</v>
-      </c>
-      <c r="G97" s="3">
-        <f t="shared" ref="G97" si="24">PRODUCT(C97:F97)</f>
-        <v>-4.5518046930221097</v>
-      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="15"/>
       <c r="H97" s="15"/>
       <c r="I97" s="15"/>
       <c r="J97" s="15"/>
       <c r="K97" s="15"/>
     </row>
-    <row r="98" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="17"/>
-      <c r="B98" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" s="19"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="20"/>
-      <c r="F98" s="20"/>
-      <c r="G98" s="2">
-        <f>SUM(G94:G97)</f>
-        <v>81.012741244487557</v>
-      </c>
-      <c r="H98" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I98" s="2">
-        <v>415.5</v>
-      </c>
-      <c r="J98" s="22">
-        <f>G98*I98</f>
-        <v>33660.79398708458</v>
-      </c>
-      <c r="K98" s="20"/>
-    </row>
-    <row r="99" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="24"/>
-      <c r="B99" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C99" s="26"/>
-      <c r="D99" s="27"/>
-      <c r="E99" s="27"/>
-      <c r="F99" s="27"/>
-      <c r="G99" s="27"/>
-      <c r="H99" s="26"/>
-      <c r="I99" s="26"/>
-      <c r="J99" s="22">
-        <f>0.13*G98*7010.67/100</f>
-        <v>738.33967305863916</v>
-      </c>
-      <c r="K99" s="26"/>
+    <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A98" s="11">
+        <v>9</v>
+      </c>
+      <c r="B98" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="15"/>
+      <c r="G98" s="15"/>
+      <c r="H98" s="15"/>
+      <c r="I98" s="15"/>
+      <c r="J98" s="15"/>
+      <c r="K98" s="15"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="15"/>
+      <c r="B99" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="45">
+        <v>2</v>
+      </c>
+      <c r="D99" s="3">
+        <f>9.75/3.281</f>
+        <v>2.9716549832368178</v>
+      </c>
+      <c r="E99" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F99" s="3">
+        <f>(10-3.5-0.33)/3.281</f>
+        <v>1.8805242304175556</v>
+      </c>
+      <c r="G99" s="3">
+        <f t="shared" ref="G99:G102" si="22">PRODUCT(C99:F99)</f>
+        <v>3.9117884402925371</v>
+      </c>
+      <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
+      <c r="J99" s="15"/>
+      <c r="K99" s="15"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="15"/>
-      <c r="B100" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C100" s="26"/>
-      <c r="D100" s="27"/>
-      <c r="E100" s="27"/>
-      <c r="F100" s="27"/>
-      <c r="G100" s="27"/>
-      <c r="H100" s="26"/>
-      <c r="I100" s="26"/>
-      <c r="J100" s="22">
-        <f>0.13*G98*4639.73/100</f>
-        <v>488.64041971457215</v>
-      </c>
+      <c r="B100" s="16"/>
+      <c r="C100" s="45">
+        <v>2</v>
+      </c>
+      <c r="D100" s="3">
+        <f>15/3.281</f>
+        <v>4.5717768972874122</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F100" s="3">
+        <f>(10-3.5-0.33)/3.281</f>
+        <v>1.8805242304175556</v>
+      </c>
+      <c r="G100" s="3">
+        <f t="shared" si="22"/>
+        <v>6.0181360619885194</v>
+      </c>
+      <c r="H100" s="15"/>
+      <c r="I100" s="15"/>
+      <c r="J100" s="15"/>
       <c r="K100" s="15"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="15"/>
-      <c r="B101" s="15"/>
-      <c r="C101" s="15"/>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
+      <c r="B101" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C101" s="45">
+        <v>-1</v>
+      </c>
+      <c r="D101" s="3">
+        <f>1.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F101" s="3">
+        <f>(7-3.5)/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G101" s="3">
+        <f t="shared" ref="G101" si="23">PRODUCT(C101:F101)</f>
+        <v>-0.56004266991770779</v>
+      </c>
       <c r="H101" s="15"/>
       <c r="I101" s="15"/>
       <c r="J101" s="15"/>
       <c r="K101" s="15"/>
     </row>
-    <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="11">
-        <v>11</v>
-      </c>
-      <c r="B102" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C102" s="15"/>
-      <c r="D102" s="15"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15"/>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="15"/>
+      <c r="B102" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C102" s="45">
+        <v>-2</v>
+      </c>
+      <c r="D102" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F102" s="3">
+        <f>(7-3.5)/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G102" s="3">
+        <f t="shared" si="22"/>
+        <v>-0.79656582127886921</v>
+      </c>
       <c r="H102" s="15"/>
       <c r="I102" s="15"/>
       <c r="J102" s="15"/>
       <c r="K102" s="15"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
-      <c r="B103" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C103" s="3">
-        <f>C94</f>
+    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="24"/>
+      <c r="B103" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C103" s="51">
+        <f>C14*2</f>
+        <v>2</v>
+      </c>
+      <c r="D103" s="27">
+        <f>N10-O10*2</f>
+        <v>1.2163181956720512</v>
+      </c>
+      <c r="E103" s="27">
+        <f>O10</f>
+        <v>0.23</v>
+      </c>
+      <c r="F103" s="27">
+        <f>P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G103" s="27">
+        <f>PRODUCT(C103:F103)</f>
+        <v>0.33570382200548615</v>
+      </c>
+      <c r="H103" s="26"/>
+      <c r="I103" s="26"/>
+      <c r="J103" s="26"/>
+      <c r="K103" s="26"/>
+    </row>
+    <row r="104" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="24"/>
+      <c r="B104" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C104" s="51">
+        <f>C14</f>
         <v>1</v>
       </c>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3">
-        <f>SUM(G94:G97)</f>
-        <v>81.012741244487557</v>
-      </c>
-      <c r="H103" s="15"/>
-      <c r="I103" s="15"/>
-      <c r="J103" s="15"/>
-      <c r="K103" s="15"/>
-    </row>
-    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="17"/>
-      <c r="B104" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" s="19"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="20"/>
-      <c r="G104" s="2">
-        <f>SUM(G103:G103)</f>
-        <v>81.012741244487557</v>
-      </c>
-      <c r="H104" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I104" s="2">
-        <v>253.8</v>
-      </c>
-      <c r="J104" s="22">
-        <f>G104*I104</f>
-        <v>20561.033727850943</v>
-      </c>
-      <c r="K104" s="20"/>
+      <c r="D104" s="27">
+        <f>M10-R10</f>
+        <v>1.3197195976836331</v>
+      </c>
+      <c r="E104" s="27">
+        <f>O10</f>
+        <v>0.23</v>
+      </c>
+      <c r="F104" s="27">
+        <f>P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G104" s="27">
+        <f>PRODUCT(C104:F104)</f>
+        <v>0.18212130448034136</v>
+      </c>
+      <c r="H104" s="26"/>
+      <c r="I104" s="26"/>
+      <c r="J104" s="26"/>
+      <c r="K104" s="26"/>
     </row>
     <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="24"/>
       <c r="B105" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C105" s="26"/>
-      <c r="D105" s="27"/>
-      <c r="E105" s="27"/>
-      <c r="F105" s="27"/>
-      <c r="G105" s="27"/>
+        <v>139</v>
+      </c>
+      <c r="C105" s="51">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D105" s="27">
+        <f>R10</f>
+        <v>0.35659859798841814</v>
+      </c>
+      <c r="E105" s="27">
+        <f>O10</f>
+        <v>0.23</v>
+      </c>
+      <c r="F105" s="27">
+        <f>Q10</f>
+        <v>1.2</v>
+      </c>
+      <c r="G105" s="27">
+        <f>PRODUCT(C105:F105)</f>
+        <v>9.8421213044803404E-2</v>
+      </c>
       <c r="H105" s="26"/>
       <c r="I105" s="26"/>
-      <c r="J105" s="22">
-        <f>0.13*G104*2304/100</f>
-        <v>242.64936257548914</v>
-      </c>
+      <c r="J105" s="26"/>
       <c r="K105" s="26"/>
     </row>
-    <row r="106" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="24"/>
-      <c r="B106" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C106" s="26"/>
-      <c r="D106" s="27"/>
-      <c r="E106" s="27"/>
-      <c r="F106" s="27"/>
-      <c r="G106" s="27"/>
-      <c r="H106" s="26"/>
-      <c r="I106" s="26"/>
+    <row r="106" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="17"/>
+      <c r="B106" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" s="19"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="2">
+        <f>SUM(G99:G105)</f>
+        <v>9.1895623506151107</v>
+      </c>
+      <c r="H106" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I106" s="2">
+        <f>14491.84</f>
+        <v>14491.84</v>
+      </c>
       <c r="J106" s="22">
-        <f>0.13*G104*10432/100</f>
-        <v>1098.6623916612425</v>
-      </c>
-      <c r="K106" s="26"/>
+        <f>G106*I106</f>
+        <v>133173.66725513808</v>
+      </c>
+      <c r="K106" s="20"/>
     </row>
     <row r="107" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="24"/>
-      <c r="B107" s="25"/>
+      <c r="B107" s="25" t="s">
+        <v>55</v>
+      </c>
       <c r="C107" s="26"/>
       <c r="D107" s="27"/>
       <c r="E107" s="27"/>
@@ -3783,12 +3997,17 @@
       <c r="G107" s="27"/>
       <c r="H107" s="26"/>
       <c r="I107" s="26"/>
-      <c r="J107" s="22"/>
+      <c r="J107" s="22">
+        <f>0.13*G106*8481.2</f>
+        <v>10132.007107044796</v>
+      </c>
       <c r="K107" s="26"/>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="24"/>
-      <c r="B108" s="25"/>
+      <c r="B108" s="25" t="s">
+        <v>32</v>
+      </c>
       <c r="C108" s="26"/>
       <c r="D108" s="27"/>
       <c r="E108" s="27"/>
@@ -3796,12 +4015,17 @@
       <c r="G108" s="27"/>
       <c r="H108" s="26"/>
       <c r="I108" s="26"/>
-      <c r="J108" s="22"/>
+      <c r="J108" s="22">
+        <f>0.13*G106*912.17</f>
+        <v>1089.7176016168762</v>
+      </c>
       <c r="K108" s="26"/>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="24"/>
-      <c r="B109" s="25"/>
+      <c r="B109" s="25" t="s">
+        <v>64</v>
+      </c>
       <c r="C109" s="26"/>
       <c r="D109" s="27"/>
       <c r="E109" s="27"/>
@@ -3809,12 +4033,17 @@
       <c r="G109" s="27"/>
       <c r="H109" s="26"/>
       <c r="I109" s="26"/>
-      <c r="J109" s="22"/>
+      <c r="J109" s="22">
+        <f>0.13*G106*953.37</f>
+        <v>1138.9368975667708</v>
+      </c>
       <c r="K109" s="26"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="24"/>
-      <c r="B110" s="25"/>
+      <c r="B110" s="25" t="s">
+        <v>36</v>
+      </c>
       <c r="C110" s="26"/>
       <c r="D110" s="27"/>
       <c r="E110" s="27"/>
@@ -3822,224 +4051,861 @@
       <c r="G110" s="27"/>
       <c r="H110" s="26"/>
       <c r="I110" s="26"/>
-      <c r="J110" s="22"/>
+      <c r="J110" s="22">
+        <f>0.13*G106*28</f>
+        <v>33.450006956239008</v>
+      </c>
       <c r="K110" s="26"/>
     </row>
-    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="24"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="27"/>
-      <c r="E111" s="27"/>
-      <c r="F111" s="27"/>
-      <c r="G111" s="27"/>
-      <c r="H111" s="26"/>
-      <c r="I111" s="26"/>
-      <c r="J111" s="22"/>
-      <c r="K111" s="26"/>
-    </row>
-    <row r="112" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="24"/>
-      <c r="B112" s="25"/>
-      <c r="C112" s="26"/>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="26"/>
-      <c r="I112" s="26"/>
-      <c r="J112" s="22"/>
-      <c r="K112" s="26"/>
-    </row>
-    <row r="113" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A113" s="17">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="15"/>
+      <c r="B111" s="15"/>
+      <c r="C111" s="15"/>
+      <c r="D111" s="15"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="15"/>
+      <c r="G111" s="15"/>
+      <c r="H111" s="15"/>
+      <c r="I111" s="15"/>
+      <c r="J111" s="15"/>
+      <c r="K111" s="15"/>
+    </row>
+    <row r="112" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A112" s="11">
+        <v>10</v>
+      </c>
+      <c r="B112" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C112" s="15"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="15"/>
+      <c r="G112" s="15"/>
+      <c r="H112" s="15"/>
+      <c r="I112" s="15"/>
+      <c r="J112" s="15"/>
+      <c r="K112" s="15"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" s="15"/>
+      <c r="B113" s="16" t="str">
+        <f>B99</f>
+        <v>-for wall continue</v>
+      </c>
+      <c r="C113" s="45">
+        <v>1</v>
+      </c>
+      <c r="D113" s="3">
+        <f>(15*2+(9.75+1.17*2)*2)/3.281</f>
+        <v>16.513258153002134</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="G113" s="3">
+        <f>PRODUCT(C113:F113)</f>
+        <v>50.329954748558777</v>
+      </c>
+      <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
+      <c r="J113" s="15"/>
+      <c r="K113" s="15"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="15"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="45">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3">
+        <f>((15-1.17*2)*2+(9.75*2))/3.281</f>
+        <v>13.660469369094788</v>
+      </c>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="G114" s="3">
+        <f>PRODUCT(C114:F114)</f>
+        <v>41.635078845153267</v>
+      </c>
+      <c r="H114" s="15"/>
+      <c r="I114" s="15"/>
+      <c r="J114" s="15"/>
+      <c r="K114" s="15"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="15"/>
+      <c r="B115" s="16" t="str">
+        <f>B101</f>
+        <v>-deduction for door</v>
+      </c>
+      <c r="C115" s="45">
+        <f>2*C101</f>
+        <v>-2</v>
+      </c>
+      <c r="D115" s="3">
+        <f>D101</f>
+        <v>1.5</v>
+      </c>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3">
+        <f>7/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
+      <c r="G115" s="3">
+        <f t="shared" ref="G115" si="24">PRODUCT(C115:F115)</f>
+        <v>-6.400487656202376</v>
+      </c>
+      <c r="H115" s="15"/>
+      <c r="I115" s="15"/>
+      <c r="J115" s="15"/>
+      <c r="K115" s="15"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="15"/>
+      <c r="B116" s="16" t="str">
+        <f>B102</f>
+        <v>-deduction for window</v>
+      </c>
+      <c r="C116" s="45">
+        <f>2*C102</f>
+        <v>-4</v>
+      </c>
+      <c r="D116" s="3">
+        <f>D102</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3">
+        <f>F102</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G116" s="3">
+        <f t="shared" ref="G116" si="25">PRODUCT(C116:F116)</f>
+        <v>-4.5518046930221097</v>
+      </c>
+      <c r="H116" s="15"/>
+      <c r="I116" s="15"/>
+      <c r="J116" s="15"/>
+      <c r="K116" s="15"/>
+    </row>
+    <row r="117" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="24"/>
+      <c r="B117" s="25" t="str">
+        <f>B103</f>
+        <v>-for wing walls of stand tap</v>
+      </c>
+      <c r="C117" s="26">
+        <f>C14*4</f>
+        <v>4</v>
+      </c>
+      <c r="D117" s="27">
+        <f>M10-O10*2</f>
+        <v>1.2163181956720512</v>
+      </c>
+      <c r="E117" s="27"/>
+      <c r="F117" s="27">
+        <f>P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G117" s="27">
+        <f>PRODUCT(C117:F117)</f>
+        <v>2.9191636696129231</v>
+      </c>
+      <c r="H117" s="26"/>
+      <c r="I117" s="26"/>
+      <c r="J117" s="26"/>
+      <c r="K117" s="26"/>
+    </row>
+    <row r="118" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="24"/>
+      <c r="B118" s="25" t="str">
+        <f>B104</f>
+        <v>-for side wall of stand tap</v>
+      </c>
+      <c r="C118" s="26">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D118" s="27">
+        <f>M10-R10</f>
+        <v>1.3197195976836331</v>
+      </c>
+      <c r="E118" s="27"/>
+      <c r="F118" s="27">
+        <f>P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G118" s="27">
+        <f>PRODUCT(C118:F118)</f>
+        <v>0.79183175861017985</v>
+      </c>
+      <c r="H118" s="26"/>
+      <c r="I118" s="26"/>
+      <c r="J118" s="26"/>
+      <c r="K118" s="26"/>
+    </row>
+    <row r="119" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="24"/>
+      <c r="B119" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C119" s="26">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D119" s="27">
+        <f>R10</f>
+        <v>0.35659859798841814</v>
+      </c>
+      <c r="E119" s="27"/>
+      <c r="F119" s="27">
+        <f>Q10</f>
+        <v>1.2</v>
+      </c>
+      <c r="G119" s="27">
+        <f>PRODUCT(C119:F119)</f>
+        <v>0.42791831758610177</v>
+      </c>
+      <c r="H119" s="26"/>
+      <c r="I119" s="26"/>
+      <c r="J119" s="26"/>
+      <c r="K119" s="26"/>
+    </row>
+    <row r="120" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="24"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="26">
+        <f>C119</f>
+        <v>1</v>
+      </c>
+      <c r="D120" s="27">
+        <f>O10*2</f>
+        <v>0.46</v>
+      </c>
+      <c r="E120" s="27"/>
+      <c r="F120" s="27">
+        <f>Q10-P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G120" s="27">
+        <f>PRODUCT(C120:F120)</f>
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="H120" s="26"/>
+      <c r="I120" s="26"/>
+      <c r="J120" s="26"/>
+      <c r="K120" s="26"/>
+    </row>
+    <row r="121" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="17"/>
+      <c r="B121" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="19"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="20"/>
+      <c r="F121" s="20"/>
+      <c r="G121" s="2">
+        <f>SUM(G113:G120)</f>
+        <v>85.427654990296773</v>
+      </c>
+      <c r="H121" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I121" s="2">
+        <v>415.5</v>
+      </c>
+      <c r="J121" s="22">
+        <f>G121*I121</f>
+        <v>35495.190648468306</v>
+      </c>
+      <c r="K121" s="20"/>
+    </row>
+    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="24"/>
+      <c r="B122" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C122" s="26"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="27"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="27"/>
+      <c r="H122" s="26"/>
+      <c r="I122" s="26"/>
+      <c r="J122" s="22">
+        <f>0.13*G121*7010.67/100</f>
+        <v>778.57662741407114</v>
+      </c>
+      <c r="K122" s="26"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="15"/>
+      <c r="B123" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C123" s="26"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="27"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="27"/>
+      <c r="H123" s="26"/>
+      <c r="I123" s="26"/>
+      <c r="J123" s="22">
+        <f>0.13*G121*4639.73/100</f>
+        <v>515.26962979456857</v>
+      </c>
+      <c r="K123" s="15"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="15"/>
+      <c r="B124" s="15"/>
+      <c r="C124" s="15"/>
+      <c r="D124" s="15"/>
+      <c r="E124" s="15"/>
+      <c r="F124" s="15"/>
+      <c r="G124" s="15"/>
+      <c r="H124" s="15"/>
+      <c r="I124" s="15"/>
+      <c r="J124" s="15"/>
+      <c r="K124" s="15"/>
+    </row>
+    <row r="125" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A125" s="11">
+        <v>11</v>
+      </c>
+      <c r="B125" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C125" s="15"/>
+      <c r="D125" s="15"/>
+      <c r="E125" s="15"/>
+      <c r="F125" s="15"/>
+      <c r="G125" s="15"/>
+      <c r="H125" s="15"/>
+      <c r="I125" s="15"/>
+      <c r="J125" s="15"/>
+      <c r="K125" s="15"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="15"/>
+      <c r="B126" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C126" s="3">
+        <f>C113</f>
+        <v>1</v>
+      </c>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3">
+        <f>SUM(G113:G116)</f>
+        <v>81.012741244487557</v>
+      </c>
+      <c r="H126" s="15"/>
+      <c r="I126" s="15"/>
+      <c r="J126" s="15"/>
+      <c r="K126" s="15"/>
+    </row>
+    <row r="127" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="17"/>
+      <c r="B127" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" s="19"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="20"/>
+      <c r="F127" s="20"/>
+      <c r="G127" s="2">
+        <f>SUM(G126:G126)</f>
+        <v>81.012741244487557</v>
+      </c>
+      <c r="H127" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127" s="2">
+        <v>253.8</v>
+      </c>
+      <c r="J127" s="22">
+        <f>G127*I127</f>
+        <v>20561.033727850943</v>
+      </c>
+      <c r="K127" s="20"/>
+    </row>
+    <row r="128" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="24"/>
+      <c r="B128" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C128" s="26"/>
+      <c r="D128" s="27"/>
+      <c r="E128" s="27"/>
+      <c r="F128" s="27"/>
+      <c r="G128" s="27"/>
+      <c r="H128" s="26"/>
+      <c r="I128" s="26"/>
+      <c r="J128" s="22">
+        <f>0.13*G127*2304/100</f>
+        <v>242.64936257548914</v>
+      </c>
+      <c r="K128" s="26"/>
+    </row>
+    <row r="129" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="24"/>
+      <c r="B129" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C129" s="26"/>
+      <c r="D129" s="27"/>
+      <c r="E129" s="27"/>
+      <c r="F129" s="27"/>
+      <c r="G129" s="27"/>
+      <c r="H129" s="26"/>
+      <c r="I129" s="26"/>
+      <c r="J129" s="22">
+        <f>0.13*G127*10432/100</f>
+        <v>1098.6623916612425</v>
+      </c>
+      <c r="K129" s="26"/>
+    </row>
+    <row r="130" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="24"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="26"/>
+      <c r="D130" s="27"/>
+      <c r="E130" s="27"/>
+      <c r="F130" s="27"/>
+      <c r="G130" s="27"/>
+      <c r="H130" s="26"/>
+      <c r="I130" s="26"/>
+      <c r="J130" s="22"/>
+      <c r="K130" s="26"/>
+    </row>
+    <row r="131" spans="1:11" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A131" s="24">
+        <v>12</v>
+      </c>
+      <c r="B131" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C131" s="26"/>
+      <c r="D131" s="27"/>
+      <c r="E131" s="27"/>
+      <c r="F131" s="27"/>
+      <c r="G131" s="27"/>
+      <c r="H131" s="26"/>
+      <c r="I131" s="26"/>
+      <c r="J131" s="22"/>
+      <c r="K131" s="26"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="15"/>
+      <c r="B132" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C132" s="3">
+        <v>1</v>
+      </c>
+      <c r="D132" s="3">
+        <f>D101</f>
+        <v>1.5</v>
+      </c>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3">
+        <f>F101</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G132" s="3">
+        <f>PRODUCT(C132:F132)</f>
+        <v>1.600121914050594</v>
+      </c>
+      <c r="H132" s="15"/>
+      <c r="I132" s="15"/>
+      <c r="J132" s="15"/>
+      <c r="K132" s="15"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="15"/>
+      <c r="B133" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C133" s="3">
+        <v>2</v>
+      </c>
+      <c r="D133" s="3">
+        <f>D102</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3">
+        <f>F102</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G133" s="3">
+        <f>PRODUCT(C133:F133)</f>
+        <v>2.2759023465110548</v>
+      </c>
+      <c r="H133" s="15"/>
+      <c r="I133" s="15"/>
+      <c r="J133" s="15"/>
+      <c r="K133" s="15"/>
+    </row>
+    <row r="134" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="17"/>
+      <c r="B134" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" s="19"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="20"/>
+      <c r="F134" s="20"/>
+      <c r="G134" s="2">
+        <f>SUM(G132:G133)</f>
+        <v>3.8760242605616488</v>
+      </c>
+      <c r="H134" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I134" s="2">
+        <v>37363.64</v>
+      </c>
+      <c r="J134" s="22">
+        <f>G134*I134</f>
+        <v>144822.37510289164</v>
+      </c>
+      <c r="K134" s="20"/>
+    </row>
+    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="24"/>
+      <c r="B135" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C135" s="26"/>
+      <c r="D135" s="27"/>
+      <c r="E135" s="27"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
+      <c r="H135" s="26"/>
+      <c r="I135" s="26"/>
+      <c r="J135" s="22">
+        <f>0.13*G134*7910.91/0.92</f>
+        <v>4332.7981313104001</v>
+      </c>
+      <c r="K135" s="26"/>
+    </row>
+    <row r="136" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="24"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="26"/>
+      <c r="D136" s="27"/>
+      <c r="E136" s="27"/>
+      <c r="F136" s="27"/>
+      <c r="G136" s="27"/>
+      <c r="H136" s="26"/>
+      <c r="I136" s="26"/>
+      <c r="J136" s="22"/>
+      <c r="K136" s="26"/>
+    </row>
+    <row r="137" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A137" s="24">
+        <v>13</v>
+      </c>
+      <c r="B137" s="75" t="s">
+        <v>143</v>
+      </c>
+      <c r="C137" s="26"/>
+      <c r="D137" s="26"/>
+      <c r="E137" s="26"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="26"/>
+      <c r="H137" s="26"/>
+      <c r="I137" s="26"/>
+      <c r="J137" s="26"/>
+      <c r="K137" s="26"/>
+    </row>
+    <row r="138" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="24"/>
+      <c r="B138" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C138" s="26">
+        <v>1</v>
+      </c>
+      <c r="D138" s="27">
+        <f>Q10</f>
+        <v>1.2</v>
+      </c>
+      <c r="E138" s="26"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="27">
+        <f t="shared" ref="G138" si="26">PRODUCT(C138:F138)</f>
+        <v>1.2</v>
+      </c>
+      <c r="H138" s="26"/>
+      <c r="I138" s="26"/>
+      <c r="J138" s="22"/>
+      <c r="K138" s="26"/>
+    </row>
+    <row r="139" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="17"/>
+      <c r="B139" s="80" t="s">
+        <v>145</v>
+      </c>
+      <c r="C139" s="19"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="20"/>
+      <c r="F139" s="20"/>
+      <c r="G139" s="81">
+        <f>SUM(G138:G138)</f>
+        <v>1.2</v>
+      </c>
+      <c r="H139" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I139" s="2">
+        <v>248</v>
+      </c>
+      <c r="J139" s="81">
+        <f>G139*I139</f>
+        <v>297.59999999999997</v>
+      </c>
+      <c r="K139" s="20"/>
+    </row>
+    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="24"/>
+      <c r="B140" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C140" s="26"/>
+      <c r="D140" s="26"/>
+      <c r="E140" s="26"/>
+      <c r="F140" s="26"/>
+      <c r="G140" s="26"/>
+      <c r="H140" s="26"/>
+      <c r="I140" s="26"/>
+      <c r="J140" s="22">
+        <f>0.13*J139</f>
+        <v>38.687999999999995</v>
+      </c>
+      <c r="K140" s="26"/>
+    </row>
+    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="24"/>
+      <c r="B141" s="75"/>
+      <c r="C141" s="26"/>
+      <c r="D141" s="26"/>
+      <c r="E141" s="26"/>
+      <c r="F141" s="26"/>
+      <c r="G141" s="26"/>
+      <c r="H141" s="26"/>
+      <c r="I141" s="26"/>
+      <c r="J141" s="26"/>
+      <c r="K141" s="26"/>
+    </row>
+    <row r="142" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A142" s="17">
+        <v>14</v>
+      </c>
+      <c r="B142" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C142" s="19">
+        <v>1</v>
+      </c>
+      <c r="D142" s="1"/>
+      <c r="E142" s="20"/>
+      <c r="F142" s="20"/>
+      <c r="G142" s="21">
+        <f t="shared" ref="G142" si="27">PRODUCT(C142:F142)</f>
+        <v>1</v>
+      </c>
+      <c r="H142" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I142" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J142" s="21">
+        <f>G142*I142</f>
+        <v>5000</v>
+      </c>
+      <c r="K142" s="20"/>
+    </row>
+    <row r="143" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="17"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="19"/>
+      <c r="D143" s="1"/>
+      <c r="E143" s="20"/>
+      <c r="F143" s="20"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="21"/>
+      <c r="I143" s="2"/>
+      <c r="J143" s="22"/>
+      <c r="K143" s="20"/>
+    </row>
+    <row r="144" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="17">
+        <v>15</v>
+      </c>
+      <c r="B144" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B113" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C113" s="19">
+      <c r="C144" s="19">
         <v>1</v>
       </c>
-      <c r="D113" s="1"/>
-      <c r="E113" s="20"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="21">
-        <f t="shared" ref="G113" si="25">PRODUCT(C113:F113)</f>
+      <c r="D144" s="1"/>
+      <c r="E144" s="20"/>
+      <c r="F144" s="20"/>
+      <c r="G144" s="21">
+        <f t="shared" ref="G144" si="28">PRODUCT(C144:F144)</f>
         <v>1</v>
       </c>
-      <c r="H113" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I113" s="2">
-        <v>5000</v>
-      </c>
-      <c r="J113" s="21">
-        <f>G113*I113</f>
-        <v>5000</v>
-      </c>
-      <c r="K113" s="20"/>
-    </row>
-    <row r="114" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="17"/>
-      <c r="B114" s="31"/>
-      <c r="C114" s="19"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="20"/>
-      <c r="F114" s="20"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="21"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="22"/>
-      <c r="K114" s="20"/>
-    </row>
-    <row r="115" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="17">
+      <c r="H144" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B115" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C115" s="19">
-        <v>1</v>
-      </c>
-      <c r="D115" s="1"/>
-      <c r="E115" s="20"/>
-      <c r="F115" s="20"/>
-      <c r="G115" s="21">
-        <f t="shared" ref="G115" si="26">PRODUCT(C115:F115)</f>
-        <v>1</v>
-      </c>
-      <c r="H115" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I115" s="2">
+      <c r="I144" s="2">
         <v>500</v>
       </c>
-      <c r="J115" s="21">
-        <f>G115*I115</f>
+      <c r="J144" s="21">
+        <f>G144*I144</f>
         <v>500</v>
       </c>
-      <c r="K115" s="20"/>
-    </row>
-    <row r="116" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="17"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="19"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="20"/>
-      <c r="F116" s="20"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="21"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="22"/>
-      <c r="K116" s="20"/>
-    </row>
-    <row r="117" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="32"/>
-      <c r="B117" s="33" t="s">
+      <c r="K144" s="20"/>
+    </row>
+    <row r="145" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="17"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="19"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="20"/>
+      <c r="F145" s="20"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="21"/>
+      <c r="I145" s="2"/>
+      <c r="J145" s="22"/>
+      <c r="K145" s="20"/>
+    </row>
+    <row r="146" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="32"/>
+      <c r="B146" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C117" s="34"/>
-      <c r="D117" s="35"/>
-      <c r="E117" s="35"/>
-      <c r="F117" s="35"/>
-      <c r="G117" s="22"/>
-      <c r="H117" s="22"/>
-      <c r="I117" s="22"/>
-      <c r="J117" s="22">
-        <f>SUM(J9:J115)</f>
-        <v>370065.78807681054</v>
-      </c>
-      <c r="K117" s="36"/>
-    </row>
-    <row r="118" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="37"/>
-      <c r="B119" s="38" t="s">
+      <c r="C146" s="34"/>
+      <c r="D146" s="35"/>
+      <c r="E146" s="35"/>
+      <c r="F146" s="35"/>
+      <c r="G146" s="22"/>
+      <c r="H146" s="22"/>
+      <c r="I146" s="22"/>
+      <c r="J146" s="22">
+        <f>SUM(J19:J144)</f>
+        <v>538273.2168044732</v>
+      </c>
+      <c r="K146" s="36"/>
+    </row>
+    <row r="147" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="37"/>
+      <c r="B148" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C119" s="56">
-        <f>J117</f>
-        <v>370065.78807681054</v>
-      </c>
-      <c r="D119" s="57"/>
-      <c r="E119" s="39">
+      <c r="C148" s="62">
+        <f>J146</f>
+        <v>538273.2168044732</v>
+      </c>
+      <c r="D148" s="63"/>
+      <c r="E148" s="39">
         <v>100</v>
       </c>
-      <c r="F119" s="37"/>
-      <c r="G119" s="40"/>
-      <c r="H119" s="37"/>
-      <c r="I119" s="41"/>
-      <c r="J119" s="42"/>
-      <c r="K119" s="43"/>
-    </row>
-    <row r="120" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="38" t="s">
+      <c r="F148" s="37"/>
+      <c r="G148" s="40"/>
+      <c r="H148" s="37"/>
+      <c r="I148" s="41"/>
+      <c r="J148" s="42"/>
+      <c r="K148" s="43"/>
+    </row>
+    <row r="149" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C120" s="60">
+      <c r="C149" s="66">
         <v>700000</v>
       </c>
-      <c r="D120" s="61"/>
-      <c r="E120" s="39"/>
-    </row>
-    <row r="121" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="38" t="s">
+      <c r="D149" s="67"/>
+      <c r="E149" s="39"/>
+    </row>
+    <row r="150" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B150" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C121" s="60">
-        <f>C120-C123-C124</f>
+      <c r="C150" s="66">
+        <f>C149-C152-C153</f>
         <v>665000</v>
       </c>
-      <c r="D121" s="61"/>
-      <c r="E121" s="39">
-        <f>C121/C119*100</f>
-        <v>179.69777845607635</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="38" t="s">
+      <c r="D150" s="67"/>
+      <c r="E150" s="39">
+        <f>C150/C148*100</f>
+        <v>123.54320802878811</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C122" s="62">
-        <f>C119-C121</f>
-        <v>-294934.21192318946</v>
-      </c>
-      <c r="D122" s="62"/>
-      <c r="E122" s="39">
-        <f>100-E121</f>
-        <v>-79.69777845607635</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="38" t="s">
+      <c r="C151" s="68">
+        <f>C148-C150</f>
+        <v>-126726.7831955268</v>
+      </c>
+      <c r="D151" s="68"/>
+      <c r="E151" s="39">
+        <f>100-E150</f>
+        <v>-23.543208028788115</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C123" s="56">
-        <f>C120*0.03</f>
+      <c r="C152" s="62">
+        <f>C149*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D123" s="57"/>
-      <c r="E123" s="39">
+      <c r="D152" s="63"/>
+      <c r="E152" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="38" t="s">
+    <row r="153" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C124" s="56">
-        <f>C120*0.02</f>
+      <c r="C153" s="62">
+        <f>C149*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D124" s="57"/>
-      <c r="E124" s="39">
+      <c r="D153" s="63"/>
+      <c r="E153" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="C151:D151"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -4047,14 +4913,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C122:D122"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -4083,113 +4941,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="59" t="s">
+      <c r="H7" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -8552,11 +9410,11 @@
       <c r="B197" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C197" s="56">
+      <c r="C197" s="62">
         <f>J195</f>
         <v>783511.5632557295</v>
       </c>
-      <c r="D197" s="57"/>
+      <c r="D197" s="63"/>
       <c r="E197" s="39">
         <v>100</v>
       </c>
@@ -8571,21 +9429,21 @@
       <c r="B198" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C198" s="60">
+      <c r="C198" s="66">
         <v>700000</v>
       </c>
-      <c r="D198" s="61"/>
+      <c r="D198" s="67"/>
       <c r="E198" s="39"/>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B199" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C199" s="60">
+      <c r="C199" s="66">
         <f>C198-C201-C202</f>
         <v>665000</v>
       </c>
-      <c r="D199" s="61"/>
+      <c r="D199" s="67"/>
       <c r="E199" s="39">
         <f>C199/C197*100</f>
         <v>84.874305777533408</v>
@@ -8595,11 +9453,11 @@
       <c r="B200" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C200" s="62">
+      <c r="C200" s="68">
         <f>C197-C199</f>
         <v>118511.5632557295</v>
       </c>
-      <c r="D200" s="62"/>
+      <c r="D200" s="68"/>
       <c r="E200" s="39">
         <f>100-E199</f>
         <v>15.125694222466592</v>
@@ -8609,11 +9467,11 @@
       <c r="B201" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C201" s="56">
+      <c r="C201" s="62">
         <f>C198*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D201" s="57"/>
+      <c r="D201" s="63"/>
       <c r="E201" s="39">
         <v>3</v>
       </c>
@@ -8622,24 +9480,17 @@
       <c r="B202" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C202" s="56">
+      <c r="C202" s="62">
         <f>C198*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D202" s="57"/>
+      <c r="D202" s="63"/>
       <c r="E202" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C201:D201"/>
     <mergeCell ref="C202:D202"/>
     <mergeCell ref="A7:F7"/>
@@ -8648,6 +9499,13 @@
     <mergeCell ref="C198:D198"/>
     <mergeCell ref="C199:D199"/>
     <mergeCell ref="C200:D200"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>

--- a/बजेट माग estimate/नगर बजेट estimate/प‍‍‌‌‌‌ञ्चपाले भिमसेन मन्दिर अधुरो/प‍‍‌‌‌‌ञ्चपाले भिमसेन मन्दिर अधुरो.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/प‍‍‌‌‌‌ञ्चपाले भिमसेन मन्दिर अधुरो/प‍‍‌‌‌‌ञ्चपाले भिमसेन मन्दिर अधुरो.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53169F8C-704B-48D7-95F9-2DD1BAD094A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="initial 2 storey" sheetId="14" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="16" r:id="rId2"/>
-    <sheet name="2.5' ht" sheetId="17" r:id="rId3"/>
+    <sheet name="initial 2 storey" sheetId="14" state="hidden" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="16" state="hidden" r:id="rId2"/>
+    <sheet name="2.5' ht" sheetId="17" state="hidden" r:id="rId3"/>
     <sheet name="total slope" sheetId="18" r:id="rId4"/>
+    <sheet name="2.667'column height" sheetId="19" state="hidden" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="description_103">[1]Abstract!$B$16</definedName>
     <definedName name="description_124" localSheetId="2">#REF!</definedName>
+    <definedName name="description_124" localSheetId="4">#REF!</definedName>
     <definedName name="description_124" localSheetId="3">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
     <definedName name="description_247">[1]Abstract!$B$22</definedName>
@@ -29,29 +32,35 @@
     <definedName name="description_276">[3]Abstract!$B$40</definedName>
     <definedName name="description_3">[1]Abstract!$B$169</definedName>
     <definedName name="description_310" localSheetId="2">#REF!</definedName>
+    <definedName name="description_310" localSheetId="4">#REF!</definedName>
     <definedName name="description_310" localSheetId="3">#REF!</definedName>
     <definedName name="description_310">#REF!</definedName>
     <definedName name="description_312" localSheetId="2">#REF!</definedName>
+    <definedName name="description_312" localSheetId="4">#REF!</definedName>
     <definedName name="description_312" localSheetId="3">#REF!</definedName>
     <definedName name="description_312">#REF!</definedName>
     <definedName name="description_5">[1]Abstract!$B$171</definedName>
     <definedName name="description_6" localSheetId="2">#REF!</definedName>
+    <definedName name="description_6" localSheetId="4">#REF!</definedName>
     <definedName name="description_6" localSheetId="3">#REF!</definedName>
     <definedName name="description_6">#REF!</definedName>
     <definedName name="description_759">[1]Abstract!$B$278</definedName>
     <definedName name="description_781" localSheetId="2">#REF!</definedName>
+    <definedName name="description_781" localSheetId="4">#REF!</definedName>
     <definedName name="description_781" localSheetId="3">#REF!</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'2.5'' ht'!$A$1:$K$193</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'2.667''column height'!$A$1:$K$193</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'initial 2 storey'!$A$1:$K$152</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'total slope'!$A$1:$K$193</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2.5'' ht'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'2.667''column height'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'initial 2 storey'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'total slope'!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -69,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="139">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -554,15 +563,18 @@
   <si>
     <t>-13% VAT for porcelain glazed tile</t>
   </si>
+  <si>
+    <t>Highly Carved salwood lattice (jali) shutter of carved door/window including wood</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -753,9 +765,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -771,14 +783,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -807,7 +819,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -844,7 +856,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -862,7 +874,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -871,8 +883,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -881,14 +893,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -904,7 +916,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -914,26 +926,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -953,6 +947,24 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -975,11 +987,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -995,7 +1007,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1089,7 +1101,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1148,7 +1160,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1212,9 +1224,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1252,9 +1264,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1289,7 +1301,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1324,7 +1336,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1497,7 +1509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y152"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1513,113 +1525,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="72" t="s">
+      <c r="H7" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
     </row>
     <row r="8" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4783,11 +4795,11 @@
       <c r="B147" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C147" s="69">
+      <c r="C147" s="63">
         <f>J145</f>
         <v>535761.86997382692</v>
       </c>
-      <c r="D147" s="70"/>
+      <c r="D147" s="64"/>
       <c r="E147" s="39">
         <v>100</v>
       </c>
@@ -4802,21 +4814,21 @@
       <c r="B148" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C148" s="73">
+      <c r="C148" s="67">
         <v>700000</v>
       </c>
-      <c r="D148" s="74"/>
+      <c r="D148" s="68"/>
       <c r="E148" s="39"/>
     </row>
     <row r="149" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B149" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C149" s="73">
+      <c r="C149" s="67">
         <f>C148-C151-C152</f>
         <v>665000</v>
       </c>
-      <c r="D149" s="74"/>
+      <c r="D149" s="68"/>
       <c r="E149" s="39">
         <f>C149/C147*100</f>
         <v>124.12230829948511</v>
@@ -4826,11 +4838,11 @@
       <c r="B150" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C150" s="75">
+      <c r="C150" s="69">
         <f>C147-C149</f>
         <v>-129238.13002617308</v>
       </c>
-      <c r="D150" s="75"/>
+      <c r="D150" s="69"/>
       <c r="E150" s="39">
         <f>100-E149</f>
         <v>-24.122308299485113</v>
@@ -4840,11 +4852,11 @@
       <c r="B151" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C151" s="69">
+      <c r="C151" s="63">
         <f>C148*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D151" s="70"/>
+      <c r="D151" s="64"/>
       <c r="E151" s="39">
         <v>3</v>
       </c>
@@ -4853,17 +4865,24 @@
       <c r="B152" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C152" s="69">
+      <c r="C152" s="63">
         <f>C148*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D152" s="70"/>
+      <c r="D152" s="64"/>
       <c r="E152" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C151:D151"/>
     <mergeCell ref="C152:D152"/>
     <mergeCell ref="A7:F7"/>
@@ -4872,13 +4891,6 @@
     <mergeCell ref="C148:D148"/>
     <mergeCell ref="C149:D149"/>
     <mergeCell ref="C150:D150"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -4889,7 +4901,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:W4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5116,7 +5128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Y193"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5132,113 +5144,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="72" t="s">
+      <c r="H7" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
     </row>
     <row r="8" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -9259,11 +9271,11 @@
       <c r="B188" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C188" s="69">
+      <c r="C188" s="63">
         <f>J186</f>
         <v>783062.29195295041</v>
       </c>
-      <c r="D188" s="70"/>
+      <c r="D188" s="64"/>
       <c r="E188" s="39">
         <v>100</v>
       </c>
@@ -9278,21 +9290,21 @@
       <c r="B189" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C189" s="73">
+      <c r="C189" s="67">
         <v>700000</v>
       </c>
-      <c r="D189" s="74"/>
+      <c r="D189" s="68"/>
       <c r="E189" s="39"/>
     </row>
     <row r="190" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B190" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C190" s="73">
+      <c r="C190" s="67">
         <f>C189-C192-C193</f>
         <v>665000</v>
       </c>
-      <c r="D190" s="74"/>
+      <c r="D190" s="68"/>
       <c r="E190" s="39">
         <f>C190/C188*100</f>
         <v>84.923001252109316</v>
@@ -9302,11 +9314,11 @@
       <c r="B191" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C191" s="75">
+      <c r="C191" s="69">
         <f>C188-C190</f>
         <v>118062.29195295041</v>
       </c>
-      <c r="D191" s="75"/>
+      <c r="D191" s="69"/>
       <c r="E191" s="39">
         <f>100-E190</f>
         <v>15.076998747890684</v>
@@ -9316,11 +9328,11 @@
       <c r="B192" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C192" s="69">
+      <c r="C192" s="63">
         <f>C189*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D192" s="70"/>
+      <c r="D192" s="64"/>
       <c r="E192" s="39">
         <v>3</v>
       </c>
@@ -9329,11 +9341,4272 @@
       <c r="B193" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C193" s="69">
+      <c r="C193" s="63">
         <f>C189*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D193" s="70"/>
+      <c r="D193" s="64"/>
+      <c r="E193" s="39">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Y193"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+    </row>
+    <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+    </row>
+    <row r="6" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="66" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+    </row>
+    <row r="8" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" s="44" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="51">
+        <v>1</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="53"/>
+      <c r="M9" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+    </row>
+    <row r="10" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="49">
+        <v>1</v>
+      </c>
+      <c r="D10" s="27">
+        <f>5.5/3.281</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="E10" s="27">
+        <f>5.5/3.281</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="F10" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="27">
+        <f>PRODUCT(C10:F10)</f>
+        <v>0.42150640397118022</v>
+      </c>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="M10" s="54">
+        <f>5.5/3.281</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="N10" s="54">
+        <f>5.5/3.281</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="O10" s="54">
+        <v>0.23</v>
+      </c>
+      <c r="P10" s="54">
+        <f>TRUNC(2/3.281,1)</f>
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="54">
+        <f>TRUNC(4/3.281,1)</f>
+        <v>1.2</v>
+      </c>
+      <c r="R10" s="54">
+        <f>1.17/3.281</f>
+        <v>0.35659859798841814</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="2">
+        <f>SUM(G10)</f>
+        <v>0.42150640397118022</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="2">
+        <v>674.12</v>
+      </c>
+      <c r="J11" s="22">
+        <f>G11*I11</f>
+        <v>284.14589704505204</v>
+      </c>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="24">
+        <v>2</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+    </row>
+    <row r="14" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25" t="str">
+        <f>B10</f>
+        <v>-for stand tap</v>
+      </c>
+      <c r="C14" s="49">
+        <f>C10</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="27">
+        <f>D10</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="E14" s="27">
+        <f>E10</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="27">
+        <f>PRODUCT(C14:F14)</f>
+        <v>2.8100426931412015</v>
+      </c>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+    </row>
+    <row r="15" spans="1:25" s="10" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="2">
+        <f>SUM(G14)</f>
+        <v>2.8100426931412015</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1017.47</v>
+      </c>
+      <c r="J15" s="22">
+        <f>G15*I15</f>
+        <v>2859.1341389903782</v>
+      </c>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="22">
+        <f>0.13*G15*6360.9/10</f>
+        <v>232.36720736842426</v>
+      </c>
+      <c r="K16" s="26"/>
+    </row>
+    <row r="17" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="22">
+        <f>0.13*G15*2256.3/10</f>
+        <v>82.423891270948417</v>
+      </c>
+      <c r="K17" s="26"/>
+    </row>
+    <row r="18" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="26"/>
+    </row>
+    <row r="19" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>3</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="45">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="D20" s="3">
+        <f>15/3.281</f>
+        <v>4.5717768972874122</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="3">
+        <f>PRODUCT(C20:F20)</f>
+        <v>0.32002438281011886</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="45">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="D21" s="3">
+        <f>9.75/3.281</f>
+        <v>2.9716549832368178</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="3">
+        <f>PRODUCT(C21:F21)</f>
+        <v>0.20801584882657723</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="str">
+        <f>B14</f>
+        <v>-for stand tap</v>
+      </c>
+      <c r="C22" s="62">
+        <f t="shared" ref="C22:E22" si="0">C14</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="57">
+        <f t="shared" si="0"/>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="E22" s="57">
+        <f t="shared" si="0"/>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="F22" s="57">
+        <v>0.1</v>
+      </c>
+      <c r="G22" s="3">
+        <f>PRODUCT(C22:F22)</f>
+        <v>0.28100426931412015</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+    </row>
+    <row r="23" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="2">
+        <f>SUM(G20:G22)</f>
+        <v>0.80904450095081626</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="2">
+        <v>12884.61</v>
+      </c>
+      <c r="J23" s="22">
+        <f>G23*I23</f>
+        <v>10424.222867395898</v>
+      </c>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="22">
+        <f>0.13*G23*4169.92</f>
+        <v>438.57460990262763</v>
+      </c>
+      <c r="K24" s="26"/>
+    </row>
+    <row r="25" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="22">
+        <f>0.13*G23*(1652.5+1106.96)</f>
+        <v>290.22837201718613</v>
+      </c>
+      <c r="K25" s="26"/>
+    </row>
+    <row r="26" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="22">
+        <f>0.13*G23*1414.16</f>
+        <v>148.73538829039884</v>
+      </c>
+      <c r="K26" s="26"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="22">
+        <f>0.13*G23*36.4</f>
+        <v>3.8283985784992627</v>
+      </c>
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="22">
+        <f>0.13*G23*392.92</f>
+        <v>41.325669490767318</v>
+      </c>
+      <c r="K28" s="15"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="22">
+        <f>0.13*G23*14.15</f>
+        <v>1.4882373594990266</v>
+      </c>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A31" s="11">
+        <v>4</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="45">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3">
+        <f>15/3.281</f>
+        <v>4.5717768972874122</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" ref="G32:G38" si="1">PRODUCT(C32:F32)</f>
+        <v>0.73605608046327342</v>
+      </c>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="45">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D33" s="3">
+        <f>9.75/3.281</f>
+        <v>2.9716549832368178</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.95687290460225527</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="45">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3">
+        <f>5/3.281</f>
+        <v>1.5239256324291375</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="1"/>
+        <v>0.16123133191100275</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="45">
+        <v>2</v>
+      </c>
+      <c r="D35" s="3">
+        <f>3.75/3.281</f>
+        <v>1.1429442243218531</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="1"/>
+        <v>0.12092349893325208</v>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" s="45">
+        <v>2</v>
+      </c>
+      <c r="D36" s="3">
+        <f>((18.25)/2)/3.281</f>
+        <v>2.7811642791831757</v>
+      </c>
+      <c r="E36" s="3">
+        <f>10.5/3.281</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F36" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="1"/>
+        <v>1.335060572908717</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="15"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="45">
+        <v>2</v>
+      </c>
+      <c r="D37" s="3">
+        <f>((15.25)/2)/3.281</f>
+        <v>2.3239865894544347</v>
+      </c>
+      <c r="E37" s="3">
+        <f>9.5/3.281</f>
+        <v>2.895458701615361</v>
+      </c>
+      <c r="F37" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G37" s="3">
+        <f t="shared" si="1"/>
+        <v>1.0093510789309872</v>
+      </c>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="15"/>
+      <c r="B38" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="45">
+        <v>4</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F38" s="3">
+        <f>(2.667/3.281)</f>
+        <v>0.81286193233770188</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" si="1"/>
+        <v>0.17200158488265774</v>
+      </c>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+    </row>
+    <row r="39" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="2">
+        <f>SUM(G32:G38)</f>
+        <v>4.4914970526321456</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="2">
+        <v>13957.29</v>
+      </c>
+      <c r="J39" s="22">
+        <f>G39*I39</f>
+        <v>62689.126897732123</v>
+      </c>
+      <c r="K39" s="20"/>
+    </row>
+    <row r="40" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="26"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="22">
+        <f>0.13*G39*5212.4</f>
+        <v>3043.492300828173</v>
+      </c>
+      <c r="K40" s="26"/>
+    </row>
+    <row r="41" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="22">
+        <f>0.13*G39*(1912.03+921.59)</f>
+        <v>1654.5354641763349</v>
+      </c>
+      <c r="K41" s="26"/>
+    </row>
+    <row r="42" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+      <c r="B42" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="26"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="22">
+        <f>0.13*G39*1350.6</f>
+        <v>788.60806950704682</v>
+      </c>
+      <c r="K42" s="26"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="15"/>
+      <c r="B43" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="15"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="22">
+        <f>0.13*G39*56</f>
+        <v>32.698098543162018</v>
+      </c>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="B44" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="22">
+        <f>0.13*G39*392.92</f>
+        <v>229.42387284962894</v>
+      </c>
+      <c r="K44" s="26"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="15"/>
+      <c r="B45" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="15"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="22">
+        <f>0.13*G39*14.15</f>
+        <v>8.2621088283168316</v>
+      </c>
+      <c r="K45" s="15"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+    </row>
+    <row r="47" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A47" s="11">
+        <v>5</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="16" t="str">
+        <f>B32</f>
+        <v>-beam</v>
+      </c>
+      <c r="C48" s="45">
+        <f>C32</f>
+        <v>2</v>
+      </c>
+      <c r="D48" s="3">
+        <f>D32</f>
+        <v>4.5717768972874122</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3">
+        <f>0.35*2</f>
+        <v>0.7</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" ref="G48:G54" si="2">PRODUCT(C48:F48)</f>
+        <v>6.4004876562023769</v>
+      </c>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="15"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="45">
+        <f>C33</f>
+        <v>4</v>
+      </c>
+      <c r="D49" s="3">
+        <f>D33</f>
+        <v>2.9716549832368178</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3">
+        <f>0.35*2</f>
+        <v>0.7</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" si="2"/>
+        <v>8.3206339530630888</v>
+      </c>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="16" t="str">
+        <f t="shared" ref="B50:D50" si="3">B34</f>
+        <v>-upper beam</v>
+      </c>
+      <c r="C50" s="45">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="3"/>
+        <v>1.5239256324291375</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3">
+        <f t="shared" ref="F50:F51" si="4">0.23*2</f>
+        <v>0.46</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4020115818348065</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="15"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="45">
+        <f>C35</f>
+        <v>2</v>
+      </c>
+      <c r="D51" s="3">
+        <f>D35</f>
+        <v>1.1429442243218531</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3">
+        <f t="shared" si="4"/>
+        <v>0.46</v>
+      </c>
+      <c r="G51" s="3">
+        <f t="shared" si="2"/>
+        <v>1.051508686376105</v>
+      </c>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="15"/>
+      <c r="B52" s="16" t="str">
+        <f t="shared" ref="B52:D52" si="5">B36</f>
+        <v>-slab</v>
+      </c>
+      <c r="C52" s="45">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" si="5"/>
+        <v>2.7811642791831757</v>
+      </c>
+      <c r="E52" s="3">
+        <f>E36</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3">
+        <f t="shared" si="2"/>
+        <v>17.800807638782896</v>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="45">
+        <f>C37</f>
+        <v>2</v>
+      </c>
+      <c r="D53" s="3">
+        <f>D37</f>
+        <v>2.3239865894544347</v>
+      </c>
+      <c r="E53" s="3">
+        <f>E37</f>
+        <v>2.895458701615361</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f t="shared" si="2"/>
+        <v>13.458014385746496</v>
+      </c>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="15"/>
+      <c r="B54" s="16" t="str">
+        <f>B38</f>
+        <v>-column</v>
+      </c>
+      <c r="C54" s="45">
+        <f>C38</f>
+        <v>4</v>
+      </c>
+      <c r="D54" s="3">
+        <f>0.23*4</f>
+        <v>0.92</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3">
+        <f>F38-0.23</f>
+        <v>0.58286193233770189</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1449319110027432</v>
+      </c>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+    </row>
+    <row r="55" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="2">
+        <f>SUM(G48:G54)</f>
+        <v>50.578395813008513</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I55" s="2">
+        <v>922.71</v>
+      </c>
+      <c r="J55" s="22">
+        <f>G55*I55</f>
+        <v>46669.191600621089</v>
+      </c>
+      <c r="K55" s="20"/>
+    </row>
+    <row r="56" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="24"/>
+      <c r="B56" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="22">
+        <f>0.13*G55*20062.02/100</f>
+        <v>1319.1162248790411</v>
+      </c>
+      <c r="K56" s="26"/>
+    </row>
+    <row r="57" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="24"/>
+      <c r="B57" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" s="26"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="22">
+        <f>0.13*G55*13328.25/100</f>
+        <v>876.35795519314979</v>
+      </c>
+      <c r="K57" s="26"/>
+    </row>
+    <row r="58" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="24"/>
+      <c r="B58" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="26"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="22">
+        <f>0.13*G55*10137.6/100</f>
+        <v>666.56660901214161</v>
+      </c>
+      <c r="K58" s="26"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="15"/>
+      <c r="B59" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="15"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="22">
+        <f>0.13*G55*3300/100</f>
+        <v>216.98131803780652</v>
+      </c>
+      <c r="K59" s="15"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+    </row>
+    <row r="61" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>6</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G61" s="23"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="15"/>
+      <c r="B62" s="16" t="str">
+        <f>B32</f>
+        <v>-beam</v>
+      </c>
+      <c r="C62" s="45">
+        <f>C48*(4)</f>
+        <v>8</v>
+      </c>
+      <c r="D62" s="3">
+        <f>D32-0.1+(0.583/3.281)*2</f>
+        <v>4.8271563547698877</v>
+      </c>
+      <c r="E62" s="3">
+        <f>16*16/162</f>
+        <v>1.5802469135802468</v>
+      </c>
+      <c r="F62" s="3">
+        <f t="shared" ref="F62:F78" si="6">PRODUCT(C62:E62)</f>
+        <v>61.024791447955117</v>
+      </c>
+      <c r="G62" s="3">
+        <f t="shared" ref="G62:G78" si="7">F62/1000</f>
+        <v>6.1024791447955119E-2</v>
+      </c>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="15"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="45">
+        <f>C48*(2)</f>
+        <v>4</v>
+      </c>
+      <c r="D63" s="3">
+        <f>D33-0.1+(0.583/3.281)*2</f>
+        <v>3.2270344407192924</v>
+      </c>
+      <c r="E63" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F63" s="3">
+        <f t="shared" si="6"/>
+        <v>11.473900233668594</v>
+      </c>
+      <c r="G63" s="3">
+        <f t="shared" si="7"/>
+        <v>1.1473900233668594E-2</v>
+      </c>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="15"/>
+      <c r="B64" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C64" s="45">
+        <f>2*(TRUNC((D48-0.1-0.23*2)/0.125,0))</f>
+        <v>64</v>
+      </c>
+      <c r="D64" s="3">
+        <f>((0.583*4)+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
+      </c>
+      <c r="E64" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F64" s="3">
+        <f t="shared" si="6"/>
+        <v>20.590891816331212</v>
+      </c>
+      <c r="G64" s="3">
+        <f t="shared" si="7"/>
+        <v>2.0590891816331211E-2</v>
+      </c>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="15"/>
+      <c r="B65" s="16" t="str">
+        <f>B48</f>
+        <v>-beam</v>
+      </c>
+      <c r="C65" s="45">
+        <f>C49*(4)</f>
+        <v>16</v>
+      </c>
+      <c r="D65" s="3">
+        <f>D33-0.1+0.23*2+(0.583/3.281)*2</f>
+        <v>3.6870344407192923</v>
+      </c>
+      <c r="E65" s="3">
+        <f>16*16/162</f>
+        <v>1.5802469135802468</v>
+      </c>
+      <c r="F65" s="3">
+        <f t="shared" si="6"/>
+        <v>93.222796723371729</v>
+      </c>
+      <c r="G65" s="3">
+        <f t="shared" si="7"/>
+        <v>9.3222796723371734E-2</v>
+      </c>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="15"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="45">
+        <f>C49*(2)</f>
+        <v>8</v>
+      </c>
+      <c r="D66" s="3">
+        <f>D34-0.1+0.23*2+(0.583/3.281)*2</f>
+        <v>2.2393050899116123</v>
+      </c>
+      <c r="E66" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F66" s="3">
+        <f t="shared" si="6"/>
+        <v>15.92394730603813</v>
+      </c>
+      <c r="G66" s="3">
+        <f t="shared" si="7"/>
+        <v>1.592394730603813E-2</v>
+      </c>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="15"/>
+      <c r="B67" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" s="45">
+        <f>4*(TRUNC((D49-0.1)/0.125,0))</f>
+        <v>88</v>
+      </c>
+      <c r="D67" s="3">
+        <f>((0.583*4)+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
+      </c>
+      <c r="E67" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F67" s="3">
+        <f t="shared" si="6"/>
+        <v>28.312476247455418</v>
+      </c>
+      <c r="G67" s="3">
+        <f t="shared" si="7"/>
+        <v>2.8312476247455417E-2</v>
+      </c>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="15"/>
+      <c r="B68" s="16" t="str">
+        <f>B50</f>
+        <v>-upper beam</v>
+      </c>
+      <c r="C68" s="45">
+        <f>C50*(3*2)</f>
+        <v>12</v>
+      </c>
+      <c r="D68" s="3">
+        <f>D34+(0.583/3.281)*2</f>
+        <v>1.8793050899116124</v>
+      </c>
+      <c r="E68" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F68" s="3">
+        <f t="shared" si="6"/>
+        <v>20.045920959057195</v>
+      </c>
+      <c r="G68" s="3">
+        <f t="shared" si="7"/>
+        <v>2.0045920959057197E-2</v>
+      </c>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="15"/>
+      <c r="B69" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C69" s="45">
+        <f>2*(TRUNC((D50-0.1-0.23*2)/0.125,0))</f>
+        <v>14</v>
+      </c>
+      <c r="D69" s="3">
+        <f>((0.583*4)+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
+      </c>
+      <c r="E69" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F69" s="3">
+        <f t="shared" si="6"/>
+        <v>4.5042575848224526</v>
+      </c>
+      <c r="G69" s="3">
+        <f t="shared" si="7"/>
+        <v>4.5042575848224528E-3</v>
+      </c>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="15"/>
+      <c r="B70" s="16" t="str">
+        <f>B34</f>
+        <v>-upper beam</v>
+      </c>
+      <c r="C70" s="45">
+        <f>C51*(3*2)</f>
+        <v>12</v>
+      </c>
+      <c r="D70" s="3">
+        <f>D35+0.23*2+(0.583/3.281)*2</f>
+        <v>1.9583236818043277</v>
+      </c>
+      <c r="E70" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F70" s="3">
+        <f t="shared" si="6"/>
+        <v>20.888785939246162</v>
+      </c>
+      <c r="G70" s="3">
+        <f t="shared" si="7"/>
+        <v>2.0888785939246163E-2</v>
+      </c>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="15"/>
+      <c r="B71" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C71" s="45">
+        <f>2*(TRUNC((D51-0.1)/0.125,0))</f>
+        <v>16</v>
+      </c>
+      <c r="D71" s="3">
+        <f>((0.583*4)+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
+      </c>
+      <c r="E71" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F71" s="3">
+        <f t="shared" si="6"/>
+        <v>5.1477229540828029</v>
+      </c>
+      <c r="G71" s="3">
+        <f t="shared" si="7"/>
+        <v>5.1477229540828028E-3</v>
+      </c>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="15"/>
+      <c r="B72" s="16" t="str">
+        <f>B52</f>
+        <v>-slab</v>
+      </c>
+      <c r="C72" s="45">
+        <f>TRUNC(((E52-0.1)/0.15),0)</f>
+        <v>20</v>
+      </c>
+      <c r="D72" s="3">
+        <f>D52*C52</f>
+        <v>5.5623285583663513</v>
+      </c>
+      <c r="E72" s="3">
+        <f t="shared" ref="E72:E75" si="8">8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F72" s="3">
+        <f t="shared" si="6"/>
+        <v>43.949262683388454</v>
+      </c>
+      <c r="G72" s="3">
+        <f t="shared" si="7"/>
+        <v>4.3949262683388453E-2</v>
+      </c>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="15"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="45">
+        <f>2*(TRUNC(((D52-0.1)/0.15),0))</f>
+        <v>34</v>
+      </c>
+      <c r="D73" s="3">
+        <f>E52</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="E73" s="3">
+        <f t="shared" si="8"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F73" s="3">
+        <f t="shared" si="6"/>
+        <v>42.985991172519661</v>
+      </c>
+      <c r="G73" s="3">
+        <f t="shared" si="7"/>
+        <v>4.2985991172519659E-2</v>
+      </c>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="M73">
+        <f>10.5/3.281</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="N73">
+        <f>M73/2</f>
+        <v>1.6001219140505942</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="15"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="45">
+        <f>2*(TRUNC(((D53-0.1)/0.15),0))</f>
+        <v>28</v>
+      </c>
+      <c r="D74" s="3">
+        <f>E53</f>
+        <v>2.895458701615361</v>
+      </c>
+      <c r="E74" s="3">
+        <f t="shared" si="8"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F74" s="3">
+        <f t="shared" si="6"/>
+        <v>32.028777736387198</v>
+      </c>
+      <c r="G74" s="3">
+        <f t="shared" si="7"/>
+        <v>3.2028777736387196E-2</v>
+      </c>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="M74">
+        <f>9.5/3.281</f>
+        <v>2.895458701615361</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="15"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="45">
+        <f>2*(TRUNC(((E53-0.1)/0.15),0))</f>
+        <v>36</v>
+      </c>
+      <c r="D75" s="3">
+        <f>D53</f>
+        <v>2.3239865894544347</v>
+      </c>
+      <c r="E75" s="3">
+        <f t="shared" si="8"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F75" s="3">
+        <f t="shared" ref="F75" si="9">PRODUCT(C75:E75)</f>
+        <v>33.052253716685293</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" ref="G75" si="10">F75/1000</f>
+        <v>3.3052253716685291E-2</v>
+      </c>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="15"/>
+      <c r="B76" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="45">
+        <v>8</v>
+      </c>
+      <c r="D76" s="3">
+        <f>((2.667-0.33)/3.281)+(0.45*2)</f>
+        <v>1.6122828405973788</v>
+      </c>
+      <c r="E76" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F76" s="3">
+        <f t="shared" si="6"/>
+        <v>11.465122422025804</v>
+      </c>
+      <c r="G76" s="3">
+        <f t="shared" si="7"/>
+        <v>1.1465122422025804E-2</v>
+      </c>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="15"/>
+      <c r="B77" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C77" s="45">
+        <f>4*(TRUNC((1.917-0.17*2)/0.33,0)+1)</f>
+        <v>20</v>
+      </c>
+      <c r="D77" s="3">
+        <f>(6*4+2*2)/12/3.281</f>
+        <v>0.7111652951335975</v>
+      </c>
+      <c r="E77" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F77" s="3">
+        <f t="shared" si="6"/>
+        <v>5.6190838134012635</v>
+      </c>
+      <c r="G77" s="3">
+        <f t="shared" si="7"/>
+        <v>5.6190838134012634E-3</v>
+      </c>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+      <c r="J77" s="15"/>
+      <c r="K77" s="15"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="15"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="45">
+        <f>C77</f>
+        <v>20</v>
+      </c>
+      <c r="D78" s="3">
+        <f>(4*4+2*2)/12/3.281</f>
+        <v>0.50797521080971253</v>
+      </c>
+      <c r="E78" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F78" s="3">
+        <f t="shared" si="6"/>
+        <v>4.0136312952866176</v>
+      </c>
+      <c r="G78" s="58">
+        <f t="shared" si="7"/>
+        <v>4.0136312952866173E-3</v>
+      </c>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
+    </row>
+    <row r="79" spans="1:14" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="17"/>
+      <c r="B79" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="19"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="2">
+        <f>SUM(G62:G78)</f>
+        <v>0.45424961405172304</v>
+      </c>
+      <c r="H79" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I79" s="46">
+        <v>132360</v>
+      </c>
+      <c r="J79" s="22">
+        <f>G79*I79</f>
+        <v>60124.478915886059</v>
+      </c>
+      <c r="K79" s="20"/>
+    </row>
+    <row r="80" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="24"/>
+      <c r="B80" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="22">
+        <f>0.13*G79*105000</f>
+        <v>6200.5072318060193</v>
+      </c>
+      <c r="K80" s="26"/>
+    </row>
+    <row r="81" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="24"/>
+      <c r="B81" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="22">
+        <f>0.13*G79*1200</f>
+        <v>70.862939792068801</v>
+      </c>
+      <c r="K81" s="26"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="15"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="15"/>
+      <c r="G82" s="15"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
+    </row>
+    <row r="83" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="11">
+        <v>7</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="15"/>
+      <c r="K83" s="15"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="15"/>
+      <c r="B84" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C84" s="45">
+        <v>2</v>
+      </c>
+      <c r="D84" s="3">
+        <f>12/3.281</f>
+        <v>3.6574215178299299</v>
+      </c>
+      <c r="E84" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F84" s="15"/>
+      <c r="G84" s="3">
+        <f>PRODUCT(C84:F84)</f>
+        <v>6.583358732093874</v>
+      </c>
+      <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
+      <c r="J84" s="15"/>
+      <c r="K84" s="15"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="15"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="45">
+        <v>2</v>
+      </c>
+      <c r="D85" s="3">
+        <f>21/3.281</f>
+        <v>6.4004876562023769</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F85" s="15"/>
+      <c r="G85" s="3">
+        <f>PRODUCT(C85:F85)</f>
+        <v>11.520877781164279</v>
+      </c>
+      <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
+      <c r="J85" s="15"/>
+      <c r="K85" s="15"/>
+    </row>
+    <row r="86" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="17"/>
+      <c r="B86" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="19"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="2">
+        <f>SUM(G84:G85)</f>
+        <v>18.104236513258151</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I86" s="2">
+        <v>689.98</v>
+      </c>
+      <c r="J86" s="22">
+        <f>G86*I86</f>
+        <v>12491.561109417858</v>
+      </c>
+      <c r="K86" s="20"/>
+    </row>
+    <row r="87" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="24"/>
+      <c r="B87" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C87" s="26"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="22">
+        <f>0.13*G86*1694.03/10</f>
+        <v>398.69855714721115</v>
+      </c>
+      <c r="K87" s="26"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="15"/>
+      <c r="B88" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" s="26"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="27"/>
+      <c r="H88" s="26"/>
+      <c r="I88" s="26"/>
+      <c r="J88" s="22">
+        <f>0.13*G86*472.02/10</f>
+        <v>111.09230234684546</v>
+      </c>
+      <c r="K88" s="15"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="15"/>
+      <c r="B89" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89" s="26"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="27"/>
+      <c r="G89" s="27"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="26"/>
+      <c r="J89" s="22">
+        <f>0.13*G86*1207.6/10</f>
+        <v>284.21478817433706</v>
+      </c>
+      <c r="K89" s="15"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="15"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="15"/>
+      <c r="G90" s="15"/>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
+    </row>
+    <row r="91" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A91" s="11">
+        <v>8</v>
+      </c>
+      <c r="B91" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="15"/>
+      <c r="B92" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C92" s="45">
+        <v>1</v>
+      </c>
+      <c r="D92" s="3">
+        <f>12.667/3.281</f>
+        <v>3.8607131971959765</v>
+      </c>
+      <c r="E92" s="3">
+        <f>9.75/3.281</f>
+        <v>2.9716549832368178</v>
+      </c>
+      <c r="F92" s="15"/>
+      <c r="G92" s="3">
+        <f>PRODUCT(C92:F92)</f>
+        <v>11.47270761129557</v>
+      </c>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
+    </row>
+    <row r="93" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="17"/>
+      <c r="B93" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" s="19"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="20"/>
+      <c r="F93" s="20"/>
+      <c r="G93" s="2">
+        <f>SUM(G92)</f>
+        <v>11.47270761129557</v>
+      </c>
+      <c r="H93" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I93" s="2">
+        <v>6851.63</v>
+      </c>
+      <c r="J93" s="22">
+        <f>G93*I93</f>
+        <v>78606.747650781064</v>
+      </c>
+      <c r="K93" s="20"/>
+    </row>
+    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="24"/>
+      <c r="B94" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C94" s="26"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="27"/>
+      <c r="G94" s="27"/>
+      <c r="H94" s="26"/>
+      <c r="I94" s="26"/>
+      <c r="J94" s="22">
+        <f>0.13*G93*1694.03/10</f>
+        <v>252.65644137191944</v>
+      </c>
+      <c r="K94" s="26"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="15"/>
+      <c r="B95" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="26"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+      <c r="H95" s="26"/>
+      <c r="I95" s="26"/>
+      <c r="J95" s="22">
+        <f>0.13*G93*581.55/10</f>
+        <v>86.735390447536204</v>
+      </c>
+      <c r="K95" s="15"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="15"/>
+      <c r="B96" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C96" s="26"/>
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="27"/>
+      <c r="G96" s="27"/>
+      <c r="H96" s="26"/>
+      <c r="I96" s="26"/>
+      <c r="J96" s="22">
+        <f>0.13*G93*43319.76/10</f>
+        <v>6460.9342235294662</v>
+      </c>
+      <c r="K96" s="15"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="15"/>
+      <c r="B97" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C97" s="26"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="27"/>
+      <c r="G97" s="27"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="26"/>
+      <c r="J97" s="22">
+        <f>0.13*G93*46.25/10</f>
+        <v>6.8979654512914621</v>
+      </c>
+      <c r="K97" s="15"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="15"/>
+      <c r="B98" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C98" s="26"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="22">
+        <f>0.13*G93*43.3/10</f>
+        <v>6.4579871143982759</v>
+      </c>
+      <c r="K98" s="15"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="15"/>
+      <c r="B99" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="26"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
+      <c r="F99" s="27"/>
+      <c r="G99" s="27"/>
+      <c r="H99" s="26"/>
+      <c r="I99" s="26"/>
+      <c r="J99" s="22">
+        <f>0.13*G93*118.89/10</f>
+        <v>17.731872702790096</v>
+      </c>
+      <c r="K99" s="15"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="15"/>
+      <c r="B100" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C100" s="26"/>
+      <c r="D100" s="27"/>
+      <c r="E100" s="27"/>
+      <c r="F100" s="27"/>
+      <c r="G100" s="27"/>
+      <c r="H100" s="26"/>
+      <c r="I100" s="26"/>
+      <c r="J100" s="22">
+        <f>0.13*G93*120/10</f>
+        <v>17.89742387362109</v>
+      </c>
+      <c r="K100" s="15"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="15"/>
+      <c r="B101" s="15"/>
+      <c r="C101" s="15"/>
+      <c r="D101" s="15"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="15"/>
+      <c r="G101" s="15"/>
+      <c r="H101" s="15"/>
+      <c r="I101" s="15"/>
+      <c r="J101" s="15"/>
+      <c r="K101" s="15"/>
+    </row>
+    <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A102" s="11">
+        <v>9</v>
+      </c>
+      <c r="B102" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C102" s="15"/>
+      <c r="D102" s="15"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="15"/>
+      <c r="G102" s="15"/>
+      <c r="H102" s="15"/>
+      <c r="I102" s="15"/>
+      <c r="J102" s="15"/>
+      <c r="K102" s="15"/>
+    </row>
+    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="24"/>
+      <c r="B103" s="25" t="str">
+        <f t="shared" ref="B103:D105" si="11">B134</f>
+        <v>-for wing walls of stand tap</v>
+      </c>
+      <c r="C103" s="49">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="D103" s="27">
+        <f t="shared" si="11"/>
+        <v>1.2163181956720512</v>
+      </c>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27">
+        <f>F134</f>
+        <v>0.6</v>
+      </c>
+      <c r="G103" s="27">
+        <f t="shared" ref="G103:G109" si="12">PRODUCT(C103:F103)</f>
+        <v>2.9191636696129231</v>
+      </c>
+      <c r="H103" s="26"/>
+      <c r="I103" s="26"/>
+      <c r="J103" s="26"/>
+      <c r="K103" s="26"/>
+    </row>
+    <row r="104" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="24"/>
+      <c r="B104" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>-for side wall of stand tap</v>
+      </c>
+      <c r="C104" s="49">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="D104" s="27">
+        <f t="shared" si="11"/>
+        <v>1.3197195976836331</v>
+      </c>
+      <c r="E104" s="27"/>
+      <c r="F104" s="27">
+        <f>F135</f>
+        <v>0.6</v>
+      </c>
+      <c r="G104" s="27">
+        <f t="shared" si="12"/>
+        <v>0.79183175861017985</v>
+      </c>
+      <c r="H104" s="26"/>
+      <c r="I104" s="26"/>
+      <c r="J104" s="26"/>
+      <c r="K104" s="26"/>
+    </row>
+    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="24"/>
+      <c r="B105" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>-stand</v>
+      </c>
+      <c r="C105" s="49">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="D105" s="27">
+        <f t="shared" si="11"/>
+        <v>0.35659859798841814</v>
+      </c>
+      <c r="E105" s="27"/>
+      <c r="F105" s="27">
+        <f>F136</f>
+        <v>1.2</v>
+      </c>
+      <c r="G105" s="27">
+        <f t="shared" si="12"/>
+        <v>0.42791831758610177</v>
+      </c>
+      <c r="H105" s="26"/>
+      <c r="I105" s="26"/>
+      <c r="J105" s="26"/>
+      <c r="K105" s="26"/>
+    </row>
+    <row r="106" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="24"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="49">
+        <f>C137</f>
+        <v>1</v>
+      </c>
+      <c r="D106" s="27">
+        <f>D137</f>
+        <v>0.46</v>
+      </c>
+      <c r="E106" s="27"/>
+      <c r="F106" s="27">
+        <f>F137</f>
+        <v>0.6</v>
+      </c>
+      <c r="G106" s="27">
+        <f t="shared" si="12"/>
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="H106" s="26"/>
+      <c r="I106" s="26"/>
+      <c r="J106" s="26"/>
+      <c r="K106" s="26"/>
+    </row>
+    <row r="107" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="24"/>
+      <c r="B107" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C107" s="49">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D107" s="27">
+        <f>M10</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="E107" s="27">
+        <f>N10</f>
+        <v>1.6763181956720512</v>
+      </c>
+      <c r="F107" s="27"/>
+      <c r="G107" s="27">
+        <f t="shared" si="12"/>
+        <v>2.8100426931412015</v>
+      </c>
+      <c r="H107" s="26"/>
+      <c r="I107" s="26"/>
+      <c r="J107" s="26"/>
+      <c r="K107" s="26"/>
+    </row>
+    <row r="108" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="24"/>
+      <c r="B108" s="25" t="str">
+        <f>B84</f>
+        <v>-peti area</v>
+      </c>
+      <c r="C108" s="49">
+        <f>C84</f>
+        <v>2</v>
+      </c>
+      <c r="D108" s="27">
+        <f>D84</f>
+        <v>3.6574215178299299</v>
+      </c>
+      <c r="E108" s="27">
+        <f>E84</f>
+        <v>0.9</v>
+      </c>
+      <c r="F108" s="27"/>
+      <c r="G108" s="27">
+        <f t="shared" si="12"/>
+        <v>6.583358732093874</v>
+      </c>
+      <c r="H108" s="26"/>
+      <c r="I108" s="26"/>
+      <c r="J108" s="26"/>
+      <c r="K108" s="26"/>
+    </row>
+    <row r="109" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="24"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="49">
+        <f>C85</f>
+        <v>2</v>
+      </c>
+      <c r="D109" s="27">
+        <f>D85</f>
+        <v>6.4004876562023769</v>
+      </c>
+      <c r="E109" s="27">
+        <f>E85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F109" s="27"/>
+      <c r="G109" s="27">
+        <f t="shared" si="12"/>
+        <v>11.520877781164279</v>
+      </c>
+      <c r="H109" s="26"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="26"/>
+      <c r="K109" s="26"/>
+    </row>
+    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="17"/>
+      <c r="B110" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" s="19"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="20"/>
+      <c r="F110" s="20"/>
+      <c r="G110" s="2">
+        <f>SUM(G103:G109)</f>
+        <v>25.329192952208558</v>
+      </c>
+      <c r="H110" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I110" s="2">
+        <v>287.32</v>
+      </c>
+      <c r="J110" s="22">
+        <f>G110*I110</f>
+        <v>7277.5837190285629</v>
+      </c>
+      <c r="K110" s="20"/>
+    </row>
+    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="24"/>
+      <c r="B111" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C111" s="26"/>
+      <c r="D111" s="27"/>
+      <c r="E111" s="27"/>
+      <c r="F111" s="27"/>
+      <c r="G111" s="27"/>
+      <c r="H111" s="26"/>
+      <c r="I111" s="26"/>
+      <c r="J111" s="22">
+        <f>0.13*G110*693.24/10</f>
+        <v>228.26972638845783</v>
+      </c>
+      <c r="K111" s="26"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="15"/>
+      <c r="B112" s="15"/>
+      <c r="C112" s="15"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="15"/>
+      <c r="G112" s="15"/>
+      <c r="H112" s="15"/>
+      <c r="I112" s="15"/>
+      <c r="J112" s="15"/>
+      <c r="K112" s="15"/>
+    </row>
+    <row r="113" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A113" s="11">
+        <v>10</v>
+      </c>
+      <c r="B113" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C113" s="15"/>
+      <c r="D113" s="15"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="15"/>
+      <c r="G113" s="15"/>
+      <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
+      <c r="J113" s="15"/>
+      <c r="K113" s="15"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="15"/>
+      <c r="B114" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C114" s="45">
+        <v>2</v>
+      </c>
+      <c r="D114" s="3">
+        <f>9.75/3.281</f>
+        <v>2.9716549832368178</v>
+      </c>
+      <c r="E114" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F114" s="3">
+        <f>(10-3.5-0.33*2)/3.281</f>
+        <v>1.7799451386772325</v>
+      </c>
+      <c r="G114" s="3">
+        <f t="shared" ref="G114:G117" si="13">PRODUCT(C114:F114)</f>
+        <v>3.7025679888668424</v>
+      </c>
+      <c r="H114" s="15"/>
+      <c r="I114" s="15"/>
+      <c r="J114" s="15"/>
+      <c r="K114" s="15"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="15"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="45">
+        <v>2</v>
+      </c>
+      <c r="D115" s="3">
+        <f>15/3.281</f>
+        <v>4.5717768972874122</v>
+      </c>
+      <c r="E115" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F115" s="3">
+        <f>(10-3.5-0.33*2)/3.281</f>
+        <v>1.7799451386772325</v>
+      </c>
+      <c r="G115" s="3">
+        <f t="shared" si="13"/>
+        <v>5.6962584444105273</v>
+      </c>
+      <c r="H115" s="15"/>
+      <c r="I115" s="15"/>
+      <c r="J115" s="15"/>
+      <c r="K115" s="15"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="15"/>
+      <c r="B116" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C116" s="45">
+        <v>-1</v>
+      </c>
+      <c r="D116" s="3">
+        <f>1.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="E116" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F116" s="3">
+        <f>(7-3.5)/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G116" s="3">
+        <f t="shared" si="13"/>
+        <v>-0.56004266991770779</v>
+      </c>
+      <c r="H116" s="15"/>
+      <c r="I116" s="15"/>
+      <c r="J116" s="15"/>
+      <c r="K116" s="15"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="15"/>
+      <c r="B117" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C117" s="45">
+        <v>-2</v>
+      </c>
+      <c r="D117" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="E117" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F117" s="3">
+        <f>(7-3.5)/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G117" s="3">
+        <f t="shared" si="13"/>
+        <v>-0.79656582127886921</v>
+      </c>
+      <c r="H117" s="15"/>
+      <c r="I117" s="15"/>
+      <c r="J117" s="15"/>
+      <c r="K117" s="15"/>
+    </row>
+    <row r="118" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="24"/>
+      <c r="B118" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C118" s="49">
+        <f>C14*2</f>
+        <v>2</v>
+      </c>
+      <c r="D118" s="27">
+        <f>N10-O10*2</f>
+        <v>1.2163181956720512</v>
+      </c>
+      <c r="E118" s="27">
+        <f>O10</f>
+        <v>0.23</v>
+      </c>
+      <c r="F118" s="27">
+        <f>P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G118" s="27">
+        <f>PRODUCT(C118:F118)</f>
+        <v>0.33570382200548615</v>
+      </c>
+      <c r="H118" s="26"/>
+      <c r="I118" s="26"/>
+      <c r="J118" s="26"/>
+      <c r="K118" s="26"/>
+    </row>
+    <row r="119" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="24"/>
+      <c r="B119" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C119" s="49">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D119" s="27">
+        <f>M10-R10</f>
+        <v>1.3197195976836331</v>
+      </c>
+      <c r="E119" s="27">
+        <f>O10</f>
+        <v>0.23</v>
+      </c>
+      <c r="F119" s="27">
+        <f>P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G119" s="27">
+        <f>PRODUCT(C119:F119)</f>
+        <v>0.18212130448034136</v>
+      </c>
+      <c r="H119" s="26"/>
+      <c r="I119" s="26"/>
+      <c r="J119" s="26"/>
+      <c r="K119" s="26"/>
+    </row>
+    <row r="120" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="24"/>
+      <c r="B120" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120" s="49">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D120" s="27">
+        <f>R10</f>
+        <v>0.35659859798841814</v>
+      </c>
+      <c r="E120" s="27">
+        <f>O10</f>
+        <v>0.23</v>
+      </c>
+      <c r="F120" s="27">
+        <f>Q10</f>
+        <v>1.2</v>
+      </c>
+      <c r="G120" s="27">
+        <f>PRODUCT(C120:F120)</f>
+        <v>9.8421213044803404E-2</v>
+      </c>
+      <c r="H120" s="26"/>
+      <c r="I120" s="26"/>
+      <c r="J120" s="26"/>
+      <c r="K120" s="26"/>
+    </row>
+    <row r="121" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="17"/>
+      <c r="B121" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="19"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="20"/>
+      <c r="F121" s="20"/>
+      <c r="G121" s="2">
+        <f>SUM(G114:G120)</f>
+        <v>8.6584642816114226</v>
+      </c>
+      <c r="H121" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I121" s="2">
+        <f>14491.84</f>
+        <v>14491.84</v>
+      </c>
+      <c r="J121" s="22">
+        <f>G121*I121</f>
+        <v>125477.07901482769</v>
+      </c>
+      <c r="K121" s="20"/>
+    </row>
+    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="24"/>
+      <c r="B122" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C122" s="26"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="27"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="27"/>
+      <c r="H122" s="26"/>
+      <c r="I122" s="26"/>
+      <c r="J122" s="22">
+        <f>0.13*G121*8481.2</f>
+        <v>9546.4417444763658</v>
+      </c>
+      <c r="K122" s="26"/>
+    </row>
+    <row r="123" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="24"/>
+      <c r="B123" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C123" s="26"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="27"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="27"/>
+      <c r="H123" s="26"/>
+      <c r="I123" s="26"/>
+      <c r="J123" s="22">
+        <f>0.13*G121*912.17</f>
+        <v>1026.738877288474</v>
+      </c>
+      <c r="K123" s="26"/>
+    </row>
+    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="24"/>
+      <c r="B124" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C124" s="26"/>
+      <c r="D124" s="27"/>
+      <c r="E124" s="27"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="27"/>
+      <c r="H124" s="26"/>
+      <c r="I124" s="26"/>
+      <c r="J124" s="22">
+        <f>0.13*G121*953.37</f>
+        <v>1073.1136119807848</v>
+      </c>
+      <c r="K124" s="26"/>
+    </row>
+    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="24"/>
+      <c r="B125" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C125" s="26"/>
+      <c r="D125" s="27"/>
+      <c r="E125" s="27"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="27"/>
+      <c r="H125" s="26"/>
+      <c r="I125" s="26"/>
+      <c r="J125" s="22">
+        <f>0.13*G121*28</f>
+        <v>31.516809985065578</v>
+      </c>
+      <c r="K125" s="26"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="15"/>
+      <c r="B126" s="15"/>
+      <c r="C126" s="15"/>
+      <c r="D126" s="15"/>
+      <c r="E126" s="15"/>
+      <c r="F126" s="15"/>
+      <c r="G126" s="15"/>
+      <c r="H126" s="15"/>
+      <c r="I126" s="15"/>
+      <c r="J126" s="15"/>
+      <c r="K126" s="15"/>
+    </row>
+    <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="11">
+        <v>11</v>
+      </c>
+      <c r="B127" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C127" s="15"/>
+      <c r="D127" s="15"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="15"/>
+      <c r="G127" s="15"/>
+      <c r="H127" s="15"/>
+      <c r="I127" s="15"/>
+      <c r="J127" s="15"/>
+      <c r="K127" s="15"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="15"/>
+      <c r="B128" s="16" t="str">
+        <f>B114</f>
+        <v>-for wall continue</v>
+      </c>
+      <c r="C128" s="45">
+        <v>1</v>
+      </c>
+      <c r="D128" s="3">
+        <f>(15*2+(9.75+1.17*2)*2)/3.281</f>
+        <v>16.513258153002134</v>
+      </c>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="G128" s="3">
+        <f>PRODUCT(C128:F128)</f>
+        <v>50.329954748558777</v>
+      </c>
+      <c r="H128" s="15"/>
+      <c r="I128" s="15"/>
+      <c r="J128" s="15"/>
+      <c r="K128" s="15"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="15"/>
+      <c r="B129" s="16"/>
+      <c r="C129" s="45">
+        <v>1</v>
+      </c>
+      <c r="D129" s="3">
+        <f>((15-1.17*2)*2+(9.75*2))/3.281</f>
+        <v>13.660469369094788</v>
+      </c>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3">
+        <f>(10-3.5)/3.281</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="G129" s="3">
+        <f>PRODUCT(C129:F129)</f>
+        <v>27.062801249349626</v>
+      </c>
+      <c r="H129" s="15"/>
+      <c r="I129" s="15"/>
+      <c r="J129" s="15"/>
+      <c r="K129" s="15"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="15"/>
+      <c r="B130" s="16" t="str">
+        <f>B116</f>
+        <v>-deduction for door</v>
+      </c>
+      <c r="C130" s="45">
+        <v>-2</v>
+      </c>
+      <c r="D130" s="3">
+        <f>D116</f>
+        <v>1.5</v>
+      </c>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3">
+        <f>7/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
+      <c r="G130" s="3">
+        <f t="shared" ref="G130:G133" si="14">PRODUCT(C130:F130)</f>
+        <v>-6.400487656202376</v>
+      </c>
+      <c r="H130" s="15"/>
+      <c r="I130" s="15"/>
+      <c r="J130" s="15"/>
+      <c r="K130" s="15"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="15"/>
+      <c r="B131" s="16" t="str">
+        <f>B117</f>
+        <v>-deduction for window</v>
+      </c>
+      <c r="C131" s="45">
+        <f>2*C117</f>
+        <v>-4</v>
+      </c>
+      <c r="D131" s="3">
+        <f>D117</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3">
+        <f>F117</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G131" s="3">
+        <f t="shared" si="14"/>
+        <v>-4.5518046930221097</v>
+      </c>
+      <c r="H131" s="15"/>
+      <c r="I131" s="15"/>
+      <c r="J131" s="15"/>
+      <c r="K131" s="15"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="15"/>
+      <c r="B132" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C132" s="45">
+        <v>2</v>
+      </c>
+      <c r="D132" s="3">
+        <f>D52</f>
+        <v>2.7811642791831757</v>
+      </c>
+      <c r="E132" s="3">
+        <f>E52</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3">
+        <f t="shared" si="14"/>
+        <v>17.800807638782896</v>
+      </c>
+      <c r="H132" s="15"/>
+      <c r="I132" s="15"/>
+      <c r="J132" s="15"/>
+      <c r="K132" s="15"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="15"/>
+      <c r="B133" s="16"/>
+      <c r="C133" s="45">
+        <v>2</v>
+      </c>
+      <c r="D133" s="3">
+        <f>D53</f>
+        <v>2.3239865894544347</v>
+      </c>
+      <c r="E133" s="3">
+        <f>E53</f>
+        <v>2.895458701615361</v>
+      </c>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3">
+        <f t="shared" si="14"/>
+        <v>13.458014385746496</v>
+      </c>
+      <c r="H133" s="15"/>
+      <c r="I133" s="15"/>
+      <c r="J133" s="15"/>
+      <c r="K133" s="15"/>
+    </row>
+    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="24"/>
+      <c r="B134" s="25" t="str">
+        <f>B118</f>
+        <v>-for wing walls of stand tap</v>
+      </c>
+      <c r="C134" s="49">
+        <f>C14*4</f>
+        <v>4</v>
+      </c>
+      <c r="D134" s="27">
+        <f>M10-O10*2</f>
+        <v>1.2163181956720512</v>
+      </c>
+      <c r="E134" s="27"/>
+      <c r="F134" s="27">
+        <f>P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G134" s="27">
+        <f>PRODUCT(C134:F134)</f>
+        <v>2.9191636696129231</v>
+      </c>
+      <c r="H134" s="26"/>
+      <c r="I134" s="26"/>
+      <c r="J134" s="26"/>
+      <c r="K134" s="26"/>
+    </row>
+    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="24"/>
+      <c r="B135" s="25" t="str">
+        <f>B119</f>
+        <v>-for side wall of stand tap</v>
+      </c>
+      <c r="C135" s="49">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D135" s="27">
+        <f>M10-R10</f>
+        <v>1.3197195976836331</v>
+      </c>
+      <c r="E135" s="27"/>
+      <c r="F135" s="27">
+        <f>P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G135" s="27">
+        <f>PRODUCT(C135:F135)</f>
+        <v>0.79183175861017985</v>
+      </c>
+      <c r="H135" s="26"/>
+      <c r="I135" s="26"/>
+      <c r="J135" s="26"/>
+      <c r="K135" s="26"/>
+    </row>
+    <row r="136" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="24"/>
+      <c r="B136" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C136" s="49">
+        <f>C14</f>
+        <v>1</v>
+      </c>
+      <c r="D136" s="27">
+        <f>R10</f>
+        <v>0.35659859798841814</v>
+      </c>
+      <c r="E136" s="27"/>
+      <c r="F136" s="27">
+        <f>Q10</f>
+        <v>1.2</v>
+      </c>
+      <c r="G136" s="27">
+        <f>PRODUCT(C136:F136)</f>
+        <v>0.42791831758610177</v>
+      </c>
+      <c r="H136" s="26"/>
+      <c r="I136" s="26"/>
+      <c r="J136" s="26"/>
+      <c r="K136" s="26"/>
+    </row>
+    <row r="137" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="24"/>
+      <c r="B137" s="25"/>
+      <c r="C137" s="49">
+        <f>C136</f>
+        <v>1</v>
+      </c>
+      <c r="D137" s="27">
+        <f>O10*2</f>
+        <v>0.46</v>
+      </c>
+      <c r="E137" s="27"/>
+      <c r="F137" s="27">
+        <f>Q10-P10</f>
+        <v>0.6</v>
+      </c>
+      <c r="G137" s="27">
+        <f>PRODUCT(C137:F137)</f>
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="H137" s="26"/>
+      <c r="I137" s="26"/>
+      <c r="J137" s="26"/>
+      <c r="K137" s="26"/>
+    </row>
+    <row r="138" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="17"/>
+      <c r="B138" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" s="19"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="20"/>
+      <c r="F138" s="20"/>
+      <c r="G138" s="2">
+        <f>SUM(G128:G137)</f>
+        <v>102.11419941902254</v>
+      </c>
+      <c r="H138" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I138" s="2">
+        <v>415.5</v>
+      </c>
+      <c r="J138" s="22">
+        <f>G138*I138</f>
+        <v>42428.449858603868</v>
+      </c>
+      <c r="K138" s="20"/>
+    </row>
+    <row r="139" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="24"/>
+      <c r="B139" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C139" s="26"/>
+      <c r="D139" s="27"/>
+      <c r="E139" s="27"/>
+      <c r="F139" s="27"/>
+      <c r="G139" s="27"/>
+      <c r="H139" s="26"/>
+      <c r="I139" s="26"/>
+      <c r="J139" s="22">
+        <f>0.13*G138*7010.67/100</f>
+        <v>930.65564077324643</v>
+      </c>
+      <c r="K139" s="26"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="15"/>
+      <c r="B140" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="26"/>
+      <c r="D140" s="27"/>
+      <c r="E140" s="27"/>
+      <c r="F140" s="27"/>
+      <c r="G140" s="27"/>
+      <c r="H140" s="26"/>
+      <c r="I140" s="26"/>
+      <c r="J140" s="22">
+        <f>0.13*G138*4639.73/100</f>
+        <v>615.91700881154782</v>
+      </c>
+      <c r="K140" s="15"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" s="15"/>
+      <c r="B141" s="15"/>
+      <c r="C141" s="15"/>
+      <c r="D141" s="15"/>
+      <c r="E141" s="15"/>
+      <c r="F141" s="15"/>
+      <c r="G141" s="15"/>
+      <c r="H141" s="15"/>
+      <c r="I141" s="15"/>
+      <c r="J141" s="15"/>
+      <c r="K141" s="15"/>
+    </row>
+    <row r="142" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A142" s="11">
+        <v>12</v>
+      </c>
+      <c r="B142" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C142" s="15"/>
+      <c r="D142" s="15"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="15"/>
+      <c r="G142" s="15"/>
+      <c r="H142" s="15"/>
+      <c r="I142" s="15"/>
+      <c r="J142" s="15"/>
+      <c r="K142" s="15"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" s="15"/>
+      <c r="B143" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C143" s="45">
+        <v>1</v>
+      </c>
+      <c r="D143" s="3">
+        <f>((15-1.17*2)*2+(9.75*2))/3.281</f>
+        <v>13.660469369094788</v>
+      </c>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3">
+        <f>(3.5)/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G143" s="3">
+        <f>PRODUCT(C143:F143)</f>
+        <v>14.572277595803643</v>
+      </c>
+      <c r="H143" s="15"/>
+      <c r="I143" s="15"/>
+      <c r="J143" s="15"/>
+      <c r="K143" s="15"/>
+    </row>
+    <row r="144" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="24"/>
+      <c r="B144" s="25" t="str">
+        <f>B130</f>
+        <v>-deduction for door</v>
+      </c>
+      <c r="C144" s="49">
+        <f>-1</f>
+        <v>-1</v>
+      </c>
+      <c r="D144" s="27">
+        <f>D130</f>
+        <v>1.5</v>
+      </c>
+      <c r="E144" s="27"/>
+      <c r="F144" s="27">
+        <f>F143</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G144" s="27">
+        <f>PRODUCT(C144:F144)</f>
+        <v>-1.600121914050594</v>
+      </c>
+      <c r="H144" s="26"/>
+      <c r="I144" s="26"/>
+      <c r="J144" s="26"/>
+      <c r="K144" s="26"/>
+    </row>
+    <row r="145" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="17"/>
+      <c r="B145" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="19"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="20"/>
+      <c r="F145" s="20"/>
+      <c r="G145" s="2">
+        <f>SUM(G143:G144)</f>
+        <v>12.972155681753048</v>
+      </c>
+      <c r="H145" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I145" s="2">
+        <v>2845.18</v>
+      </c>
+      <c r="J145" s="22">
+        <f>G145*I145</f>
+        <v>36908.117902610131</v>
+      </c>
+      <c r="K145" s="20"/>
+    </row>
+    <row r="146" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="24"/>
+      <c r="B146" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C146" s="26"/>
+      <c r="D146" s="27"/>
+      <c r="E146" s="27"/>
+      <c r="F146" s="27"/>
+      <c r="G146" s="27"/>
+      <c r="H146" s="26"/>
+      <c r="I146" s="26"/>
+      <c r="J146" s="22">
+        <f>0.13*G145*729.73/10</f>
+        <v>123.06022515339347</v>
+      </c>
+      <c r="K146" s="26"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="15"/>
+      <c r="B147" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147" s="26"/>
+      <c r="D147" s="27"/>
+      <c r="E147" s="27"/>
+      <c r="F147" s="27"/>
+      <c r="G147" s="27"/>
+      <c r="H147" s="26"/>
+      <c r="I147" s="26"/>
+      <c r="J147" s="22">
+        <f>0.13*G145*483.04/10</f>
+        <v>81.458911046681905</v>
+      </c>
+      <c r="K147" s="15"/>
+    </row>
+    <row r="148" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="24"/>
+      <c r="B148" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C148" s="26"/>
+      <c r="D148" s="27"/>
+      <c r="E148" s="27"/>
+      <c r="F148" s="27"/>
+      <c r="G148" s="27"/>
+      <c r="H148" s="26"/>
+      <c r="I148" s="26"/>
+      <c r="J148" s="22">
+        <f>0.13*G145*100.06/10</f>
+        <v>16.873920667710731</v>
+      </c>
+      <c r="K148" s="26"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" s="15"/>
+      <c r="B149" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C149" s="26"/>
+      <c r="D149" s="27"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="22">
+        <f>0.13*G145*6746.52/10</f>
+        <v>1137.7198007507875</v>
+      </c>
+      <c r="K149" s="15"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" s="15"/>
+      <c r="B150" s="15"/>
+      <c r="C150" s="15"/>
+      <c r="D150" s="15"/>
+      <c r="E150" s="15"/>
+      <c r="F150" s="15"/>
+      <c r="G150" s="15"/>
+      <c r="H150" s="15"/>
+      <c r="I150" s="15"/>
+      <c r="J150" s="15"/>
+      <c r="K150" s="15"/>
+    </row>
+    <row r="151" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A151" s="11">
+        <v>13</v>
+      </c>
+      <c r="B151" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C151" s="15"/>
+      <c r="D151" s="15"/>
+      <c r="E151" s="15"/>
+      <c r="F151" s="15"/>
+      <c r="G151" s="15"/>
+      <c r="H151" s="15"/>
+      <c r="I151" s="15"/>
+      <c r="J151" s="15"/>
+      <c r="K151" s="15"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="15"/>
+      <c r="B152" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C152" s="45">
+        <f>C128</f>
+        <v>1</v>
+      </c>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3">
+        <f>SUM(G128:G133)</f>
+        <v>97.699285673213325</v>
+      </c>
+      <c r="H152" s="15"/>
+      <c r="I152" s="15"/>
+      <c r="J152" s="15"/>
+      <c r="K152" s="15"/>
+    </row>
+    <row r="153" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="17"/>
+      <c r="B153" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" s="19"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="20"/>
+      <c r="F153" s="20"/>
+      <c r="G153" s="2">
+        <f>SUM(G152:G152)</f>
+        <v>97.699285673213325</v>
+      </c>
+      <c r="H153" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I153" s="2">
+        <v>253.8</v>
+      </c>
+      <c r="J153" s="22">
+        <f>G153*I153</f>
+        <v>24796.078703861542</v>
+      </c>
+      <c r="K153" s="20"/>
+    </row>
+    <row r="154" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="24"/>
+      <c r="B154" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C154" s="26"/>
+      <c r="D154" s="27"/>
+      <c r="E154" s="27"/>
+      <c r="F154" s="27"/>
+      <c r="G154" s="27"/>
+      <c r="H154" s="26"/>
+      <c r="I154" s="26"/>
+      <c r="J154" s="22">
+        <f>0.13*G153*2304/100</f>
+        <v>292.62890044840856</v>
+      </c>
+      <c r="K154" s="26"/>
+    </row>
+    <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="24"/>
+      <c r="B155" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C155" s="26"/>
+      <c r="D155" s="27"/>
+      <c r="E155" s="27"/>
+      <c r="F155" s="27"/>
+      <c r="G155" s="27"/>
+      <c r="H155" s="26"/>
+      <c r="I155" s="26"/>
+      <c r="J155" s="22">
+        <f>0.13*G153*10432/100</f>
+        <v>1324.95863258585</v>
+      </c>
+      <c r="K155" s="26"/>
+    </row>
+    <row r="156" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="24"/>
+      <c r="B156" s="25"/>
+      <c r="C156" s="26"/>
+      <c r="D156" s="27"/>
+      <c r="E156" s="27"/>
+      <c r="F156" s="27"/>
+      <c r="G156" s="27"/>
+      <c r="H156" s="26"/>
+      <c r="I156" s="26"/>
+      <c r="J156" s="22"/>
+      <c r="K156" s="26"/>
+    </row>
+    <row r="157" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A157" s="11">
+        <v>14</v>
+      </c>
+      <c r="B157" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C157" s="15"/>
+      <c r="D157" s="15"/>
+      <c r="E157" s="15"/>
+      <c r="F157" s="15"/>
+      <c r="G157" s="15"/>
+      <c r="H157" s="15"/>
+      <c r="I157" s="15"/>
+      <c r="J157" s="15"/>
+      <c r="K157" s="15"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" s="15"/>
+      <c r="B158" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C158" s="45">
+        <f>C135</f>
+        <v>1</v>
+      </c>
+      <c r="D158" s="3">
+        <f>(18.25*2+15.25*2)/3.281</f>
+        <v>20.42060347455044</v>
+      </c>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3">
+        <f>PRODUCT(C158:F158)</f>
+        <v>20.42060347455044</v>
+      </c>
+      <c r="H158" s="15"/>
+      <c r="I158" s="15"/>
+      <c r="J158" s="15"/>
+      <c r="K158" s="15"/>
+    </row>
+    <row r="159" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="17"/>
+      <c r="B159" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" s="19"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="20"/>
+      <c r="F159" s="20"/>
+      <c r="G159" s="2">
+        <f>SUM(G158:G158)</f>
+        <v>20.42060347455044</v>
+      </c>
+      <c r="H159" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="I159" s="2">
+        <v>144.41</v>
+      </c>
+      <c r="J159" s="22">
+        <f>G159*I159</f>
+        <v>2948.9393477598287</v>
+      </c>
+      <c r="K159" s="20"/>
+    </row>
+    <row r="160" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="24"/>
+      <c r="B160" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C160" s="26"/>
+      <c r="D160" s="27"/>
+      <c r="E160" s="27"/>
+      <c r="F160" s="27"/>
+      <c r="G160" s="27"/>
+      <c r="H160" s="26"/>
+      <c r="I160" s="26"/>
+      <c r="J160" s="22">
+        <f>0.13*G159*91.21</f>
+        <v>242.1332215787869</v>
+      </c>
+      <c r="K160" s="26"/>
+    </row>
+    <row r="161" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="24"/>
+      <c r="B161" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C161" s="26"/>
+      <c r="D161" s="27"/>
+      <c r="E161" s="27"/>
+      <c r="F161" s="27"/>
+      <c r="G161" s="27"/>
+      <c r="H161" s="26"/>
+      <c r="I161" s="26"/>
+      <c r="J161" s="22">
+        <f>0.13*G159*12.71</f>
+        <v>33.740963120999695</v>
+      </c>
+      <c r="K161" s="26"/>
+    </row>
+    <row r="162" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="24"/>
+      <c r="B162" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C162" s="26"/>
+      <c r="D162" s="27"/>
+      <c r="E162" s="27"/>
+      <c r="F162" s="27"/>
+      <c r="G162" s="27"/>
+      <c r="H162" s="26"/>
+      <c r="I162" s="26"/>
+      <c r="J162" s="22">
+        <f>0.13*G159*0.02</f>
+        <v>5.3093569033831146E-2</v>
+      </c>
+      <c r="K162" s="26"/>
+    </row>
+    <row r="163" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="24"/>
+      <c r="B163" s="25"/>
+      <c r="C163" s="26"/>
+      <c r="D163" s="27"/>
+      <c r="E163" s="27"/>
+      <c r="F163" s="27"/>
+      <c r="G163" s="27"/>
+      <c r="H163" s="26"/>
+      <c r="I163" s="26"/>
+      <c r="J163" s="22"/>
+      <c r="K163" s="26"/>
+    </row>
+    <row r="164" spans="1:11" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A164" s="24">
+        <v>15</v>
+      </c>
+      <c r="B164" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C164" s="26"/>
+      <c r="D164" s="27"/>
+      <c r="E164" s="27"/>
+      <c r="F164" s="27"/>
+      <c r="G164" s="27"/>
+      <c r="H164" s="26"/>
+      <c r="I164" s="26"/>
+      <c r="J164" s="22"/>
+      <c r="K164" s="26"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" s="15"/>
+      <c r="B165" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C165" s="45">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3">
+        <f>D116</f>
+        <v>1.5</v>
+      </c>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3">
+        <f>7/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
+      <c r="G165" s="3">
+        <f>PRODUCT(C165:F165)</f>
+        <v>3.200243828101188</v>
+      </c>
+      <c r="H165" s="15"/>
+      <c r="I165" s="15"/>
+      <c r="J165" s="15"/>
+      <c r="K165" s="15"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" s="15"/>
+      <c r="B166" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C166" s="45">
+        <v>2</v>
+      </c>
+      <c r="D166" s="3">
+        <f>D117</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3">
+        <f>F117</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G166" s="3">
+        <f>PRODUCT(C166:F166)</f>
+        <v>2.2759023465110548</v>
+      </c>
+      <c r="H166" s="15"/>
+      <c r="I166" s="15"/>
+      <c r="J166" s="15"/>
+      <c r="K166" s="15"/>
+    </row>
+    <row r="167" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="17"/>
+      <c r="B167" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" s="19"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="20"/>
+      <c r="F167" s="20"/>
+      <c r="G167" s="2">
+        <f>SUM(G165:G166)</f>
+        <v>5.4761461746122428</v>
+      </c>
+      <c r="H167" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I167" s="2">
+        <v>37363.64</v>
+      </c>
+      <c r="J167" s="22">
+        <f>G167*I167</f>
+        <v>204608.75425558898</v>
+      </c>
+      <c r="K167" s="20"/>
+    </row>
+    <row r="168" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="24"/>
+      <c r="B168" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C168" s="26"/>
+      <c r="D168" s="27"/>
+      <c r="E168" s="27"/>
+      <c r="F168" s="27"/>
+      <c r="G168" s="27"/>
+      <c r="H168" s="26"/>
+      <c r="I168" s="26"/>
+      <c r="J168" s="22">
+        <f>0.13*G167*7910.91/0.92</f>
+        <v>6121.4879776589405</v>
+      </c>
+      <c r="K168" s="26"/>
+    </row>
+    <row r="169" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="24"/>
+      <c r="B169" s="25"/>
+      <c r="C169" s="26"/>
+      <c r="D169" s="27"/>
+      <c r="E169" s="27"/>
+      <c r="F169" s="27"/>
+      <c r="G169" s="27"/>
+      <c r="H169" s="26"/>
+      <c r="I169" s="26"/>
+      <c r="J169" s="22"/>
+      <c r="K169" s="26"/>
+    </row>
+    <row r="170" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A170" s="24">
+        <v>16</v>
+      </c>
+      <c r="B170" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C170" s="26"/>
+      <c r="D170" s="26"/>
+      <c r="E170" s="26"/>
+      <c r="F170" s="26"/>
+      <c r="G170" s="26"/>
+      <c r="H170" s="26"/>
+      <c r="I170" s="26"/>
+      <c r="J170" s="26"/>
+      <c r="K170" s="26"/>
+    </row>
+    <row r="171" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="24"/>
+      <c r="B171" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C171" s="26">
+        <v>1</v>
+      </c>
+      <c r="D171" s="27">
+        <f>Q10</f>
+        <v>1.2</v>
+      </c>
+      <c r="E171" s="26"/>
+      <c r="F171" s="26"/>
+      <c r="G171" s="27">
+        <f t="shared" ref="G171" si="15">PRODUCT(C171:F171)</f>
+        <v>1.2</v>
+      </c>
+      <c r="H171" s="26"/>
+      <c r="I171" s="26"/>
+      <c r="J171" s="22"/>
+      <c r="K171" s="26"/>
+    </row>
+    <row r="172" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="17"/>
+      <c r="B172" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="C172" s="19"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="20"/>
+      <c r="F172" s="20"/>
+      <c r="G172" s="56">
+        <f>SUM(G171:G171)</f>
+        <v>1.2</v>
+      </c>
+      <c r="H172" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="I172" s="2">
+        <v>248</v>
+      </c>
+      <c r="J172" s="56">
+        <f>G172*I172</f>
+        <v>297.59999999999997</v>
+      </c>
+      <c r="K172" s="20"/>
+    </row>
+    <row r="173" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="24"/>
+      <c r="B173" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C173" s="26"/>
+      <c r="D173" s="26"/>
+      <c r="E173" s="26"/>
+      <c r="F173" s="26"/>
+      <c r="G173" s="26"/>
+      <c r="H173" s="26"/>
+      <c r="I173" s="26"/>
+      <c r="J173" s="22">
+        <f>0.13*J172</f>
+        <v>38.687999999999995</v>
+      </c>
+      <c r="K173" s="26"/>
+    </row>
+    <row r="174" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="24"/>
+      <c r="B174" s="50"/>
+      <c r="C174" s="26"/>
+      <c r="D174" s="26"/>
+      <c r="E174" s="26"/>
+      <c r="F174" s="26"/>
+      <c r="G174" s="26"/>
+      <c r="H174" s="26"/>
+      <c r="I174" s="26"/>
+      <c r="J174" s="26"/>
+      <c r="K174" s="26"/>
+    </row>
+    <row r="175" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A175" s="11">
+        <v>17</v>
+      </c>
+      <c r="B175" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C175" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="E175" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="F175" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="G175" s="15"/>
+      <c r="H175" s="15"/>
+      <c r="I175" s="15"/>
+      <c r="J175" s="15"/>
+      <c r="K175" s="15"/>
+    </row>
+    <row r="176" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A176" s="13"/>
+      <c r="B176" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="C176" s="45">
+        <f>8+6+6+4</f>
+        <v>24</v>
+      </c>
+      <c r="D176" s="3">
+        <f>0.9+0.23</f>
+        <v>1.1300000000000001</v>
+      </c>
+      <c r="E176" s="3">
+        <v>3.54</v>
+      </c>
+      <c r="F176" s="3">
+        <f>PRODUCT(C176:E176)</f>
+        <v>96.004800000000017</v>
+      </c>
+      <c r="G176" s="3">
+        <f>F176</f>
+        <v>96.004800000000017</v>
+      </c>
+      <c r="H176" s="15"/>
+      <c r="I176" s="15"/>
+      <c r="J176" s="15"/>
+      <c r="K176" s="15"/>
+    </row>
+    <row r="177" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A177" s="13"/>
+      <c r="B177" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="C177" s="45">
+        <v>1</v>
+      </c>
+      <c r="D177" s="3">
+        <f>(21+18+18+16-0.25*4)/3.281</f>
+        <v>21.94452910697958</v>
+      </c>
+      <c r="E177" s="3">
+        <v>2.93</v>
+      </c>
+      <c r="F177" s="3">
+        <f>PRODUCT(C177:E177)</f>
+        <v>64.297470283450167</v>
+      </c>
+      <c r="G177" s="3">
+        <f>F177</f>
+        <v>64.297470283450167</v>
+      </c>
+      <c r="H177" s="15"/>
+      <c r="I177" s="15"/>
+      <c r="J177" s="15"/>
+      <c r="K177" s="15"/>
+    </row>
+    <row r="178" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="17"/>
+      <c r="B178" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" s="19"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="20"/>
+      <c r="F178" s="20"/>
+      <c r="G178" s="2">
+        <f>SUM(G176:G177)</f>
+        <v>160.30227028345018</v>
+      </c>
+      <c r="H178" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="I178" s="2">
+        <v>182.51</v>
+      </c>
+      <c r="J178" s="22">
+        <f>G178*I178</f>
+        <v>29256.767349432492</v>
+      </c>
+      <c r="K178" s="20"/>
+    </row>
+    <row r="179" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A179" s="24"/>
+      <c r="B179" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="C179" s="38"/>
+      <c r="D179" s="39"/>
+      <c r="E179" s="39"/>
+      <c r="F179" s="39"/>
+      <c r="G179" s="39"/>
+      <c r="H179" s="38"/>
+      <c r="I179" s="38"/>
+      <c r="J179" s="21">
+        <f>0.13*G178*1761.42/18.94</f>
+        <v>1938.0544477269127</v>
+      </c>
+      <c r="K179" s="38"/>
+    </row>
+    <row r="180" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="24"/>
+      <c r="B180" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C180" s="26"/>
+      <c r="D180" s="27"/>
+      <c r="E180" s="27"/>
+      <c r="F180" s="27"/>
+      <c r="G180" s="27"/>
+      <c r="H180" s="26"/>
+      <c r="I180" s="26"/>
+      <c r="J180" s="22">
+        <f>0.13*G178*110/18.94</f>
+        <v>121.03075317071475</v>
+      </c>
+      <c r="K180" s="26"/>
+    </row>
+    <row r="181" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="24"/>
+      <c r="B181" s="25"/>
+      <c r="C181" s="26"/>
+      <c r="D181" s="27"/>
+      <c r="E181" s="27"/>
+      <c r="F181" s="27"/>
+      <c r="G181" s="27"/>
+      <c r="H181" s="26"/>
+      <c r="I181" s="26"/>
+      <c r="J181" s="22"/>
+      <c r="K181" s="26"/>
+    </row>
+    <row r="182" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A182" s="17">
+        <v>18</v>
+      </c>
+      <c r="B182" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C182" s="19">
+        <v>1</v>
+      </c>
+      <c r="D182" s="1"/>
+      <c r="E182" s="20"/>
+      <c r="F182" s="20"/>
+      <c r="G182" s="21">
+        <f t="shared" ref="G182" si="16">PRODUCT(C182:F182)</f>
+        <v>1</v>
+      </c>
+      <c r="H182" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I182" s="2">
+        <v>15000</v>
+      </c>
+      <c r="J182" s="21">
+        <f>G182*I182</f>
+        <v>15000</v>
+      </c>
+      <c r="K182" s="20"/>
+    </row>
+    <row r="183" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="17"/>
+      <c r="B183" s="31"/>
+      <c r="C183" s="19"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="20"/>
+      <c r="F183" s="20"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="21"/>
+      <c r="I183" s="2"/>
+      <c r="J183" s="22"/>
+      <c r="K183" s="20"/>
+    </row>
+    <row r="184" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="17">
+        <v>19</v>
+      </c>
+      <c r="B184" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C184" s="19">
+        <v>1</v>
+      </c>
+      <c r="D184" s="1"/>
+      <c r="E184" s="20"/>
+      <c r="F184" s="20"/>
+      <c r="G184" s="21">
+        <f t="shared" ref="G184" si="17">PRODUCT(C184:F184)</f>
+        <v>1</v>
+      </c>
+      <c r="H184" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I184" s="2">
+        <v>1000</v>
+      </c>
+      <c r="J184" s="21">
+        <f>G184*I184</f>
+        <v>1000</v>
+      </c>
+      <c r="K184" s="20"/>
+    </row>
+    <row r="185" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="17"/>
+      <c r="B185" s="31"/>
+      <c r="C185" s="19"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="20"/>
+      <c r="F185" s="20"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="21"/>
+      <c r="I185" s="2"/>
+      <c r="J185" s="22"/>
+      <c r="K185" s="20"/>
+    </row>
+    <row r="186" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="32"/>
+      <c r="B186" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="34"/>
+      <c r="D186" s="35"/>
+      <c r="E186" s="35"/>
+      <c r="F186" s="35"/>
+      <c r="G186" s="22"/>
+      <c r="H186" s="22"/>
+      <c r="I186" s="22"/>
+      <c r="J186" s="22">
+        <f>SUM(J19:J184)</f>
+        <v>809604.15128198045</v>
+      </c>
+      <c r="K186" s="36"/>
+    </row>
+    <row r="187" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="37"/>
+      <c r="B188" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C188" s="63">
+        <f>J186</f>
+        <v>809604.15128198045</v>
+      </c>
+      <c r="D188" s="64"/>
+      <c r="E188" s="39">
+        <v>100</v>
+      </c>
+      <c r="F188" s="37"/>
+      <c r="G188" s="40"/>
+      <c r="H188" s="37"/>
+      <c r="I188" s="41"/>
+      <c r="J188" s="42"/>
+      <c r="K188" s="43"/>
+    </row>
+    <row r="189" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B189" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C189" s="67">
+        <v>700000</v>
+      </c>
+      <c r="D189" s="68"/>
+      <c r="E189" s="39"/>
+    </row>
+    <row r="190" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B190" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C190" s="67">
+        <f>C189-C192-C193</f>
+        <v>665000</v>
+      </c>
+      <c r="D190" s="68"/>
+      <c r="E190" s="39">
+        <f>C190/C188*100</f>
+        <v>82.138906890113546</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B191" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C191" s="69">
+        <f>C188-C190</f>
+        <v>144604.15128198045</v>
+      </c>
+      <c r="D191" s="69"/>
+      <c r="E191" s="39">
+        <f>100-E190</f>
+        <v>17.861093109886454</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B192" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C192" s="63">
+        <f>C189*0.03</f>
+        <v>21000</v>
+      </c>
+      <c r="D192" s="64"/>
+      <c r="E192" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B193" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C193" s="63">
+        <f>C189*0.02</f>
+        <v>14000</v>
+      </c>
+      <c r="D193" s="64"/>
       <c r="E193" s="39">
         <v>2</v>
       </c>
@@ -9364,8 +13637,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992611D8-A0C5-4567-9F40-3446FA06F1FA}">
   <dimension ref="A1:Y193"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9381,113 +13654,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="72" t="s">
+      <c r="H7" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
     </row>
     <row r="8" spans="1:25" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -10155,19 +14428,19 @@
         <v>2</v>
       </c>
       <c r="D36" s="3">
-        <f>((18.25)/2)/3.281</f>
-        <v>2.7811642791831757</v>
+        <f>((18.25+6.5)/2)/3.281</f>
+        <v>3.7717159402621152</v>
       </c>
       <c r="E36" s="3">
-        <f>10.5/3.281</f>
-        <v>3.2002438281011885</v>
+        <f>6.917/3.281</f>
+        <v>2.1081987199024685</v>
       </c>
       <c r="F36" s="3">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G36" s="3">
         <f t="shared" si="1"/>
-        <v>1.335060572908717</v>
+        <v>1.192729007564449</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
@@ -10181,19 +14454,19 @@
         <v>2</v>
       </c>
       <c r="D37" s="3">
-        <f>((15.25)/2)/3.281</f>
-        <v>2.3239865894544347</v>
+        <f>((15.25+5.25)/2)/3.281</f>
+        <v>3.1240475464797317</v>
       </c>
       <c r="E37" s="3">
-        <f>9.5/3.281</f>
-        <v>2.895458701615361</v>
+        <f>6.25/3.281</f>
+        <v>1.9049070405364217</v>
       </c>
       <c r="F37" s="3">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G37" s="3">
         <f t="shared" si="1"/>
-        <v>1.0093510789309872</v>
+        <v>0.89265302493896614</v>
       </c>
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
@@ -10238,7 +14511,7 @@
       <c r="F39" s="20"/>
       <c r="G39" s="2">
         <f>SUM(G32:G38)</f>
-        <v>4.4914970526321456</v>
+        <v>4.2324674332958558</v>
       </c>
       <c r="H39" s="21" t="s">
         <v>28</v>
@@ -10248,7 +14521,7 @@
       </c>
       <c r="J39" s="22">
         <f>G39*I39</f>
-        <v>62689.126897732123</v>
+        <v>59073.77538206592</v>
       </c>
       <c r="K39" s="20"/>
     </row>
@@ -10266,7 +14539,7 @@
       <c r="I40" s="26"/>
       <c r="J40" s="22">
         <f>0.13*G39*5212.4</f>
-        <v>3043.492300828173</v>
+        <v>2867.9707224104714</v>
       </c>
       <c r="K40" s="26"/>
     </row>
@@ -10284,7 +14557,7 @@
       <c r="I41" s="26"/>
       <c r="J41" s="22">
         <f>0.13*G39*(1912.03+921.59)</f>
-        <v>1654.5354641763349</v>
+        <v>1559.1165678836544</v>
       </c>
       <c r="K41" s="26"/>
     </row>
@@ -10302,7 +14575,7 @@
       <c r="I42" s="26"/>
       <c r="J42" s="22">
         <f>0.13*G39*1350.6</f>
-        <v>788.60806950704682</v>
+        <v>743.1281670032198</v>
       </c>
       <c r="K42" s="26"/>
     </row>
@@ -10320,7 +14593,7 @@
       <c r="I43" s="15"/>
       <c r="J43" s="22">
         <f>0.13*G39*56</f>
-        <v>32.698098543162018</v>
+        <v>30.81236291439383</v>
       </c>
       <c r="K43" s="15"/>
     </row>
@@ -10338,7 +14611,7 @@
       <c r="I44" s="26"/>
       <c r="J44" s="22">
         <f>0.13*G39*392.92</f>
-        <v>229.42387284962894</v>
+        <v>216.19274350577902</v>
       </c>
       <c r="K44" s="26"/>
     </row>
@@ -10356,7 +14629,7 @@
       <c r="I45" s="15"/>
       <c r="J45" s="22">
         <f>0.13*G39*14.15</f>
-        <v>8.2621088283168316</v>
+        <v>7.785623843547727</v>
       </c>
       <c r="K45" s="15"/>
     </row>
@@ -10508,16 +14781,16 @@
       </c>
       <c r="D52" s="3">
         <f t="shared" si="5"/>
-        <v>2.7811642791831757</v>
+        <v>3.7717159402621152</v>
       </c>
       <c r="E52" s="3">
         <f>E36</f>
-        <v>3.2002438281011885</v>
+        <v>2.1081987199024685</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3">
         <f t="shared" si="2"/>
-        <v>17.800807638782896</v>
+        <v>15.903053434192653</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="15"/>
@@ -10533,16 +14806,16 @@
       </c>
       <c r="D53" s="3">
         <f>D37</f>
-        <v>2.3239865894544347</v>
+        <v>3.1240475464797317</v>
       </c>
       <c r="E53" s="3">
         <f>E37</f>
-        <v>2.895458701615361</v>
+        <v>1.9049070405364217</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f t="shared" si="2"/>
-        <v>13.458014385746496</v>
+        <v>11.902040332519549</v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="15"/>
@@ -10588,7 +14861,7 @@
       <c r="F55" s="20"/>
       <c r="G55" s="2">
         <f>SUM(G48:G54)</f>
-        <v>50.578395813008513</v>
+        <v>47.124667555191323</v>
       </c>
       <c r="H55" s="21" t="s">
         <v>34</v>
@@ -10598,7 +14871,7 @@
       </c>
       <c r="J55" s="22">
         <f>G55*I55</f>
-        <v>46669.191600621089</v>
+        <v>43482.40199985059</v>
       </c>
       <c r="K55" s="20"/>
     </row>
@@ -10616,7 +14889,7 @@
       <c r="I56" s="26"/>
       <c r="J56" s="22">
         <f>0.13*G55*20062.02/100</f>
-        <v>1319.1162248790411</v>
+        <v>1229.0408298812793</v>
       </c>
       <c r="K56" s="26"/>
     </row>
@@ -10634,7 +14907,7 @@
       <c r="I57" s="26"/>
       <c r="J57" s="22">
         <f>0.13*G55*13328.25/100</f>
-        <v>876.35795519314979</v>
+        <v>816.51615544522235</v>
       </c>
       <c r="K57" s="26"/>
     </row>
@@ -10652,7 +14925,7 @@
       <c r="I58" s="26"/>
       <c r="J58" s="22">
         <f>0.13*G55*10137.6/100</f>
-        <v>666.56660901214161</v>
+        <v>621.05033874975993</v>
       </c>
       <c r="K58" s="26"/>
     </row>
@@ -10670,7 +14943,7 @@
       <c r="I59" s="15"/>
       <c r="J59" s="22">
         <f>0.13*G55*3300/100</f>
-        <v>216.98131803780652</v>
+        <v>202.16482381177076</v>
       </c>
       <c r="K59" s="15"/>
     </row>
@@ -11020,11 +15293,11 @@
       </c>
       <c r="C72" s="45">
         <f>TRUNC(((E52-0.1)/0.15),0)</f>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D72" s="3">
         <f>D52*C52</f>
-        <v>5.5623285583663513</v>
+        <v>7.5434318805242304</v>
       </c>
       <c r="E72" s="3">
         <f t="shared" ref="E72:E75" si="8">8*8/162</f>
@@ -11032,11 +15305,11 @@
       </c>
       <c r="F72" s="3">
         <f t="shared" si="6"/>
-        <v>43.949262683388454</v>
+        <v>38.741576077754075</v>
       </c>
       <c r="G72" s="3">
         <f t="shared" si="7"/>
-        <v>4.3949262683388453E-2</v>
+        <v>3.8741576077754074E-2</v>
       </c>
       <c r="H72" s="15"/>
       <c r="I72" s="15"/>
@@ -11048,11 +15321,11 @@
       <c r="B73" s="16"/>
       <c r="C73" s="45">
         <f>2*(TRUNC(((D52-0.1)/0.15),0))</f>
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D73" s="3">
         <f>E52</f>
-        <v>3.2002438281011885</v>
+        <v>2.1081987199024685</v>
       </c>
       <c r="E73" s="3">
         <f t="shared" si="8"/>
@@ -11060,11 +15333,11 @@
       </c>
       <c r="F73" s="3">
         <f t="shared" si="6"/>
-        <v>42.985991172519661</v>
+        <v>39.977694244076439</v>
       </c>
       <c r="G73" s="3">
         <f t="shared" si="7"/>
-        <v>4.2985991172519659E-2</v>
+        <v>3.9977694244076441E-2</v>
       </c>
       <c r="H73" s="15"/>
       <c r="I73" s="15"/>
@@ -11084,11 +15357,11 @@
       <c r="B74" s="16"/>
       <c r="C74" s="45">
         <f>2*(TRUNC(((D53-0.1)/0.15),0))</f>
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D74" s="3">
         <f>E53</f>
-        <v>2.895458701615361</v>
+        <v>1.9049070405364217</v>
       </c>
       <c r="E74" s="3">
         <f t="shared" si="8"/>
@@ -11096,11 +15369,11 @@
       </c>
       <c r="F74" s="3">
         <f t="shared" si="6"/>
-        <v>32.028777736387198</v>
+        <v>30.102234714649622</v>
       </c>
       <c r="G74" s="3">
         <f t="shared" si="7"/>
-        <v>3.2028777736387196E-2</v>
+        <v>3.0102234714649623E-2</v>
       </c>
       <c r="H74" s="15"/>
       <c r="I74" s="15"/>
@@ -11116,23 +15389,23 @@
       <c r="B75" s="16"/>
       <c r="C75" s="45">
         <f>2*(TRUNC(((E53-0.1)/0.15),0))</f>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D75" s="3">
         <f>D53</f>
-        <v>2.3239865894544347</v>
+        <v>3.1240475464797317</v>
       </c>
       <c r="E75" s="3">
         <f t="shared" si="8"/>
         <v>0.39506172839506171</v>
       </c>
       <c r="F75" s="3">
-        <f t="shared" ref="F75" si="9">PRODUCT(C75:E75)</f>
-        <v>33.052253716685293</v>
+        <f t="shared" si="6"/>
+        <v>29.620598959215233</v>
       </c>
       <c r="G75" s="3">
-        <f t="shared" ref="G75" si="10">F75/1000</f>
-        <v>3.3052253716685291E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.9620598959215233E-2</v>
       </c>
       <c r="H75" s="15"/>
       <c r="I75" s="15"/>
@@ -11148,8 +15421,8 @@
         <v>8</v>
       </c>
       <c r="D76" s="3">
-        <f>((2.667-0.33)/3.281)+(0.45*2)</f>
-        <v>1.6122828405973788</v>
+        <f>((3.33-0.33)/3.281)+(0.45*2)</f>
+        <v>1.8143553794574825</v>
       </c>
       <c r="E76" s="3">
         <f>12*12/162</f>
@@ -11157,11 +15430,11 @@
       </c>
       <c r="F76" s="3">
         <f t="shared" si="6"/>
-        <v>11.465122422025804</v>
+        <v>12.902082698364319</v>
       </c>
       <c r="G76" s="3">
         <f t="shared" si="7"/>
-        <v>1.1465122422025804E-2</v>
+        <v>1.290208269836432E-2</v>
       </c>
       <c r="H76" s="15"/>
       <c r="I76" s="15"/>
@@ -11237,7 +15510,7 @@
       <c r="F79" s="20"/>
       <c r="G79" s="2">
         <f>SUM(G62:G78)</f>
-        <v>0.45424961405172304</v>
+        <v>0.44211239301477639</v>
       </c>
       <c r="H79" s="21" t="s">
         <v>41</v>
@@ -11247,7 +15520,7 @@
       </c>
       <c r="J79" s="22">
         <f>G79*I79</f>
-        <v>60124.478915886059</v>
+        <v>58517.996339435806</v>
       </c>
       <c r="K79" s="20"/>
     </row>
@@ -11265,7 +15538,7 @@
       <c r="I80" s="26"/>
       <c r="J80" s="22">
         <f>0.13*G79*105000</f>
-        <v>6200.5072318060193</v>
+        <v>6034.8341646516974</v>
       </c>
       <c r="K80" s="26"/>
     </row>
@@ -11283,7 +15556,7 @@
       <c r="I81" s="26"/>
       <c r="J81" s="22">
         <f>0.13*G79*1200</f>
-        <v>70.862939792068801</v>
+        <v>68.969533310305124</v>
       </c>
       <c r="K81" s="26"/>
     </row>
@@ -11684,15 +15957,15 @@
     <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="24"/>
       <c r="B103" s="25" t="str">
-        <f t="shared" ref="B103:D105" si="11">B134</f>
+        <f t="shared" ref="B103:D105" si="9">B134</f>
         <v>-for wing walls of stand tap</v>
       </c>
       <c r="C103" s="49">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="D103" s="27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.2163181956720512</v>
       </c>
       <c r="E103" s="27"/>
@@ -11701,7 +15974,7 @@
         <v>0.6</v>
       </c>
       <c r="G103" s="27">
-        <f t="shared" ref="G103:G109" si="12">PRODUCT(C103:F103)</f>
+        <f t="shared" ref="G103:G109" si="10">PRODUCT(C103:F103)</f>
         <v>2.9191636696129231</v>
       </c>
       <c r="H103" s="26"/>
@@ -11712,15 +15985,15 @@
     <row r="104" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="24"/>
       <c r="B104" s="25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-for side wall of stand tap</v>
       </c>
       <c r="C104" s="49">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D104" s="27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.3197195976836331</v>
       </c>
       <c r="E104" s="27"/>
@@ -11729,7 +16002,7 @@
         <v>0.6</v>
       </c>
       <c r="G104" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.79183175861017985</v>
       </c>
       <c r="H104" s="26"/>
@@ -11740,15 +16013,15 @@
     <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="24"/>
       <c r="B105" s="25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-stand</v>
       </c>
       <c r="C105" s="49">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D105" s="27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.35659859798841814</v>
       </c>
       <c r="E105" s="27"/>
@@ -11757,7 +16030,7 @@
         <v>1.2</v>
       </c>
       <c r="G105" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.42791831758610177</v>
       </c>
       <c r="H105" s="26"/>
@@ -11782,7 +16055,7 @@
         <v>0.6</v>
       </c>
       <c r="G106" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.27600000000000002</v>
       </c>
       <c r="H106" s="26"/>
@@ -11800,17 +16073,17 @@
         <v>1</v>
       </c>
       <c r="D107" s="27">
-        <f>M10</f>
-        <v>1.6763181956720512</v>
+        <f>M10-0.23*2</f>
+        <v>1.2163181956720512</v>
       </c>
       <c r="E107" s="27">
-        <f>N10</f>
-        <v>1.6763181956720512</v>
+        <f>N10-0.23</f>
+        <v>1.4463181956720512</v>
       </c>
       <c r="F107" s="27"/>
       <c r="G107" s="27">
-        <f t="shared" si="12"/>
-        <v>2.8100426931412015</v>
+        <f t="shared" si="10"/>
+        <v>1.7591831381274861</v>
       </c>
       <c r="H107" s="26"/>
       <c r="I107" s="26"/>
@@ -11837,7 +16110,7 @@
       </c>
       <c r="F108" s="27"/>
       <c r="G108" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>6.583358732093874</v>
       </c>
       <c r="H108" s="26"/>
@@ -11862,7 +16135,7 @@
       </c>
       <c r="F109" s="27"/>
       <c r="G109" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>11.520877781164279</v>
       </c>
       <c r="H109" s="26"/>
@@ -11881,7 +16154,7 @@
       <c r="F110" s="20"/>
       <c r="G110" s="2">
         <f>SUM(G103:G109)</f>
-        <v>25.329192952208558</v>
+        <v>24.278333397194842</v>
       </c>
       <c r="H110" s="21" t="s">
         <v>34</v>
@@ -11891,7 +16164,7 @@
       </c>
       <c r="J110" s="22">
         <f>G110*I110</f>
-        <v>7277.5837190285629</v>
+        <v>6975.650751682022</v>
       </c>
       <c r="K110" s="20"/>
     </row>
@@ -11909,7 +16182,7 @@
       <c r="I111" s="26"/>
       <c r="J111" s="22">
         <f>0.13*G110*693.24/10</f>
-        <v>228.26972638845783</v>
+        <v>218.79925397552762</v>
       </c>
       <c r="K111" s="26"/>
     </row>
@@ -11963,7 +16236,7 @@
         <v>1.7799451386772325</v>
       </c>
       <c r="G114" s="3">
-        <f t="shared" ref="G114:G117" si="13">PRODUCT(C114:F114)</f>
+        <f t="shared" ref="G114:G117" si="11">PRODUCT(C114:F114)</f>
         <v>3.7025679888668424</v>
       </c>
       <c r="H114" s="15"/>
@@ -11989,7 +16262,7 @@
         <v>1.7799451386772325</v>
       </c>
       <c r="G115" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>5.6962584444105273</v>
       </c>
       <c r="H115" s="15"/>
@@ -12017,7 +16290,7 @@
         <v>1.0667479427003961</v>
       </c>
       <c r="G116" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>-0.56004266991770779</v>
       </c>
       <c r="H116" s="15"/>
@@ -12045,7 +16318,7 @@
         <v>1.0667479427003961</v>
       </c>
       <c r="G117" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>-0.79656582127886921</v>
       </c>
       <c r="H117" s="15"/>
@@ -12341,7 +16614,7 @@
         <v>2.1334958854007922</v>
       </c>
       <c r="G130" s="3">
-        <f t="shared" ref="G130:G133" si="14">PRODUCT(C130:F130)</f>
+        <f t="shared" ref="G130:G133" si="12">PRODUCT(C130:F130)</f>
         <v>-6.400487656202376</v>
       </c>
       <c r="H130" s="15"/>
@@ -12369,7 +16642,7 @@
         <v>1.0667479427003961</v>
       </c>
       <c r="G131" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-4.5518046930221097</v>
       </c>
       <c r="H131" s="15"/>
@@ -12387,16 +16660,16 @@
       </c>
       <c r="D132" s="3">
         <f>D52</f>
-        <v>2.7811642791831757</v>
+        <v>3.7717159402621152</v>
       </c>
       <c r="E132" s="3">
         <f>E52</f>
-        <v>3.2002438281011885</v>
+        <v>2.1081987199024685</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="3">
-        <f t="shared" si="14"/>
-        <v>17.800807638782896</v>
+        <f t="shared" si="12"/>
+        <v>15.903053434192653</v>
       </c>
       <c r="H132" s="15"/>
       <c r="I132" s="15"/>
@@ -12411,16 +16684,16 @@
       </c>
       <c r="D133" s="3">
         <f>D53</f>
-        <v>2.3239865894544347</v>
+        <v>3.1240475464797317</v>
       </c>
       <c r="E133" s="3">
         <f>E53</f>
-        <v>2.895458701615361</v>
+        <v>1.9049070405364217</v>
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="3">
-        <f t="shared" si="14"/>
-        <v>13.458014385746496</v>
+        <f t="shared" si="12"/>
+        <v>11.902040332519549</v>
       </c>
       <c r="H133" s="15"/>
       <c r="I133" s="15"/>
@@ -12546,7 +16819,7 @@
       <c r="F138" s="20"/>
       <c r="G138" s="2">
         <f>SUM(G128:G137)</f>
-        <v>102.11419941902254</v>
+        <v>98.660471161205351</v>
       </c>
       <c r="H138" s="21" t="s">
         <v>34</v>
@@ -12556,7 +16829,7 @@
       </c>
       <c r="J138" s="22">
         <f>G138*I138</f>
-        <v>42428.449858603868</v>
+        <v>40993.425767480825</v>
       </c>
       <c r="K138" s="20"/>
     </row>
@@ -12574,7 +16847,7 @@
       <c r="I139" s="26"/>
       <c r="J139" s="22">
         <f>0.13*G138*7010.67/100</f>
-        <v>930.65564077324643</v>
+        <v>899.17880696244583</v>
       </c>
       <c r="K139" s="26"/>
     </row>
@@ -12592,7 +16865,7 @@
       <c r="I140" s="26"/>
       <c r="J140" s="22">
         <f>0.13*G138*4639.73/100</f>
-        <v>615.91700881154782</v>
+        <v>595.08533221901303</v>
       </c>
       <c r="K140" s="15"/>
     </row>
@@ -12820,8 +17093,8 @@
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3">
-        <f>SUM(G128:G133)</f>
-        <v>97.699285673213325</v>
+        <f>SUM(G128:G131)</f>
+        <v>66.440463648683931</v>
       </c>
       <c r="H152" s="15"/>
       <c r="I152" s="15"/>
@@ -12839,7 +17112,7 @@
       <c r="F153" s="20"/>
       <c r="G153" s="2">
         <f>SUM(G152:G152)</f>
-        <v>97.699285673213325</v>
+        <v>66.440463648683931</v>
       </c>
       <c r="H153" s="21" t="s">
         <v>34</v>
@@ -12849,7 +17122,7 @@
       </c>
       <c r="J153" s="22">
         <f>G153*I153</f>
-        <v>24796.078703861542</v>
+        <v>16862.589674035982</v>
       </c>
       <c r="K153" s="20"/>
     </row>
@@ -12867,7 +17140,7 @@
       <c r="I154" s="26"/>
       <c r="J154" s="22">
         <f>0.13*G153*2304/100</f>
-        <v>292.62890044840856</v>
+        <v>199.00247672053811</v>
       </c>
       <c r="K154" s="26"/>
     </row>
@@ -12885,7 +17158,7 @@
       <c r="I155" s="26"/>
       <c r="J155" s="22">
         <f>0.13*G153*10432/100</f>
-        <v>1324.95863258585</v>
+        <v>901.03899181799204</v>
       </c>
       <c r="K155" s="26"/>
     </row>
@@ -13040,7 +17313,7 @@
         <v>13</v>
       </c>
       <c r="B164" s="30" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="C164" s="26"/>
       <c r="D164" s="27"/>
@@ -13066,12 +17339,12 @@
       </c>
       <c r="E165" s="3"/>
       <c r="F165" s="3">
-        <f>F116</f>
-        <v>1.0667479427003961</v>
+        <f>F116+3.5/3.281</f>
+        <v>2.1334958854007922</v>
       </c>
       <c r="G165" s="3">
         <f>PRODUCT(C165:F165)</f>
-        <v>1.600121914050594</v>
+        <v>3.200243828101188</v>
       </c>
       <c r="H165" s="15"/>
       <c r="I165" s="15"/>
@@ -13115,7 +17388,7 @@
       <c r="F167" s="20"/>
       <c r="G167" s="2">
         <f>SUM(G165:G166)</f>
-        <v>3.8760242605616488</v>
+        <v>5.4761461746122428</v>
       </c>
       <c r="H167" s="21" t="s">
         <v>34</v>
@@ -13125,7 +17398,7 @@
       </c>
       <c r="J167" s="22">
         <f>G167*I167</f>
-        <v>144822.37510289164</v>
+        <v>204608.75425558898</v>
       </c>
       <c r="K167" s="20"/>
     </row>
@@ -13143,7 +17416,7 @@
       <c r="I168" s="26"/>
       <c r="J168" s="22">
         <f>0.13*G167*7910.91/0.92</f>
-        <v>4332.7981313104001</v>
+        <v>6121.4879776589405</v>
       </c>
       <c r="K168" s="26"/>
     </row>
@@ -13192,7 +17465,7 @@
       <c r="E171" s="26"/>
       <c r="F171" s="26"/>
       <c r="G171" s="27">
-        <f t="shared" ref="G171" si="15">PRODUCT(C171:F171)</f>
+        <f t="shared" ref="G171" si="13">PRODUCT(C171:F171)</f>
         <v>1.2</v>
       </c>
       <c r="H171" s="26"/>
@@ -13426,18 +17699,18 @@
       <c r="E182" s="20"/>
       <c r="F182" s="20"/>
       <c r="G182" s="21">
-        <f t="shared" ref="G182" si="16">PRODUCT(C182:F182)</f>
+        <f t="shared" ref="G182" si="14">PRODUCT(C182:F182)</f>
         <v>1</v>
       </c>
       <c r="H182" s="21" t="s">
         <v>30</v>
       </c>
       <c r="I182" s="2">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="J182" s="21">
         <f>G182*I182</f>
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="K182" s="20"/>
     </row>
@@ -13468,7 +17741,7 @@
       <c r="E184" s="20"/>
       <c r="F184" s="20"/>
       <c r="G184" s="21">
-        <f t="shared" ref="G184" si="17">PRODUCT(C184:F184)</f>
+        <f t="shared" ref="G184" si="15">PRODUCT(C184:F184)</f>
         <v>1</v>
       </c>
       <c r="H184" s="21" t="s">
@@ -13510,7 +17783,7 @@
       <c r="I186" s="22"/>
       <c r="J186" s="22">
         <f>SUM(J19:J184)</f>
-        <v>782529.08228293457</v>
+        <v>799735.92629344447</v>
       </c>
       <c r="K186" s="36"/>
     </row>
@@ -13520,11 +17793,11 @@
       <c r="B188" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C188" s="69">
+      <c r="C188" s="63">
         <f>J186</f>
-        <v>782529.08228293457</v>
-      </c>
-      <c r="D188" s="70"/>
+        <v>799735.92629344447</v>
+      </c>
+      <c r="D188" s="64"/>
       <c r="E188" s="39">
         <v>100</v>
       </c>
@@ -13539,49 +17812,49 @@
       <c r="B189" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C189" s="73">
+      <c r="C189" s="67">
         <v>700000</v>
       </c>
-      <c r="D189" s="74"/>
+      <c r="D189" s="68"/>
       <c r="E189" s="39"/>
     </row>
     <row r="190" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B190" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C190" s="73">
+      <c r="C190" s="67">
         <f>C189-C192-C193</f>
         <v>665000</v>
       </c>
-      <c r="D190" s="74"/>
+      <c r="D190" s="68"/>
       <c r="E190" s="39">
         <f>C190/C188*100</f>
-        <v>84.980867172366601</v>
+        <v>83.152447968930403</v>
       </c>
     </row>
     <row r="191" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B191" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C191" s="75">
+      <c r="C191" s="69">
         <f>C188-C190</f>
-        <v>117529.08228293457</v>
-      </c>
-      <c r="D191" s="75"/>
+        <v>134735.92629344447</v>
+      </c>
+      <c r="D191" s="69"/>
       <c r="E191" s="39">
         <f>100-E190</f>
-        <v>15.019132827633399</v>
+        <v>16.847552031069597</v>
       </c>
     </row>
     <row r="192" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B192" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C192" s="69">
+      <c r="C192" s="63">
         <f>C189*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D192" s="70"/>
+      <c r="D192" s="64"/>
       <c r="E192" s="39">
         <v>3</v>
       </c>
@@ -13590,11 +17863,11 @@
       <c r="B193" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C193" s="69">
+      <c r="C193" s="63">
         <f>C189*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D193" s="70"/>
+      <c r="D193" s="64"/>
       <c r="E193" s="39">
         <v>2</v>
       </c>
